--- a/카드_아키타입/12_완제베이스+활성.xlsx
+++ b/카드_아키타입/12_완제베이스+활성.xlsx
@@ -3231,7 +3231,7 @@
       <row>203</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="122" name="Image 122" descr="Picture"/>
@@ -3256,7 +3256,7 @@
       <row>203</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="123" name="Image 123" descr="Picture"/>
@@ -3281,7 +3281,7 @@
       <row>203</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="124" name="Image 124" descr="Picture"/>
@@ -3306,7 +3306,7 @@
       <row>203</row>
       <rowOff>1085850</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="125" name="Image 125" descr="Picture"/>
@@ -3331,7 +3331,7 @@
       <row>203</row>
       <rowOff>1085850</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="126" name="Image 126" descr="Picture"/>
@@ -3356,7 +3356,7 @@
       <row>203</row>
       <rowOff>1085850</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="127" name="Image 127" descr="Picture"/>
@@ -3431,7 +3431,7 @@
       <row>214</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="130" name="Image 130" descr="Picture"/>
@@ -3456,7 +3456,7 @@
       <row>214</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="131" name="Image 131" descr="Picture"/>
@@ -3481,7 +3481,7 @@
       <row>214</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="132" name="Image 132" descr="Picture"/>
@@ -3506,7 +3506,7 @@
       <row>214</row>
       <rowOff>1085850</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="133" name="Image 133" descr="Picture"/>
@@ -5756,7 +5756,7 @@
       <row>362</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="762000"/>
+    <ext cx="1047750" cy="752475"/>
     <pic>
       <nvPicPr>
         <cNvPr id="223" name="Image 223" descr="Picture"/>
@@ -6702,6 +6702,31 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
+      <colOff>3257550</colOff>
+      <row>430</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="1047750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="261" name="Image 261" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId261"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
       <colOff>0</colOff>
       <row>442</row>
       <rowOff>0</rowOff>
@@ -6709,11 +6734,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="261" name="Image 261" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId261"/>
+        <cNvPr id="262" name="Image 262" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId262"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6734,11 +6759,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="262" name="Image 262" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId262"/>
+        <cNvPr id="263" name="Image 263" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId263"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6759,11 +6784,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="263" name="Image 263" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId263"/>
+        <cNvPr id="264" name="Image 264" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId264"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6784,11 +6809,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="264" name="Image 264" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId264"/>
+        <cNvPr id="265" name="Image 265" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId265"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6809,11 +6834,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="265" name="Image 265" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId265"/>
+        <cNvPr id="266" name="Image 266" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId266"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6834,11 +6859,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="266" name="Image 266" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId266"/>
+        <cNvPr id="267" name="Image 267" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId267"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6859,11 +6884,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="267" name="Image 267" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId267"/>
+        <cNvPr id="268" name="Image 268" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId268"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6884,11 +6909,11 @@
     <ext cx="1047750" cy="981075"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="268" name="Image 268" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId268"/>
+        <cNvPr id="269" name="Image 269" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId269"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6909,11 +6934,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="269" name="Image 269" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId269"/>
+        <cNvPr id="270" name="Image 270" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId270"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6934,11 +6959,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="270" name="Image 270" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId270"/>
+        <cNvPr id="271" name="Image 271" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId271"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6959,11 +6984,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="271" name="Image 271" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId271"/>
+        <cNvPr id="272" name="Image 272" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId272"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6984,11 +7009,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="272" name="Image 272" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId272"/>
+        <cNvPr id="273" name="Image 273" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId273"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7009,11 +7034,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="273" name="Image 273" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId273"/>
+        <cNvPr id="274" name="Image 274" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId274"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7034,11 +7059,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="274" name="Image 274" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId274"/>
+        <cNvPr id="275" name="Image 275" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId275"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7059,11 +7084,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="275" name="Image 275" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId275"/>
+        <cNvPr id="276" name="Image 276" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId276"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7084,11 +7109,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="276" name="Image 276" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId276"/>
+        <cNvPr id="277" name="Image 277" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId277"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7109,11 +7134,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="277" name="Image 277" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId277"/>
+        <cNvPr id="278" name="Image 278" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId278"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7134,11 +7159,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="278" name="Image 278" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId278"/>
+        <cNvPr id="279" name="Image 279" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId279"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7159,11 +7184,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="279" name="Image 279" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId279"/>
+        <cNvPr id="280" name="Image 280" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId280"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7184,11 +7209,11 @@
     <ext cx="1047750" cy="628650"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="280" name="Image 280" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId280"/>
+        <cNvPr id="281" name="Image 281" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId281"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7209,11 +7234,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="281" name="Image 281" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId281"/>
+        <cNvPr id="282" name="Image 282" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId282"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7234,11 +7259,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="282" name="Image 282" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId282"/>
+        <cNvPr id="283" name="Image 283" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId283"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7259,11 +7284,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="283" name="Image 283" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId283"/>
+        <cNvPr id="284" name="Image 284" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId284"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7284,11 +7309,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="284" name="Image 284" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId284"/>
+        <cNvPr id="285" name="Image 285" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId285"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7309,11 +7334,11 @@
     <ext cx="1047750" cy="628650"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="285" name="Image 285" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId285"/>
+        <cNvPr id="286" name="Image 286" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId286"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7334,11 +7359,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="286" name="Image 286" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId286"/>
+        <cNvPr id="287" name="Image 287" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId287"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7359,11 +7384,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="287" name="Image 287" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId287"/>
+        <cNvPr id="288" name="Image 288" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId288"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7384,11 +7409,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="288" name="Image 288" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId288"/>
+        <cNvPr id="289" name="Image 289" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId289"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7409,11 +7434,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="289" name="Image 289" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId289"/>
+        <cNvPr id="290" name="Image 290" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId290"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7434,11 +7459,11 @@
     <ext cx="1047750" cy="638175"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="290" name="Image 290" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId290"/>
+        <cNvPr id="291" name="Image 291" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId291"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7459,11 +7484,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="291" name="Image 291" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId291"/>
+        <cNvPr id="292" name="Image 292" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId292"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7484,11 +7509,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="292" name="Image 292" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId292"/>
+        <cNvPr id="293" name="Image 293" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId293"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7509,11 +7534,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="293" name="Image 293" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId293"/>
+        <cNvPr id="294" name="Image 294" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId294"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7534,11 +7559,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="294" name="Image 294" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId294"/>
+        <cNvPr id="295" name="Image 295" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId295"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7559,11 +7584,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="295" name="Image 295" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId295"/>
+        <cNvPr id="296" name="Image 296" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId296"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7584,11 +7609,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="296" name="Image 296" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId296"/>
+        <cNvPr id="297" name="Image 297" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId297"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7609,11 +7634,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="297" name="Image 297" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId297"/>
+        <cNvPr id="298" name="Image 298" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId298"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7634,11 +7659,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="298" name="Image 298" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId298"/>
+        <cNvPr id="299" name="Image 299" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId299"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7659,11 +7684,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="299" name="Image 299" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId299"/>
+        <cNvPr id="300" name="Image 300" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId300"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7684,11 +7709,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="300" name="Image 300" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId300"/>
+        <cNvPr id="301" name="Image 301" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId301"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7709,11 +7734,11 @@
     <ext cx="1047750" cy="504825"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="301" name="Image 301" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId301"/>
+        <cNvPr id="302" name="Image 302" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId302"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7734,11 +7759,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="302" name="Image 302" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId302"/>
+        <cNvPr id="303" name="Image 303" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId303"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7759,11 +7784,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="303" name="Image 303" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId303"/>
+        <cNvPr id="304" name="Image 304" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId304"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7784,11 +7809,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="304" name="Image 304" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId304"/>
+        <cNvPr id="305" name="Image 305" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId305"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7809,11 +7834,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="305" name="Image 305" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId305"/>
+        <cNvPr id="306" name="Image 306" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId306"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7834,11 +7859,11 @@
     <ext cx="800100" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="306" name="Image 306" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId306"/>
+        <cNvPr id="307" name="Image 307" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId307"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7859,11 +7884,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="307" name="Image 307" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId307"/>
+        <cNvPr id="308" name="Image 308" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId308"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7884,11 +7909,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="308" name="Image 308" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId308"/>
+        <cNvPr id="309" name="Image 309" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId309"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7909,11 +7934,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="309" name="Image 309" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId309"/>
+        <cNvPr id="310" name="Image 310" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId310"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7934,11 +7959,11 @@
     <ext cx="847725" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="310" name="Image 310" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId310"/>
+        <cNvPr id="311" name="Image 311" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId311"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7959,11 +7984,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="311" name="Image 311" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId311"/>
+        <cNvPr id="312" name="Image 312" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId312"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7984,11 +8009,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="312" name="Image 312" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId312"/>
+        <cNvPr id="313" name="Image 313" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId313"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -8009,11 +8034,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="313" name="Image 313" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId313"/>
+        <cNvPr id="314" name="Image 314" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId314"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -8034,11 +8059,11 @@
     <ext cx="1047750" cy="885825"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="314" name="Image 314" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId314"/>
+        <cNvPr id="315" name="Image 315" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId315"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -8059,11 +8084,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="315" name="Image 315" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId315"/>
+        <cNvPr id="316" name="Image 316" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId316"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -8084,11 +8109,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="316" name="Image 316" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId316"/>
+        <cNvPr id="317" name="Image 317" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId317"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -8109,11 +8134,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="317" name="Image 317" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId317"/>
+        <cNvPr id="318" name="Image 318" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId318"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -8134,11 +8159,11 @@
     <ext cx="952500" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="318" name="Image 318" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId318"/>
+        <cNvPr id="319" name="Image 319" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId319"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -8159,11 +8184,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="319" name="Image 319" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId319"/>
+        <cNvPr id="320" name="Image 320" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId320"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -8184,11 +8209,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="320" name="Image 320" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId320"/>
+        <cNvPr id="321" name="Image 321" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId321"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -8209,11 +8234,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="321" name="Image 321" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId321"/>
+        <cNvPr id="322" name="Image 322" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId322"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -8234,11 +8259,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="322" name="Image 322" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId322"/>
+        <cNvPr id="323" name="Image 323" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId323"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -8259,11 +8284,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="323" name="Image 323" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId323"/>
+        <cNvPr id="324" name="Image 324" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId324"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -8284,11 +8309,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="324" name="Image 324" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId324"/>
+        <cNvPr id="325" name="Image 325" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId325"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -8309,11 +8334,11 @@
     <ext cx="1047750" cy="1009650"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="325" name="Image 325" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId325"/>
+        <cNvPr id="326" name="Image 326" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId326"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -8334,11 +8359,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="326" name="Image 326" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId326"/>
+        <cNvPr id="327" name="Image 327" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId327"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -8359,11 +8384,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="327" name="Image 327" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId327"/>
+        <cNvPr id="328" name="Image 328" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId328"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -8384,11 +8409,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="328" name="Image 328" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId328"/>
+        <cNvPr id="329" name="Image 329" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId329"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -8409,11 +8434,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="329" name="Image 329" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId329"/>
+        <cNvPr id="330" name="Image 330" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId330"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -8434,11 +8459,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="330" name="Image 330" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId330"/>
+        <cNvPr id="331" name="Image 331" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId331"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -8459,11 +8484,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="331" name="Image 331" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId331"/>
+        <cNvPr id="332" name="Image 332" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId332"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -8484,11 +8509,11 @@
     <ext cx="990600" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="332" name="Image 332" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId332"/>
+        <cNvPr id="333" name="Image 333" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId333"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -8509,11 +8534,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="333" name="Image 333" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId333"/>
+        <cNvPr id="334" name="Image 334" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId334"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -8534,11 +8559,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="334" name="Image 334" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId334"/>
+        <cNvPr id="335" name="Image 335" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId335"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -8559,11 +8584,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="335" name="Image 335" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId335"/>
+        <cNvPr id="336" name="Image 336" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId336"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -8584,11 +8609,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="336" name="Image 336" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId336"/>
+        <cNvPr id="337" name="Image 337" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId337"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -8609,11 +8634,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="337" name="Image 337" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId337"/>
+        <cNvPr id="338" name="Image 338" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId338"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -8634,11 +8659,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="338" name="Image 338" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId338"/>
+        <cNvPr id="339" name="Image 339" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId339"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -8659,11 +8684,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="339" name="Image 339" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId339"/>
+        <cNvPr id="340" name="Image 340" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId340"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -8684,11 +8709,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="340" name="Image 340" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId340"/>
+        <cNvPr id="341" name="Image 341" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId341"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -8709,11 +8734,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="341" name="Image 341" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId341"/>
+        <cNvPr id="342" name="Image 342" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId342"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -8734,11 +8759,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="342" name="Image 342" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId342"/>
+        <cNvPr id="343" name="Image 343" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId343"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -8759,11 +8784,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="343" name="Image 343" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId343"/>
+        <cNvPr id="344" name="Image 344" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId344"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -8784,11 +8809,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="344" name="Image 344" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId344"/>
+        <cNvPr id="345" name="Image 345" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId345"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -8809,11 +8834,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="345" name="Image 345" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId345"/>
+        <cNvPr id="346" name="Image 346" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId346"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -8834,11 +8859,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="346" name="Image 346" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId346"/>
+        <cNvPr id="347" name="Image 347" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId347"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -8859,11 +8884,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="347" name="Image 347" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId347"/>
+        <cNvPr id="348" name="Image 348" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId348"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -8884,11 +8909,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="348" name="Image 348" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId348"/>
+        <cNvPr id="349" name="Image 349" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId349"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -8909,11 +8934,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="349" name="Image 349" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId349"/>
+        <cNvPr id="350" name="Image 350" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId350"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -8934,11 +8959,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="350" name="Image 350" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId350"/>
+        <cNvPr id="351" name="Image 351" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId351"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -8959,11 +8984,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="351" name="Image 351" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId351"/>
+        <cNvPr id="352" name="Image 352" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId352"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -8984,11 +9009,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="352" name="Image 352" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId352"/>
+        <cNvPr id="353" name="Image 353" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId353"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -9009,11 +9034,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="353" name="Image 353" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId353"/>
+        <cNvPr id="354" name="Image 354" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId354"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -9034,11 +9059,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="354" name="Image 354" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId354"/>
+        <cNvPr id="355" name="Image 355" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId355"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -9059,11 +9084,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="355" name="Image 355" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId355"/>
+        <cNvPr id="356" name="Image 356" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId356"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -9084,11 +9109,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="356" name="Image 356" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId356"/>
+        <cNvPr id="357" name="Image 357" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId357"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -9109,11 +9134,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="357" name="Image 357" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId357"/>
+        <cNvPr id="358" name="Image 358" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId358"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -9134,11 +9159,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="358" name="Image 358" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId358"/>
+        <cNvPr id="359" name="Image 359" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId359"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -9159,11 +9184,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="359" name="Image 359" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId359"/>
+        <cNvPr id="360" name="Image 360" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId360"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -9184,11 +9209,11 @@
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="360" name="Image 360" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId360"/>
+        <cNvPr id="361" name="Image 361" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId361"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -9209,11 +9234,11 @@
     <ext cx="857250" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="361" name="Image 361" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId361"/>
+        <cNvPr id="362" name="Image 362" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId362"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -9234,11 +9259,11 @@
     <ext cx="1047750" cy="333375"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="362" name="Image 362" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId362"/>
+        <cNvPr id="363" name="Image 363" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId363"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -9259,11 +9284,11 @@
     <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="363" name="Image 363" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId363"/>
+        <cNvPr id="364" name="Image 364" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId364"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -9284,11 +9309,11 @@
     <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="364" name="Image 364" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId364"/>
+        <cNvPr id="365" name="Image 365" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId365"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -9309,11 +9334,11 @@
     <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="365" name="Image 365" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId365"/>
+        <cNvPr id="366" name="Image 366" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId366"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -9334,11 +9359,11 @@
     <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="366" name="Image 366" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId366"/>
+        <cNvPr id="367" name="Image 367" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId367"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -9359,11 +9384,11 @@
     <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="367" name="Image 367" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId367"/>
+        <cNvPr id="368" name="Image 368" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId368"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -9384,11 +9409,11 @@
     <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="368" name="Image 368" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId368"/>
+        <cNvPr id="369" name="Image 369" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId369"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -9409,11 +9434,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="369" name="Image 369" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId369"/>
+        <cNvPr id="370" name="Image 370" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId370"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -9434,11 +9459,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="370" name="Image 370" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId370"/>
+        <cNvPr id="371" name="Image 371" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId371"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -9459,11 +9484,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="371" name="Image 371" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId371"/>
+        <cNvPr id="372" name="Image 372" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId372"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -9484,11 +9509,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="372" name="Image 372" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId372"/>
+        <cNvPr id="373" name="Image 373" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId373"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -9509,11 +9534,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="373" name="Image 373" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId373"/>
+        <cNvPr id="374" name="Image 374" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId374"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -9534,11 +9559,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="374" name="Image 374" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId374"/>
+        <cNvPr id="375" name="Image 375" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId375"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -9559,11 +9584,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="375" name="Image 375" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId375"/>
+        <cNvPr id="376" name="Image 376" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId376"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -9584,11 +9609,11 @@
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="376" name="Image 376" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId376"/>
+        <cNvPr id="377" name="Image 377" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId377"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -9609,11 +9634,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="377" name="Image 377" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId377"/>
+        <cNvPr id="378" name="Image 378" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId378"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -9634,11 +9659,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="378" name="Image 378" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId378"/>
+        <cNvPr id="379" name="Image 379" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId379"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -9659,11 +9684,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="379" name="Image 379" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId379"/>
+        <cNvPr id="380" name="Image 380" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId380"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -9684,11 +9709,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="380" name="Image 380" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId380"/>
+        <cNvPr id="381" name="Image 381" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId381"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -9709,11 +9734,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="381" name="Image 381" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId381"/>
+        <cNvPr id="382" name="Image 382" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId382"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -9734,11 +9759,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="382" name="Image 382" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId382"/>
+        <cNvPr id="383" name="Image 383" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId383"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -9759,11 +9784,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="383" name="Image 383" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId383"/>
+        <cNvPr id="384" name="Image 384" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId384"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -9784,11 +9809,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="384" name="Image 384" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId384"/>
+        <cNvPr id="385" name="Image 385" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId385"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -9809,11 +9834,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="385" name="Image 385" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId385"/>
+        <cNvPr id="386" name="Image 386" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId386"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -9834,11 +9859,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="386" name="Image 386" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId386"/>
+        <cNvPr id="387" name="Image 387" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId387"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -9859,11 +9884,11 @@
     <ext cx="1047750" cy="876300"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="387" name="Image 387" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId387"/>
+        <cNvPr id="388" name="Image 388" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId388"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -9884,11 +9909,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="388" name="Image 388" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId388"/>
+        <cNvPr id="389" name="Image 389" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId389"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -9909,11 +9934,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="389" name="Image 389" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId389"/>
+        <cNvPr id="390" name="Image 390" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId390"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -9934,11 +9959,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="390" name="Image 390" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId390"/>
+        <cNvPr id="391" name="Image 391" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId391"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -9959,11 +9984,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="391" name="Image 391" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId391"/>
+        <cNvPr id="392" name="Image 392" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId392"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -9984,11 +10009,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="392" name="Image 392" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId392"/>
+        <cNvPr id="393" name="Image 393" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId393"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10009,11 +10034,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="393" name="Image 393" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId393"/>
+        <cNvPr id="394" name="Image 394" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId394"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10034,11 +10059,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="394" name="Image 394" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId394"/>
+        <cNvPr id="395" name="Image 395" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId395"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10059,11 +10084,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="395" name="Image 395" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId395"/>
+        <cNvPr id="396" name="Image 396" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId396"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10084,11 +10109,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="396" name="Image 396" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId396"/>
+        <cNvPr id="397" name="Image 397" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId397"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10109,11 +10134,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="397" name="Image 397" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId397"/>
+        <cNvPr id="398" name="Image 398" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId398"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10134,11 +10159,11 @@
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="398" name="Image 398" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId398"/>
+        <cNvPr id="399" name="Image 399" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId399"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10159,11 +10184,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="399" name="Image 399" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId399"/>
+        <cNvPr id="400" name="Image 400" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId400"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10184,11 +10209,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="400" name="Image 400" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId400"/>
+        <cNvPr id="401" name="Image 401" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId401"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10209,11 +10234,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="401" name="Image 401" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId401"/>
+        <cNvPr id="402" name="Image 402" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId402"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10234,11 +10259,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="402" name="Image 402" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId402"/>
+        <cNvPr id="403" name="Image 403" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId403"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10259,11 +10284,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="403" name="Image 403" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId403"/>
+        <cNvPr id="404" name="Image 404" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId404"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10284,11 +10309,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="404" name="Image 404" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId404"/>
+        <cNvPr id="405" name="Image 405" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId405"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10309,11 +10334,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="405" name="Image 405" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId405"/>
+        <cNvPr id="406" name="Image 406" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId406"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10334,11 +10359,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="406" name="Image 406" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId406"/>
+        <cNvPr id="407" name="Image 407" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId407"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10359,11 +10384,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="407" name="Image 407" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId407"/>
+        <cNvPr id="408" name="Image 408" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId408"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10384,11 +10409,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="408" name="Image 408" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId408"/>
+        <cNvPr id="409" name="Image 409" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId409"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10409,11 +10434,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="409" name="Image 409" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId409"/>
+        <cNvPr id="410" name="Image 410" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId410"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10434,11 +10459,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="410" name="Image 410" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId410"/>
+        <cNvPr id="411" name="Image 411" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId411"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10459,11 +10484,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="411" name="Image 411" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId411"/>
+        <cNvPr id="412" name="Image 412" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId412"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10484,11 +10509,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="412" name="Image 412" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId412"/>
+        <cNvPr id="413" name="Image 413" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId413"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10509,11 +10534,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="413" name="Image 413" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId413"/>
+        <cNvPr id="414" name="Image 414" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId414"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10534,11 +10559,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="414" name="Image 414" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId414"/>
+        <cNvPr id="415" name="Image 415" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId415"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10559,11 +10584,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="415" name="Image 415" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId415"/>
+        <cNvPr id="416" name="Image 416" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId416"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10584,11 +10609,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="416" name="Image 416" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId416"/>
+        <cNvPr id="417" name="Image 417" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId417"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10609,11 +10634,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="417" name="Image 417" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId417"/>
+        <cNvPr id="418" name="Image 418" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId418"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10634,11 +10659,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="418" name="Image 418" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId418"/>
+        <cNvPr id="419" name="Image 419" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId419"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10659,11 +10684,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="419" name="Image 419" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId419"/>
+        <cNvPr id="420" name="Image 420" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId420"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10684,11 +10709,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="420" name="Image 420" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId420"/>
+        <cNvPr id="421" name="Image 421" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId421"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10709,11 +10734,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="421" name="Image 421" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId421"/>
+        <cNvPr id="422" name="Image 422" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId422"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10734,11 +10759,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="422" name="Image 422" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId422"/>
+        <cNvPr id="423" name="Image 423" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId423"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10759,11 +10784,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="423" name="Image 423" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId423"/>
+        <cNvPr id="424" name="Image 424" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId424"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10784,11 +10809,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="424" name="Image 424" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId424"/>
+        <cNvPr id="425" name="Image 425" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId425"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10809,11 +10834,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="425" name="Image 425" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId425"/>
+        <cNvPr id="426" name="Image 426" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId426"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10834,11 +10859,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="426" name="Image 426" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId426"/>
+        <cNvPr id="427" name="Image 427" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId427"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10859,11 +10884,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="427" name="Image 427" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId427"/>
+        <cNvPr id="428" name="Image 428" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId428"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10884,11 +10909,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="428" name="Image 428" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId428"/>
+        <cNvPr id="429" name="Image 429" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId429"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10909,11 +10934,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="429" name="Image 429" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId429"/>
+        <cNvPr id="430" name="Image 430" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId430"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10934,11 +10959,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="430" name="Image 430" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId430"/>
+        <cNvPr id="431" name="Image 431" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId431"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10959,11 +10984,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="431" name="Image 431" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId431"/>
+        <cNvPr id="432" name="Image 432" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId432"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -10984,11 +11009,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="432" name="Image 432" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId432"/>
+        <cNvPr id="433" name="Image 433" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId433"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11009,11 +11034,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="433" name="Image 433" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId433"/>
+        <cNvPr id="434" name="Image 434" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId434"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11034,11 +11059,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="434" name="Image 434" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId434"/>
+        <cNvPr id="435" name="Image 435" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId435"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11059,11 +11084,11 @@
     <ext cx="1047750" cy="752475"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="435" name="Image 435" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId435"/>
+        <cNvPr id="436" name="Image 436" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId436"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11084,11 +11109,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="436" name="Image 436" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId436"/>
+        <cNvPr id="437" name="Image 437" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId437"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11109,11 +11134,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="437" name="Image 437" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId437"/>
+        <cNvPr id="438" name="Image 438" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId438"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11134,11 +11159,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="438" name="Image 438" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId438"/>
+        <cNvPr id="439" name="Image 439" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId439"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11159,11 +11184,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="439" name="Image 439" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId439"/>
+        <cNvPr id="440" name="Image 440" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId440"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11184,11 +11209,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="440" name="Image 440" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId440"/>
+        <cNvPr id="441" name="Image 441" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId441"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11209,11 +11234,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="441" name="Image 441" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId441"/>
+        <cNvPr id="442" name="Image 442" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId442"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11234,11 +11259,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="442" name="Image 442" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId442"/>
+        <cNvPr id="443" name="Image 443" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId443"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11259,11 +11284,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="443" name="Image 443" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId443"/>
+        <cNvPr id="444" name="Image 444" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId444"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11284,11 +11309,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="444" name="Image 444" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId444"/>
+        <cNvPr id="445" name="Image 445" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId445"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11309,11 +11334,11 @@
     <ext cx="1047750" cy="752475"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="445" name="Image 445" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId445"/>
+        <cNvPr id="446" name="Image 446" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId446"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11334,11 +11359,11 @@
     <ext cx="1047750" cy="752475"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="446" name="Image 446" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId446"/>
+        <cNvPr id="447" name="Image 447" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId447"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11359,11 +11384,11 @@
     <ext cx="1047750" cy="752475"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="447" name="Image 447" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId447"/>
+        <cNvPr id="448" name="Image 448" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId448"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11384,11 +11409,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="448" name="Image 448" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId448"/>
+        <cNvPr id="449" name="Image 449" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId449"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11409,11 +11434,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="449" name="Image 449" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId449"/>
+        <cNvPr id="450" name="Image 450" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId450"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11434,11 +11459,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="450" name="Image 450" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId450"/>
+        <cNvPr id="451" name="Image 451" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId451"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11459,11 +11484,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="451" name="Image 451" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId451"/>
+        <cNvPr id="452" name="Image 452" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId452"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11484,11 +11509,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="452" name="Image 452" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId452"/>
+        <cNvPr id="453" name="Image 453" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId453"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11509,11 +11534,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="453" name="Image 453" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId453"/>
+        <cNvPr id="454" name="Image 454" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId454"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11534,11 +11559,11 @@
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="454" name="Image 454" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId454"/>
+        <cNvPr id="455" name="Image 455" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId455"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11559,11 +11584,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="455" name="Image 455" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId455"/>
+        <cNvPr id="456" name="Image 456" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId456"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11584,11 +11609,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="456" name="Image 456" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId456"/>
+        <cNvPr id="457" name="Image 457" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId457"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11609,11 +11634,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="457" name="Image 457" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId457"/>
+        <cNvPr id="458" name="Image 458" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId458"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11634,11 +11659,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="458" name="Image 458" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId458"/>
+        <cNvPr id="459" name="Image 459" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId459"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11659,11 +11684,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="459" name="Image 459" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId459"/>
+        <cNvPr id="460" name="Image 460" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId460"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11684,11 +11709,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="460" name="Image 460" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId460"/>
+        <cNvPr id="461" name="Image 461" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId461"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11709,11 +11734,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="461" name="Image 461" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId461"/>
+        <cNvPr id="462" name="Image 462" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId462"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11734,11 +11759,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="462" name="Image 462" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId462"/>
+        <cNvPr id="463" name="Image 463" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId463"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11759,11 +11784,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="463" name="Image 463" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId463"/>
+        <cNvPr id="464" name="Image 464" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId464"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11784,11 +11809,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="464" name="Image 464" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId464"/>
+        <cNvPr id="465" name="Image 465" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId465"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11809,11 +11834,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="465" name="Image 465" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId465"/>
+        <cNvPr id="466" name="Image 466" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId466"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11834,11 +11859,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="466" name="Image 466" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId466"/>
+        <cNvPr id="467" name="Image 467" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId467"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11859,11 +11884,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="467" name="Image 467" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId467"/>
+        <cNvPr id="468" name="Image 468" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId468"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11884,11 +11909,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="468" name="Image 468" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId468"/>
+        <cNvPr id="469" name="Image 469" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId469"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11909,11 +11934,11 @@
     <ext cx="952500" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="469" name="Image 469" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId469"/>
+        <cNvPr id="470" name="Image 470" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId470"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11934,11 +11959,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="470" name="Image 470" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId470"/>
+        <cNvPr id="471" name="Image 471" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId471"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11959,11 +11984,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="471" name="Image 471" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId471"/>
+        <cNvPr id="472" name="Image 472" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId472"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -11984,11 +12009,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="472" name="Image 472" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId472"/>
+        <cNvPr id="473" name="Image 473" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId473"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12009,11 +12034,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="473" name="Image 473" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId473"/>
+        <cNvPr id="474" name="Image 474" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId474"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12034,11 +12059,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="474" name="Image 474" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId474"/>
+        <cNvPr id="475" name="Image 475" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId475"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12059,11 +12084,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="475" name="Image 475" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId475"/>
+        <cNvPr id="476" name="Image 476" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId476"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12084,11 +12109,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="476" name="Image 476" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId476"/>
+        <cNvPr id="477" name="Image 477" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId477"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12109,11 +12134,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="477" name="Image 477" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId477"/>
+        <cNvPr id="478" name="Image 478" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId478"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12134,11 +12159,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="478" name="Image 478" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId478"/>
+        <cNvPr id="479" name="Image 479" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId479"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12159,11 +12184,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="479" name="Image 479" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId479"/>
+        <cNvPr id="480" name="Image 480" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId480"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12184,11 +12209,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="480" name="Image 480" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId480"/>
+        <cNvPr id="481" name="Image 481" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId481"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12209,11 +12234,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="481" name="Image 481" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId481"/>
+        <cNvPr id="482" name="Image 482" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId482"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12234,11 +12259,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="482" name="Image 482" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId482"/>
+        <cNvPr id="483" name="Image 483" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId483"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12259,11 +12284,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="483" name="Image 483" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId483"/>
+        <cNvPr id="484" name="Image 484" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId484"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12284,11 +12309,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="484" name="Image 484" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId484"/>
+        <cNvPr id="485" name="Image 485" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId485"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12309,11 +12334,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="485" name="Image 485" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId485"/>
+        <cNvPr id="486" name="Image 486" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId486"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12334,11 +12359,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="486" name="Image 486" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId486"/>
+        <cNvPr id="487" name="Image 487" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId487"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12359,11 +12384,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="487" name="Image 487" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId487"/>
+        <cNvPr id="488" name="Image 488" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId488"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12384,11 +12409,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="488" name="Image 488" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId488"/>
+        <cNvPr id="489" name="Image 489" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId489"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12409,11 +12434,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="489" name="Image 489" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId489"/>
+        <cNvPr id="490" name="Image 490" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId490"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12434,11 +12459,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="490" name="Image 490" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId490"/>
+        <cNvPr id="491" name="Image 491" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId491"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12459,11 +12484,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="491" name="Image 491" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId491"/>
+        <cNvPr id="492" name="Image 492" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId492"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12484,11 +12509,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="492" name="Image 492" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId492"/>
+        <cNvPr id="493" name="Image 493" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId493"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12509,11 +12534,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="493" name="Image 493" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId493"/>
+        <cNvPr id="494" name="Image 494" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId494"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12534,11 +12559,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="494" name="Image 494" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId494"/>
+        <cNvPr id="495" name="Image 495" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId495"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12559,11 +12584,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="495" name="Image 495" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId495"/>
+        <cNvPr id="496" name="Image 496" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId496"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12584,11 +12609,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="496" name="Image 496" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId496"/>
+        <cNvPr id="497" name="Image 497" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId497"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12609,11 +12634,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="497" name="Image 497" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId497"/>
+        <cNvPr id="498" name="Image 498" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId498"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12634,11 +12659,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="498" name="Image 498" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId498"/>
+        <cNvPr id="499" name="Image 499" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId499"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12659,11 +12684,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="499" name="Image 499" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId499"/>
+        <cNvPr id="500" name="Image 500" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId500"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12684,11 +12709,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="500" name="Image 500" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId500"/>
+        <cNvPr id="501" name="Image 501" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId501"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12709,11 +12734,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="501" name="Image 501" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId501"/>
+        <cNvPr id="502" name="Image 502" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId502"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12734,11 +12759,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="502" name="Image 502" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId502"/>
+        <cNvPr id="503" name="Image 503" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId503"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12759,11 +12784,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="503" name="Image 503" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId503"/>
+        <cNvPr id="504" name="Image 504" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId504"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12784,11 +12809,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="504" name="Image 504" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId504"/>
+        <cNvPr id="505" name="Image 505" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId505"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12809,11 +12834,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="505" name="Image 505" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId505"/>
+        <cNvPr id="506" name="Image 506" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId506"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12834,11 +12859,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="506" name="Image 506" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId506"/>
+        <cNvPr id="507" name="Image 507" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId507"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12859,11 +12884,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="507" name="Image 507" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId507"/>
+        <cNvPr id="508" name="Image 508" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId508"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12884,11 +12909,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="508" name="Image 508" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId508"/>
+        <cNvPr id="509" name="Image 509" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId509"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12909,11 +12934,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="509" name="Image 509" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId509"/>
+        <cNvPr id="510" name="Image 510" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId510"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12934,11 +12959,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="510" name="Image 510" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId510"/>
+        <cNvPr id="511" name="Image 511" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId511"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12959,11 +12984,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="511" name="Image 511" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId511"/>
+        <cNvPr id="512" name="Image 512" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId512"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12984,11 +13009,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="512" name="Image 512" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId512"/>
+        <cNvPr id="513" name="Image 513" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId513"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -13009,11 +13034,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="513" name="Image 513" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId513"/>
+        <cNvPr id="514" name="Image 514" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId514"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>

--- a/카드_아키타입/12_완제베이스+활성.xlsx
+++ b/카드_아키타입/12_완제베이스+활성.xlsx
@@ -199,13 +199,8 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
+  <absoluteAnchor>
+    <pos x="6162675" y="0"/>
     <ext cx="1809750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -223,14 +218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -248,14 +238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -273,14 +258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -298,14 +278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="1847850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -323,14 +298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>0</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="1847850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -348,14 +318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>0</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="1847850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -373,14 +338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>11</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="10248900"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -398,14 +358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>11</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="10248900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -423,14 +378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>11</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="10248900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -448,14 +398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>11</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="10248900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -473,14 +418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>11</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="12096750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -498,14 +438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>21</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="15214600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -523,14 +458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>21</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="15214600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -548,14 +478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>21</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="15214600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -573,14 +498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>21</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="15214600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -598,14 +518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>21</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="17062450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -623,14 +538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>21</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="17062450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -648,14 +558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>21</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="17062450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -673,14 +578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>32</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="22212300"/>
     <ext cx="1809750" cy="1752600"/>
     <pic>
       <nvPicPr>
@@ -698,14 +598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>32</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="22212300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -723,14 +618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>32</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="22212300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -748,14 +638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>32</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="22212300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -773,14 +658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>32</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="24060150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -798,14 +678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>32</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="24060150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -823,14 +698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>32</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="24060150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -848,14 +718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>43</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="27787600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -873,14 +738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>43</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="27787600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -898,14 +758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>43</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="27787600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -923,14 +778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>43</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="27787600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -948,14 +798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>43</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="29635450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -973,14 +818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>43</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="29635450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -998,14 +838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>43</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="29635450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1023,14 +858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>52</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="35598100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1048,14 +878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>52</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="35598100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1073,14 +898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>52</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="35598100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1098,14 +918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>52</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="35598100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1123,14 +938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>62</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="41783000"/>
     <ext cx="1466850" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1148,14 +958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>62</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="41783000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1173,14 +978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>62</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="41783000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1198,14 +998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>62</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="41783000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1223,14 +1018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>72</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="48374300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1248,14 +1038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>72</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="48374300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1273,14 +1058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>72</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="48374300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1298,14 +1078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>72</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="48374300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1323,14 +1098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>72</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="50222150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1348,14 +1118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>72</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="50222150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1373,14 +1138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>72</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="50222150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1398,14 +1158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>81</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="55981600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1423,14 +1178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>81</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="55981600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1448,14 +1198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>81</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="55981600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1473,14 +1218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>81</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="55981600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1498,14 +1238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>81</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="57829450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1523,14 +1258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>81</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="57829450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1548,14 +1278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>81</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="57829450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1573,14 +1298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>81</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="57829450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1598,14 +1318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>91</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="61353700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1623,14 +1338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>91</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="61353700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1648,14 +1358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>91</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="61353700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1673,14 +1378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>91</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="61353700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1698,14 +1398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>91</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="63201550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1723,14 +1418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>91</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="63201550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1748,14 +1438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>91</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="63201550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1773,14 +1458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>102</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="68148200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1798,14 +1478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>102</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="68148200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1823,14 +1498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>102</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="68148200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1848,14 +1518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>102</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="68148200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1873,14 +1538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>102</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="69996050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1898,14 +1558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>102</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="69996050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1923,14 +1578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>102</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="69996050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1948,14 +1598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>102</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="69996050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1973,14 +1618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>102</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="71843900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1998,14 +1638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>102</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="71843900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2023,14 +1658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>102</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="71843900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2048,14 +1678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>102</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="71843900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2073,14 +1698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>102</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="73691750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2098,14 +1718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>112</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="77177900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2123,14 +1738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>112</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="77177900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2148,14 +1758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>112</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="77177900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2173,14 +1778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>112</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="77177900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2198,14 +1798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>112</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="79025750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2223,14 +1818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>112</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="79025750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2248,14 +1838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>112</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="79025750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2273,14 +1858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>112</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="79025750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2298,14 +1878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>112</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="80873600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2323,14 +1898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>112</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="80873600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2348,14 +1918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>112</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="80873600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2373,14 +1938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>112</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="80873600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2398,14 +1958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>112</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="82721450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2423,14 +1978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>122</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="86207600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2448,14 +1998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>122</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="86207600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2473,14 +2018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>122</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="86207600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2498,14 +2038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>122</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="86207600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2523,14 +2058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>122</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="88055450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2548,14 +2078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>122</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="88055450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2573,14 +2098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>122</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="88055450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2598,14 +2118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>122</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="88055450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2623,14 +2138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>132</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="91376500"/>
     <ext cx="1704975" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2648,14 +2158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>132</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="91376500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2673,14 +2178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>132</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="91376500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2698,14 +2198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>132</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="91376500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2723,14 +2218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>132</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="93224350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2748,14 +2238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>132</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="93224350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2773,14 +2258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>132</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="93224350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2798,14 +2278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>142</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="97358200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2823,14 +2298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>142</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="97358200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2848,14 +2318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>142</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="97358200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2873,14 +2338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>142</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="97358200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2898,14 +2358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>142</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="99206050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2923,14 +2378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>142</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="99206050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2948,14 +2398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>153</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="105575100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2973,14 +2418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>153</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="105575100"/>
     <ext cx="1809750" cy="1657350"/>
     <pic>
       <nvPicPr>
@@ -2998,14 +2438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>153</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="105575100"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -3023,14 +2458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>153</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="105575100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3048,14 +2478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>153</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="107422950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3073,14 +2498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>153</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="107422950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3098,14 +2518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>153</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="107422950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3123,14 +2538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>153</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="107422950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3148,14 +2558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>153</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="109270800"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3173,14 +2578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>163</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="111556800"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3198,14 +2598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>163</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="111556800"/>
     <ext cx="1504950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3223,14 +2618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>163</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="111556800"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3248,14 +2638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>163</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="111556800"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3273,14 +2658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>163</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="113404650"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3298,14 +2678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>163</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="113404650"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3323,14 +2698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>163</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="113404650"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3348,14 +2718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>163</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="113404650"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3373,14 +2738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>172</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="116725700"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3398,14 +2758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>172</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="116725700"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -3423,14 +2778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>172</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="116725700"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3448,14 +2798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>172</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="116725700"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3473,14 +2818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>172</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="118573550"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3498,14 +2838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>172</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="118573550"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3523,14 +2858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>172</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="118573550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3548,14 +2878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>181</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="120878600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3573,14 +2898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>181</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="120878600"/>
     <ext cx="1809750" cy="1647825"/>
     <pic>
       <nvPicPr>
@@ -3598,14 +2918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>181</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="120878600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3623,14 +2938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>181</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="120878600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3648,14 +2958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>181</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="122726450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3673,14 +2978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>181</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="122726450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3698,14 +2998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>181</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="122726450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3723,14 +3018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>181</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="122726450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3748,14 +3038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>181</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="124574300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3773,14 +3058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>181</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="124574300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3798,14 +3078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>181</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="124574300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3823,14 +3098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>181</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="124574300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3848,14 +3118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>181</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="126422150"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3873,14 +3138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>181</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="126422150"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3898,14 +3158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>192</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="130111500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3923,14 +3178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>192</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="130111500"/>
     <ext cx="1809750" cy="1609725"/>
     <pic>
       <nvPicPr>
@@ -3948,14 +3198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>192</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="130111500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3973,14 +3218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>192</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="130111500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3998,14 +3238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>192</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="131959350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4023,14 +3258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>192</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="131959350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4048,14 +3278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>192</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="131959350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4073,14 +3298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>192</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="131959350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4098,14 +3318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>192</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="133807200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4123,14 +3338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>192</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="133807200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4148,14 +3358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>203</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="138125200"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4173,14 +3378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>203</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="138125200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4198,14 +3398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>203</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="138125200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4223,14 +3418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>203</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="138125200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4248,14 +3438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>203</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="139973050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4273,14 +3458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>203</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="139973050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4298,14 +3478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>203</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="139973050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4323,14 +3498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>203</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="139973050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4348,14 +3518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>203</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="141820900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4373,14 +3538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>203</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="141820900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4398,14 +3558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>203</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="141820900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4423,14 +3578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>214</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="148577300"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4448,14 +3598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>214</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="148577300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4473,14 +3618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>214</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="148577300"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -4498,14 +3638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>214</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="148577300"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4523,14 +3658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>214</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="150425150"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4548,14 +3678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>214</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="150425150"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4573,14 +3698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>214</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="150425150"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4598,14 +3718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>214</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="150425150"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4623,14 +3738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>214</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="152273000"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4648,14 +3758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>225</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="154197050"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4673,14 +3778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>225</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="154197050"/>
     <ext cx="1809750" cy="971550"/>
     <pic>
       <nvPicPr>
@@ -4698,14 +3798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>225</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="154197050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4723,14 +3818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>225</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="154197050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4748,14 +3838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>225</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="156044900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4773,14 +3858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>225</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="156044900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4798,14 +3878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>225</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="156044900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4823,14 +3898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>225</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="156044900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4848,14 +3918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>225</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="157892749"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4873,14 +3938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>225</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="157892749"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4898,14 +3958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>236</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="166681150"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4923,14 +3978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>236</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="166681150"/>
     <ext cx="1809750" cy="1609725"/>
     <pic>
       <nvPicPr>
@@ -4948,14 +3998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>236</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="166681150"/>
     <ext cx="1809750" cy="1704975"/>
     <pic>
       <nvPicPr>
@@ -4973,14 +4018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>236</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="166681150"/>
     <ext cx="1809750" cy="1162050"/>
     <pic>
       <nvPicPr>
@@ -4998,14 +4038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>245</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="170224450"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5023,14 +4058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>245</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="170224450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5048,14 +4078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>245</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="170224450"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5073,14 +4098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>255</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="184334150"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5098,14 +4118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>255</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="184334150"/>
     <ext cx="1809750" cy="1447800"/>
     <pic>
       <nvPicPr>
@@ -5123,14 +4138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>255</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="184334150"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5148,14 +4158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>255</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="184334150"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5173,14 +4178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>255</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="186182000"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5198,14 +4198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>265</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="189096650"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5223,14 +4218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>265</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="189096650"/>
     <ext cx="1428750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5248,14 +4238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>265</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="189096650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5273,14 +4258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>265</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="189096650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5298,14 +4278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>265</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="190944500"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5323,14 +4298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>277</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="196500750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5348,14 +4318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>277</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="196500750"/>
     <ext cx="1809750" cy="523875"/>
     <pic>
       <nvPicPr>
@@ -5373,14 +4338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>277</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="196500750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5398,14 +4358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>277</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="196500750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5423,14 +4378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>277</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="198348600"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5448,14 +4398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>277</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="198348600"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5473,14 +4418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>277</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="198348600"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5498,14 +4438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>277</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="198348600"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5523,14 +4458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>287</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="203295250"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5548,14 +4478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>287</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="203295250"/>
     <ext cx="1809750" cy="1609725"/>
     <pic>
       <nvPicPr>
@@ -5573,14 +4498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>287</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="203295250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5598,14 +4518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>287</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="203295250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5623,14 +4538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>287</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="205143100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5648,14 +4558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>287</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="205143100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5673,14 +4578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>287</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="205143100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5698,14 +4598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>287</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="205143100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5723,14 +4618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>296</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="208057750"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5748,14 +4638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>296</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="208057750"/>
     <ext cx="1809750" cy="1304925"/>
     <pic>
       <nvPicPr>
@@ -5773,14 +4658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>296</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="208057750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5798,14 +4678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>296</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="208057750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5823,14 +4698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>296</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="209905600"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5848,14 +4718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>308</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="216071450"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5873,14 +4738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>308</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="216071450"/>
     <ext cx="1809750" cy="1476375"/>
     <pic>
       <nvPicPr>
@@ -5898,14 +4758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>308</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="216071450"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -5923,14 +4778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>308</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="216071450"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5948,14 +4798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>308</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="217919300"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5973,14 +4818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>308</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="217919300"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5998,14 +4838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>308</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="217919300"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6023,14 +4858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>308</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="217919300"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6048,14 +4878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>308</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="219767150"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6073,14 +4898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>308</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="219767150"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6098,14 +4918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>308</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="219767150"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6123,14 +4938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>308</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="219767150"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6148,14 +4958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>321</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="226726750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6173,14 +4978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>321</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="226726750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6198,14 +4998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>321</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="226726750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6223,14 +5018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>321</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="226726750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6248,14 +5038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>321</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="228574600"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6273,14 +5058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>321</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="228574600"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6298,14 +5078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>321</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="228574600"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6323,14 +5098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>321</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="228574600"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6348,14 +5118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>321</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="230422450"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6373,14 +5138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>321</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="230422450"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6398,14 +5158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>321</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="230422450"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6423,14 +5178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>333</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="236366050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6448,14 +5198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>333</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="236366050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6473,14 +5218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>333</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="236366050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6498,14 +5238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>333</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="236366050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6523,14 +5258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>344</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="243160550"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -6548,14 +5278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>344</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="243160550"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6573,14 +5298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>344</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="243160550"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6598,14 +5318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>344</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="243160550"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6623,14 +5338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>354</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="249548650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6648,14 +5358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>354</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="249548650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6673,14 +5378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>354</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="249548650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6698,14 +5398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>354</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="249548650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6723,14 +5418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>366</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="259187950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6748,14 +5438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>366</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="259187950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6773,14 +5458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>366</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="259187950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6798,14 +5478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>366</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="259187950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6823,14 +5498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>366</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="261035800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6848,14 +5518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>366</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="261035800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6873,14 +5538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>366</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="261035800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6898,14 +5558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>376</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="264966450"/>
     <ext cx="1809750" cy="1695450"/>
     <pic>
       <nvPicPr>
@@ -6923,14 +5578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>376</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="264966450"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6948,14 +5598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>376</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="264966450"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6973,14 +5618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>376</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="264966450"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6998,14 +5638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>387</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="273183350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7023,14 +5658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>387</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="273183350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7048,14 +5678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>387</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="273183350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7073,14 +5698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>387</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="273183350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7098,14 +5718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>387</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="275031200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7123,14 +5738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>387</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="275031200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7148,14 +5758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>387</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="275031200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7173,14 +5778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>398</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="281197050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7198,14 +5798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>398</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="281197050"/>
     <ext cx="1809750" cy="1085850"/>
     <pic>
       <nvPicPr>
@@ -7223,14 +5818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>398</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="281197050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7248,14 +5838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>398</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="281197050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7273,14 +5858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>398</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="283044900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7298,14 +5878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>407</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="286569150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7323,14 +5898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>407</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="286569150"/>
     <ext cx="1809750" cy="1085850"/>
     <pic>
       <nvPicPr>
@@ -7348,14 +5918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>407</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="286569150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7373,14 +5938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>407</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="286569150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7398,14 +5958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>407</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="288417000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7423,14 +5978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>416</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="293160450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7448,14 +5998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>416</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="293160450"/>
     <ext cx="1809750" cy="1095375"/>
     <pic>
       <nvPicPr>
@@ -7473,14 +6018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>416</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="293160450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7498,14 +6038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>416</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="293160450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7523,14 +6058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>416</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="295008300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7548,14 +6078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>425</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="300158150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7573,14 +6098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>425</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="300158150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7598,14 +6118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>425</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="300158150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7623,14 +6138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>425</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="300158150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7648,14 +6158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>425</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="302006000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7673,14 +6178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>425</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="302006000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7698,14 +6198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>425</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="302006000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7723,14 +6218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>425</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="302006000"/>
     <ext cx="1809750" cy="876300"/>
     <pic>
       <nvPicPr>
@@ -7748,14 +6238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>436</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="309594250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7773,14 +6258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>436</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="309594250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7798,14 +6278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>436</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="309594250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7823,14 +6298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>436</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="309594250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7848,14 +6318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>445</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="315575950"/>
     <ext cx="1381125" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7873,14 +6338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>445</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="315575950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7898,14 +6358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>445</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="315575950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7923,14 +6378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>445</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="315575950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7948,14 +6398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>456</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="322370450"/>
     <ext cx="1466850" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7973,14 +6418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>456</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="322370450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7998,14 +6438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>456</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="322370450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8023,14 +6458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>456</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="322370450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8048,14 +6478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>467</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="329977750"/>
     <ext cx="1809750" cy="1533525"/>
     <pic>
       <nvPicPr>
@@ -8073,14 +6498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>467</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="329977750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8098,14 +6518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>467</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="329977750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8123,14 +6538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>467</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="329977750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8148,14 +6558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>478</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="335756250"/>
     <ext cx="1647825" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8173,14 +6578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>478</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="335756250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8198,14 +6598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>478</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="335756250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8223,14 +6618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>478</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="335756250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8248,14 +6638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>478</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="337604100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8273,14 +6658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>478</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="337604100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8298,14 +6678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>478</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="337604100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8323,14 +6698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>489</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="342550750"/>
     <ext cx="1809750" cy="1752600"/>
     <pic>
       <nvPicPr>
@@ -8348,14 +6718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>489</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="342550750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8373,14 +6738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>489</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="342550750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8398,14 +6758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>489</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="342550750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8423,14 +6778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>489</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="344398600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8448,14 +6798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>489</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="344398600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8473,14 +6818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>489</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="344398600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8498,14 +6838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>500</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="348126050"/>
     <ext cx="1704975" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8523,14 +6858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>500</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="348126050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8548,14 +6878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>500</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="348126050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8573,14 +6898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>500</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="348126050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8598,14 +6918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>500</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="349973900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8623,14 +6938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>500</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="349973900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8648,14 +6958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>500</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="349973900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8673,14 +6978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>510</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="354107750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8698,14 +6998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>510</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="354107750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8723,14 +7018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>510</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="354107750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8748,14 +7038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>510</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="354107750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8773,14 +7058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>510</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="355955600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8798,14 +7078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>510</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="355955600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8823,14 +7098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>510</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="355955600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8848,14 +7118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>521</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="360902250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8873,14 +7138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>521</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="360902250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8898,14 +7158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>521</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="360902250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8923,14 +7178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>521</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="360902250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8948,14 +7198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>521</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="362750100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8973,14 +7218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>521</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="362750100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8998,14 +7238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>521</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="362750100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9023,14 +7258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>532</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="367087150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9048,14 +7278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>532</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="367087150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9073,14 +7298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>532</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="367087150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9098,14 +7318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>532</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="367087150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9123,14 +7338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>532</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="368935000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9148,14 +7358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>532</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="368935000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9173,14 +7378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>532</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="368935000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9198,14 +7398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>543</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="374084850"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -9223,14 +7418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>543</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="374084850"/>
     <ext cx="1476375" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9248,14 +7438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>543</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="374084850"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -9273,14 +7458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>543</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="374084850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9298,14 +7478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>543</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="375932700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9323,14 +7498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>543</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="375932700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9348,14 +7518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>543</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="375932700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9373,14 +7538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>543</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="375932700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9398,14 +7558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>543</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="377780550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9423,14 +7578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>555</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="384536950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9448,14 +7598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>555</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="384536950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9473,14 +7618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>555</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="384536950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9498,14 +7638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>555</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="384536950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9523,14 +7658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>555</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="386384800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9548,14 +7678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>555</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="386384800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9573,14 +7698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>555</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="386384800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9598,14 +7718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>563</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="389909050"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -9623,14 +7738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>563</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="389909050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9648,14 +7758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>563</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="389909050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -9673,14 +7778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>563</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="389909050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -9698,14 +7798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>563</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="391756900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -9723,14 +7818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>563</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="391756900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -9748,14 +7838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>563</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="391756900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -9773,14 +7858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>563</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="391756900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -9798,14 +7878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>563</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="393604750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -9823,14 +7898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>563</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="393604750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -9848,14 +7918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>563</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="393604750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -9873,14 +7938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>577</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="401377150"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -9898,14 +7958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>577</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="401377150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9923,14 +7978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>577</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="401377150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9948,14 +7998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>577</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="401377150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9973,14 +8018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>589</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="409594050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9998,14 +8038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>589</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="409594050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10023,14 +8058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>589</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="409594050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10048,14 +8078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>589</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="409594050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10073,14 +8098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>589</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="411441900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10098,14 +8118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>589</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="411441900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10123,14 +8138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>589</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="411441900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10148,14 +8158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>600</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="415778950"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -10173,14 +8178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>600</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="415778950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10198,14 +8198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>600</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="415778950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10223,14 +8218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>600</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="415778950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10248,14 +8238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>600</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="417626800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10273,14 +8258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>600</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="417626800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10298,14 +8278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>600</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="417626800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10323,14 +8298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>600</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="417626800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10348,14 +8318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>610</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="421963850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10373,14 +8338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>610</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="421963850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10398,14 +8358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>610</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="421963850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10423,14 +8378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>610</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="421963850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10448,14 +8398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>610</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="423811700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10473,14 +8418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>610</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="423811700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10498,14 +8438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>610</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="423811700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10523,14 +8458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>610</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="423811700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10548,14 +8478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>610</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="425659550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10573,14 +8498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>610</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="425659550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10598,14 +8518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>622</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="432415950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10623,14 +8538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>622</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="432415950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10648,14 +8558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>622</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="432415950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10673,14 +8578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>622</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="432415950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10698,14 +8598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>622</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="434263800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10723,14 +8618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>622</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="434263800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10748,14 +8638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>633</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="441039250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10773,14 +8658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>633</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="441039250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10798,14 +8678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>633</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="441039250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10823,14 +8698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>633</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="441039250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10848,14 +8718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>633</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="442887100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10873,14 +8738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>633</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="442887100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10898,14 +8758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>633</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="442887100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10923,14 +8778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>633</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="442887100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10948,14 +8798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>633</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="444734950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10973,14 +8818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>633</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="444734950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10998,14 +8838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>633</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="444734950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -11023,14 +8858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>633</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="444734950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -11048,14 +8878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>633</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="446582800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -11073,14 +8898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>644</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="448506850"/>
     <ext cx="1809750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -11098,14 +8918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>644</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="448506850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -11123,14 +8938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>644</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="448506850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -11148,14 +8958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>644</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="448506850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -11173,14 +8978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>644</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="450354700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -11198,14 +8998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>644</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="450354700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -11223,14 +9018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>644</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="450354700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -11248,14 +9038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>644</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="450354700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -11273,14 +9058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>644</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="452202550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -11298,14 +9078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>644</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="452202550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -11323,14 +9098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>644</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="452202550"/>
     <ext cx="1809750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -11348,14 +9118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>644</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="452202550"/>
     <ext cx="1809750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -11373,14 +9138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>654</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="457130150"/>
     <ext cx="1809750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -11398,14 +9158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>654</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="457130150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -11423,14 +9178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>654</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="457130150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -11448,14 +9198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>654</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="457130150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -11473,14 +9218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>654</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="458978000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -11498,14 +9238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>654</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="458978000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -11523,14 +9258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>654</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="458978000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -11548,14 +9278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>665</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="466769450"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -11573,14 +9298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>665</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="466769450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -11598,14 +9318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>665</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="466769450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -11623,14 +9338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>665</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="466769450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -11648,14 +9358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>665</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="468617300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -11673,14 +9378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>665</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="468617300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -11698,14 +9398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>665</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="468617300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -11723,14 +9418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>665</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="468617300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -11748,14 +9438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>675</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="472547950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -11773,14 +9458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>675</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="472547950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -11798,14 +9478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>675</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="472547950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -11823,14 +9498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>675</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="472547950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -11848,14 +9518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>675</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="474395800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -11873,14 +9538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>675</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="474395800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -11898,14 +9558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>675</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="474395800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -11923,14 +9578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>684</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="479952050"/>
     <ext cx="1647825" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -11948,14 +9598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>684</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="479952050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -11973,14 +9618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>684</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="479952050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -11998,14 +9638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>684</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="479952050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -12023,14 +9658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>684</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="481799900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -12048,14 +9678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>684</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="481799900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -12073,14 +9698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>684</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="481799900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -12098,14 +9718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>695</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="486746550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -12123,14 +9738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>695</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="486746550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -12148,14 +9758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>695</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="486746550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -12173,14 +9778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>695</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="486746550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -12198,14 +9798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>695</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="488594400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -12223,14 +9818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>695</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="488594400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -12248,14 +9838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>695</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="488594400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -12273,14 +9858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>695</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="488594400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -12298,14 +9878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>695</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="490442250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -12323,14 +9898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>695</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="490442250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -12348,14 +9918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>695</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="490442250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -12373,14 +9938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>713</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="498011450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -12398,14 +9958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>713</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="498011450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -12423,14 +9978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>713</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="498011450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -12448,14 +9998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>713</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="498011450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -12473,14 +10018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>713</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="499859300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -12498,14 +10038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>713</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="499859300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -12523,14 +10058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>713</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="499859300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -12548,14 +10078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>713</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="499859300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -12573,14 +10098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>713</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="501707150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -12598,14 +10118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>713</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="501707150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -12623,14 +10138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>713</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="501707150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -12648,14 +10158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>713</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="501707150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -12673,14 +10178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>713</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="503555000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -12698,14 +10198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>723</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="507853950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -12723,14 +10218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>723</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="507853950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -12748,14 +10238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>723</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="507853950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -12773,14 +10258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>723</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="507853950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -12798,14 +10278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>733</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="515867650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -12823,14 +10298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>733</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="515867650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -12848,14 +10318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>733</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="515867650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -12873,14 +10338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>733</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="515867650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -12898,14 +10358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>733</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="517715500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -12923,14 +10378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>733</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="517715500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -12948,14 +10398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>733</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="517715500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -12973,14 +10418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>733</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="517715500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -12998,14 +10438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>733</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="519563350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -13023,14 +10458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>733</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="519563350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -13048,7 +10478,7 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
+  </absoluteAnchor>
 </wsDr>
 </file>
 

--- a/카드_아키타입/12_완제베이스+활성.xlsx
+++ b/카드_아키타입/12_완제베이스+활성.xlsx
@@ -200,7 +200,7 @@
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <absoluteAnchor>
-    <pos x="6162675" y="0"/>
+    <pos x="7391400" y="0"/>
     <ext cx="1809750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -220,7 +220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="0"/>
+    <pos x="9239250" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -240,7 +240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="0"/>
+    <pos x="11087100" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -260,7 +260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="0"/>
+    <pos x="12934950" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -280,7 +280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="1847850"/>
+    <pos x="7391400" y="1847850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -300,7 +300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="1847850"/>
+    <pos x="9239250" y="1847850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -320,7 +320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="1847850"/>
+    <pos x="11087100" y="1847850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -340,7 +340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="10248900"/>
+    <pos x="7391400" y="10248900"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -360,7 +360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="10248900"/>
+    <pos x="9239250" y="10248900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -380,7 +380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="10248900"/>
+    <pos x="11087100" y="10248900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -400,7 +400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="10248900"/>
+    <pos x="12934950" y="10248900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -420,7 +420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="12096750"/>
+    <pos x="7391400" y="12096750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -440,7 +440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="15214600"/>
+    <pos x="7391400" y="15214600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -460,7 +460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="15214600"/>
+    <pos x="9239250" y="15214600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -480,7 +480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="15214600"/>
+    <pos x="11087100" y="15214600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -500,7 +500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="15214600"/>
+    <pos x="12934950" y="15214600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -520,7 +520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="17062450"/>
+    <pos x="7391400" y="17062450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -540,7 +540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="17062450"/>
+    <pos x="9239250" y="17062450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -560,7 +560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="17062450"/>
+    <pos x="11087100" y="17062450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -580,7 +580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="22212300"/>
+    <pos x="7391400" y="22212300"/>
     <ext cx="1809750" cy="1752600"/>
     <pic>
       <nvPicPr>
@@ -600,7 +600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="22212300"/>
+    <pos x="9239250" y="22212300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -620,7 +620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="22212300"/>
+    <pos x="11087100" y="22212300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -640,7 +640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="22212300"/>
+    <pos x="12934950" y="22212300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -660,7 +660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="24060150"/>
+    <pos x="7391400" y="24060150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -680,7 +680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="24060150"/>
+    <pos x="9239250" y="24060150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -700,7 +700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="24060150"/>
+    <pos x="11087100" y="24060150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -720,7 +720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="27787600"/>
+    <pos x="7391400" y="27787600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -740,7 +740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="27787600"/>
+    <pos x="9239250" y="27787600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -760,7 +760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="27787600"/>
+    <pos x="11087100" y="27787600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -780,7 +780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="27787600"/>
+    <pos x="12934950" y="27787600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -800,7 +800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="29635450"/>
+    <pos x="7391400" y="29635450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -820,7 +820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="29635450"/>
+    <pos x="9239250" y="29635450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -840,7 +840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="29635450"/>
+    <pos x="11087100" y="29635450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -860,7 +860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="35598100"/>
+    <pos x="7391400" y="35598100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -880,7 +880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="35598100"/>
+    <pos x="9239250" y="35598100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -900,7 +900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="35598100"/>
+    <pos x="11087100" y="35598100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -920,7 +920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="35598100"/>
+    <pos x="12934950" y="35598100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -940,7 +940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="41783000"/>
+    <pos x="7391400" y="41783000"/>
     <ext cx="1466850" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -960,7 +960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="41783000"/>
+    <pos x="9239250" y="41783000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -980,7 +980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="41783000"/>
+    <pos x="11087100" y="41783000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1000,7 +1000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="41783000"/>
+    <pos x="12934950" y="41783000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1020,7 +1020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="48374300"/>
+    <pos x="7391400" y="48374300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1040,7 +1040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="48374300"/>
+    <pos x="9239250" y="48374300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1060,7 +1060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="48374300"/>
+    <pos x="11087100" y="48374300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1080,7 +1080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="48374300"/>
+    <pos x="12934950" y="48374300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1100,7 +1100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="50222150"/>
+    <pos x="7391400" y="50222150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1120,7 +1120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="50222150"/>
+    <pos x="9239250" y="50222150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1140,7 +1140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="50222150"/>
+    <pos x="11087100" y="50222150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1160,7 +1160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="55981600"/>
+    <pos x="7391400" y="55981600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1180,7 +1180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="55981600"/>
+    <pos x="9239250" y="55981600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1200,7 +1200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="55981600"/>
+    <pos x="11087100" y="55981600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1220,7 +1220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="55981600"/>
+    <pos x="12934950" y="55981600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1240,7 +1240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="57829450"/>
+    <pos x="7391400" y="57829450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1260,7 +1260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="57829450"/>
+    <pos x="9239250" y="57829450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1280,7 +1280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="57829450"/>
+    <pos x="11087100" y="57829450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1300,7 +1300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="57829450"/>
+    <pos x="12934950" y="57829450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1320,7 +1320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="61353700"/>
+    <pos x="7391400" y="61353700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1340,7 +1340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="61353700"/>
+    <pos x="9239250" y="61353700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1360,7 +1360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="61353700"/>
+    <pos x="11087100" y="61353700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1380,7 +1380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="61353700"/>
+    <pos x="12934950" y="61353700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1400,7 +1400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="63201550"/>
+    <pos x="7391400" y="63201550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1420,7 +1420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="63201550"/>
+    <pos x="9239250" y="63201550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1440,7 +1440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="63201550"/>
+    <pos x="11087100" y="63201550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1460,7 +1460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="68148200"/>
+    <pos x="7391400" y="68148200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1480,7 +1480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="68148200"/>
+    <pos x="9239250" y="68148200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1500,7 +1500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="68148200"/>
+    <pos x="11087100" y="68148200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1520,7 +1520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="68148200"/>
+    <pos x="12934950" y="68148200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1540,7 +1540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="69996050"/>
+    <pos x="7391400" y="69996050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1560,7 +1560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="69996050"/>
+    <pos x="9239250" y="69996050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1580,7 +1580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="69996050"/>
+    <pos x="11087100" y="69996050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1600,7 +1600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="69996050"/>
+    <pos x="12934950" y="69996050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1620,7 +1620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="71843900"/>
+    <pos x="7391400" y="71843900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1640,7 +1640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="71843900"/>
+    <pos x="9239250" y="71843900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1660,7 +1660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="71843900"/>
+    <pos x="11087100" y="71843900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1680,7 +1680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="71843900"/>
+    <pos x="12934950" y="71843900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1700,7 +1700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="73691750"/>
+    <pos x="7391400" y="73691750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1720,7 +1720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="77177900"/>
+    <pos x="7391400" y="77177900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1740,7 +1740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="77177900"/>
+    <pos x="9239250" y="77177900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1760,7 +1760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="77177900"/>
+    <pos x="11087100" y="77177900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1780,7 +1780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="77177900"/>
+    <pos x="12934950" y="77177900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1800,7 +1800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="79025750"/>
+    <pos x="7391400" y="79025750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1820,7 +1820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="79025750"/>
+    <pos x="9239250" y="79025750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1840,7 +1840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="79025750"/>
+    <pos x="11087100" y="79025750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1860,7 +1860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="79025750"/>
+    <pos x="12934950" y="79025750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1880,7 +1880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="80873600"/>
+    <pos x="7391400" y="80873600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1900,7 +1900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="80873600"/>
+    <pos x="9239250" y="80873600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1920,7 +1920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="80873600"/>
+    <pos x="11087100" y="80873600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1940,7 +1940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="80873600"/>
+    <pos x="12934950" y="80873600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1960,7 +1960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="82721450"/>
+    <pos x="7391400" y="82721450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1980,7 +1980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="86207600"/>
+    <pos x="7391400" y="86207600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2000,7 +2000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="86207600"/>
+    <pos x="9239250" y="86207600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2020,7 +2020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="86207600"/>
+    <pos x="11087100" y="86207600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2040,7 +2040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="86207600"/>
+    <pos x="12934950" y="86207600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2060,7 +2060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="88055450"/>
+    <pos x="7391400" y="88055450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2080,7 +2080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="88055450"/>
+    <pos x="9239250" y="88055450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2100,7 +2100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="88055450"/>
+    <pos x="11087100" y="88055450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2120,7 +2120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="88055450"/>
+    <pos x="12934950" y="88055450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2140,7 +2140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="91376500"/>
+    <pos x="7391400" y="91376500"/>
     <ext cx="1704975" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2160,7 +2160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="91376500"/>
+    <pos x="9239250" y="91376500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2180,7 +2180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="91376500"/>
+    <pos x="11087100" y="91376500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2200,7 +2200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="91376500"/>
+    <pos x="12934950" y="91376500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2220,7 +2220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="93224350"/>
+    <pos x="7391400" y="93224350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2240,7 +2240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="93224350"/>
+    <pos x="9239250" y="93224350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2260,7 +2260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="93224350"/>
+    <pos x="11087100" y="93224350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2280,7 +2280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="97358200"/>
+    <pos x="7391400" y="97358200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2300,7 +2300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="97358200"/>
+    <pos x="9239250" y="97358200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2320,7 +2320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="97358200"/>
+    <pos x="11087100" y="97358200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2340,7 +2340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="97358200"/>
+    <pos x="12934950" y="97358200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2360,7 +2360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="99206050"/>
+    <pos x="7391400" y="99206050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2380,7 +2380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="99206050"/>
+    <pos x="9239250" y="99206050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2400,7 +2400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="105575100"/>
+    <pos x="7391400" y="105575100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2420,7 +2420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="105575100"/>
+    <pos x="9239250" y="105575100"/>
     <ext cx="1809750" cy="1657350"/>
     <pic>
       <nvPicPr>
@@ -2440,7 +2440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="105575100"/>
+    <pos x="11087100" y="105575100"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -2460,7 +2460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="105575100"/>
+    <pos x="12934950" y="105575100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2480,7 +2480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="107422950"/>
+    <pos x="7391400" y="107422950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2500,7 +2500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="107422950"/>
+    <pos x="9239250" y="107422950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2520,7 +2520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="107422950"/>
+    <pos x="11087100" y="107422950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2540,7 +2540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="107422950"/>
+    <pos x="12934950" y="107422950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2560,7 +2560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="109270800"/>
+    <pos x="7391400" y="109270800"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2580,7 +2580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="111556800"/>
+    <pos x="7391400" y="111556800"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2600,7 +2600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="111556800"/>
+    <pos x="9239250" y="111556800"/>
     <ext cx="1504950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2620,7 +2620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="111556800"/>
+    <pos x="11087100" y="111556800"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2640,7 +2640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="111556800"/>
+    <pos x="12934950" y="111556800"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2660,7 +2660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="113404650"/>
+    <pos x="7391400" y="113404650"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2680,7 +2680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="113404650"/>
+    <pos x="9239250" y="113404650"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2700,7 +2700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="113404650"/>
+    <pos x="11087100" y="113404650"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2720,7 +2720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="113404650"/>
+    <pos x="12934950" y="113404650"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2740,7 +2740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="116725700"/>
+    <pos x="7391400" y="116725700"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2760,7 +2760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="116725700"/>
+    <pos x="9239250" y="116725700"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -2780,7 +2780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="116725700"/>
+    <pos x="11087100" y="116725700"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2800,7 +2800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="116725700"/>
+    <pos x="12934950" y="116725700"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2820,7 +2820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="118573550"/>
+    <pos x="7391400" y="118573550"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2840,7 +2840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="118573550"/>
+    <pos x="9239250" y="118573550"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2860,7 +2860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="118573550"/>
+    <pos x="11087100" y="118573550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2880,7 +2880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="120878600"/>
+    <pos x="7391400" y="120878600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2900,7 +2900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="120878600"/>
+    <pos x="9239250" y="120878600"/>
     <ext cx="1809750" cy="1647825"/>
     <pic>
       <nvPicPr>
@@ -2920,7 +2920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="120878600"/>
+    <pos x="11087100" y="120878600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2940,7 +2940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="120878600"/>
+    <pos x="12934950" y="120878600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2960,7 +2960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="122726450"/>
+    <pos x="7391400" y="122726450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2980,7 +2980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="122726450"/>
+    <pos x="9239250" y="122726450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3000,7 +3000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="122726450"/>
+    <pos x="11087100" y="122726450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3020,7 +3020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="122726450"/>
+    <pos x="12934950" y="122726450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3040,7 +3040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="124574300"/>
+    <pos x="7391400" y="124574300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3060,7 +3060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="124574300"/>
+    <pos x="9239250" y="124574300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3080,7 +3080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="124574300"/>
+    <pos x="11087100" y="124574300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3100,7 +3100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="124574300"/>
+    <pos x="12934950" y="124574300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3120,7 +3120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="126422150"/>
+    <pos x="7391400" y="126422150"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3140,7 +3140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="126422150"/>
+    <pos x="9239250" y="126422150"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3160,7 +3160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="130111500"/>
+    <pos x="7391400" y="130111500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3180,7 +3180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="130111500"/>
+    <pos x="9239250" y="130111500"/>
     <ext cx="1809750" cy="1609725"/>
     <pic>
       <nvPicPr>
@@ -3200,7 +3200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="130111500"/>
+    <pos x="11087100" y="130111500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3220,7 +3220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="130111500"/>
+    <pos x="12934950" y="130111500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3240,7 +3240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="131959350"/>
+    <pos x="7391400" y="131959350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3260,7 +3260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="131959350"/>
+    <pos x="9239250" y="131959350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3280,7 +3280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="131959350"/>
+    <pos x="11087100" y="131959350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3300,7 +3300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="131959350"/>
+    <pos x="12934950" y="131959350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3320,7 +3320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="133807200"/>
+    <pos x="7391400" y="133807200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3340,7 +3340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="133807200"/>
+    <pos x="9239250" y="133807200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3360,7 +3360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="138125200"/>
+    <pos x="7391400" y="138125200"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3380,7 +3380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="138125200"/>
+    <pos x="9239250" y="138125200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3400,7 +3400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="138125200"/>
+    <pos x="11087100" y="138125200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3420,7 +3420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="138125200"/>
+    <pos x="12934950" y="138125200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3440,7 +3440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="139973050"/>
+    <pos x="7391400" y="139973050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3460,7 +3460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="139973050"/>
+    <pos x="9239250" y="139973050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3480,7 +3480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="139973050"/>
+    <pos x="11087100" y="139973050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3500,7 +3500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="139973050"/>
+    <pos x="12934950" y="139973050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3520,7 +3520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="141820900"/>
+    <pos x="7391400" y="141820900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3540,7 +3540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="141820900"/>
+    <pos x="9239250" y="141820900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3560,7 +3560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="141820900"/>
+    <pos x="11087100" y="141820900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3580,7 +3580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="148577300"/>
+    <pos x="7391400" y="148577300"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3600,7 +3600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="148577300"/>
+    <pos x="9239250" y="148577300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3620,7 +3620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="148577300"/>
+    <pos x="11087100" y="148577300"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -3640,7 +3640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="148577300"/>
+    <pos x="12934950" y="148577300"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3660,7 +3660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="150425150"/>
+    <pos x="7391400" y="150425150"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3680,7 +3680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="150425150"/>
+    <pos x="9239250" y="150425150"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3700,7 +3700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="150425150"/>
+    <pos x="11087100" y="150425150"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3720,7 +3720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="150425150"/>
+    <pos x="12934950" y="150425150"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3740,7 +3740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="152273000"/>
+    <pos x="7391400" y="152273000"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3760,7 +3760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="154197050"/>
+    <pos x="7391400" y="154197050"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3780,7 +3780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="154197050"/>
+    <pos x="9239250" y="154197050"/>
     <ext cx="1809750" cy="971550"/>
     <pic>
       <nvPicPr>
@@ -3800,7 +3800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="154197050"/>
+    <pos x="11087100" y="154197050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3820,7 +3820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="154197050"/>
+    <pos x="12934950" y="154197050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3840,7 +3840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="156044900"/>
+    <pos x="7391400" y="156044900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3860,7 +3860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="156044900"/>
+    <pos x="9239250" y="156044900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3880,7 +3880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="156044900"/>
+    <pos x="11087100" y="156044900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3900,7 +3900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="156044900"/>
+    <pos x="12934950" y="156044900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3920,7 +3920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="157892749"/>
+    <pos x="7391400" y="157892749"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3940,7 +3940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="157892749"/>
+    <pos x="9239250" y="157892749"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3960,7 +3960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="166681150"/>
+    <pos x="7391400" y="166681150"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3980,7 +3980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="166681150"/>
+    <pos x="9239250" y="166681150"/>
     <ext cx="1809750" cy="1609725"/>
     <pic>
       <nvPicPr>
@@ -4000,7 +4000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="166681150"/>
+    <pos x="11087100" y="166681150"/>
     <ext cx="1809750" cy="1704975"/>
     <pic>
       <nvPicPr>
@@ -4020,7 +4020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="166681150"/>
+    <pos x="12934950" y="166681150"/>
     <ext cx="1809750" cy="1162050"/>
     <pic>
       <nvPicPr>
@@ -4040,7 +4040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="170224450"/>
+    <pos x="7391400" y="170224450"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4060,7 +4060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="170224450"/>
+    <pos x="9239250" y="170224450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4080,7 +4080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="170224450"/>
+    <pos x="11087100" y="170224450"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4100,7 +4100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="184334150"/>
+    <pos x="7391400" y="184334150"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4120,7 +4120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="184334150"/>
+    <pos x="9239250" y="184334150"/>
     <ext cx="1809750" cy="1447800"/>
     <pic>
       <nvPicPr>
@@ -4140,7 +4140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="184334150"/>
+    <pos x="11087100" y="184334150"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4160,7 +4160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="184334150"/>
+    <pos x="12934950" y="184334150"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4180,7 +4180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="186182000"/>
+    <pos x="7391400" y="186182000"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4200,7 +4200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="189096650"/>
+    <pos x="7391400" y="189096650"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4220,7 +4220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="189096650"/>
+    <pos x="9239250" y="189096650"/>
     <ext cx="1428750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4240,7 +4240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="189096650"/>
+    <pos x="11087100" y="189096650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4260,7 +4260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="189096650"/>
+    <pos x="12934950" y="189096650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4280,7 +4280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="190944500"/>
+    <pos x="7391400" y="190944500"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4300,7 +4300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="196500750"/>
+    <pos x="7391400" y="196500750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4320,7 +4320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="196500750"/>
+    <pos x="9239250" y="196500750"/>
     <ext cx="1809750" cy="523875"/>
     <pic>
       <nvPicPr>
@@ -4340,7 +4340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="196500750"/>
+    <pos x="11087100" y="196500750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4360,7 +4360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="196500750"/>
+    <pos x="12934950" y="196500750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4380,7 +4380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="198348600"/>
+    <pos x="7391400" y="198348600"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4400,7 +4400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="198348600"/>
+    <pos x="9239250" y="198348600"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4420,7 +4420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="198348600"/>
+    <pos x="11087100" y="198348600"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4440,7 +4440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="198348600"/>
+    <pos x="12934950" y="198348600"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4460,7 +4460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="203295250"/>
+    <pos x="7391400" y="203295250"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4480,7 +4480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="203295250"/>
+    <pos x="9239250" y="203295250"/>
     <ext cx="1809750" cy="1609725"/>
     <pic>
       <nvPicPr>
@@ -4500,7 +4500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="203295250"/>
+    <pos x="11087100" y="203295250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4520,7 +4520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="203295250"/>
+    <pos x="12934950" y="203295250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4540,7 +4540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="205143100"/>
+    <pos x="7391400" y="205143100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4560,7 +4560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="205143100"/>
+    <pos x="9239250" y="205143100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4580,7 +4580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="205143100"/>
+    <pos x="11087100" y="205143100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4600,7 +4600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="205143100"/>
+    <pos x="12934950" y="205143100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4620,7 +4620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="208057750"/>
+    <pos x="7391400" y="208057750"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4640,7 +4640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="208057750"/>
+    <pos x="9239250" y="208057750"/>
     <ext cx="1809750" cy="1304925"/>
     <pic>
       <nvPicPr>
@@ -4660,7 +4660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="208057750"/>
+    <pos x="11087100" y="208057750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4680,7 +4680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="208057750"/>
+    <pos x="12934950" y="208057750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4700,7 +4700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="209905600"/>
+    <pos x="7391400" y="209905600"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4720,7 +4720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="216071450"/>
+    <pos x="7391400" y="216071450"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4740,7 +4740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="216071450"/>
+    <pos x="9239250" y="216071450"/>
     <ext cx="1809750" cy="1476375"/>
     <pic>
       <nvPicPr>
@@ -4760,7 +4760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="216071450"/>
+    <pos x="11087100" y="216071450"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -4780,7 +4780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="216071450"/>
+    <pos x="12934950" y="216071450"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4800,7 +4800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="217919300"/>
+    <pos x="7391400" y="217919300"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4820,7 +4820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="217919300"/>
+    <pos x="9239250" y="217919300"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4840,7 +4840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="217919300"/>
+    <pos x="11087100" y="217919300"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4860,7 +4860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="217919300"/>
+    <pos x="12934950" y="217919300"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4880,7 +4880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="219767150"/>
+    <pos x="7391400" y="219767150"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4900,7 +4900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="219767150"/>
+    <pos x="9239250" y="219767150"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4920,7 +4920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="219767150"/>
+    <pos x="11087100" y="219767150"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4940,7 +4940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="219767150"/>
+    <pos x="12934950" y="219767150"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4960,7 +4960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="226726750"/>
+    <pos x="7391400" y="226726750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4980,7 +4980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="226726750"/>
+    <pos x="9239250" y="226726750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5000,7 +5000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="226726750"/>
+    <pos x="11087100" y="226726750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5020,7 +5020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="226726750"/>
+    <pos x="12934950" y="226726750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5040,7 +5040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="228574600"/>
+    <pos x="7391400" y="228574600"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5060,7 +5060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="228574600"/>
+    <pos x="9239250" y="228574600"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5080,7 +5080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="228574600"/>
+    <pos x="11087100" y="228574600"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5100,7 +5100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="228574600"/>
+    <pos x="12934950" y="228574600"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5120,7 +5120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="230422450"/>
+    <pos x="7391400" y="230422450"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5140,7 +5140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="230422450"/>
+    <pos x="9239250" y="230422450"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5160,7 +5160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="230422450"/>
+    <pos x="11087100" y="230422450"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5180,7 +5180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="236366050"/>
+    <pos x="7391400" y="236366050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5200,7 +5200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="236366050"/>
+    <pos x="9239250" y="236366050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5220,7 +5220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="236366050"/>
+    <pos x="11087100" y="236366050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5240,7 +5240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="236366050"/>
+    <pos x="12934950" y="236366050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5260,7 +5260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="243160550"/>
+    <pos x="7391400" y="243160550"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -5280,7 +5280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="243160550"/>
+    <pos x="9239250" y="243160550"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5300,7 +5300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="243160550"/>
+    <pos x="11087100" y="243160550"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5320,7 +5320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="243160550"/>
+    <pos x="12934950" y="243160550"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5340,7 +5340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="249548650"/>
+    <pos x="7391400" y="249548650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5360,7 +5360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="249548650"/>
+    <pos x="9239250" y="249548650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5380,7 +5380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="249548650"/>
+    <pos x="11087100" y="249548650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5400,7 +5400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="249548650"/>
+    <pos x="12934950" y="249548650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5420,7 +5420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="259187950"/>
+    <pos x="7391400" y="259187950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5440,7 +5440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="259187950"/>
+    <pos x="9239250" y="259187950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5460,7 +5460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="259187950"/>
+    <pos x="11087100" y="259187950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5480,7 +5480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="259187950"/>
+    <pos x="12934950" y="259187950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5500,7 +5500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="261035800"/>
+    <pos x="7391400" y="261035800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5520,7 +5520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="261035800"/>
+    <pos x="9239250" y="261035800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5540,7 +5540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="261035800"/>
+    <pos x="11087100" y="261035800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5560,7 +5560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="264966450"/>
+    <pos x="7391400" y="264966450"/>
     <ext cx="1809750" cy="1695450"/>
     <pic>
       <nvPicPr>
@@ -5580,7 +5580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="264966450"/>
+    <pos x="9239250" y="264966450"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5600,7 +5600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="264966450"/>
+    <pos x="11087100" y="264966450"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5620,7 +5620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="264966450"/>
+    <pos x="12934950" y="264966450"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5640,7 +5640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="273183350"/>
+    <pos x="7391400" y="273183350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5660,7 +5660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="273183350"/>
+    <pos x="9239250" y="273183350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5680,7 +5680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="273183350"/>
+    <pos x="11087100" y="273183350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5700,7 +5700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="273183350"/>
+    <pos x="12934950" y="273183350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5720,7 +5720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="275031200"/>
+    <pos x="7391400" y="275031200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5740,7 +5740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="275031200"/>
+    <pos x="9239250" y="275031200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5760,7 +5760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="275031200"/>
+    <pos x="11087100" y="275031200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5780,7 +5780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="281197050"/>
+    <pos x="7391400" y="281197050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5800,7 +5800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="281197050"/>
+    <pos x="9239250" y="281197050"/>
     <ext cx="1809750" cy="1085850"/>
     <pic>
       <nvPicPr>
@@ -5820,7 +5820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="281197050"/>
+    <pos x="11087100" y="281197050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5840,7 +5840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="281197050"/>
+    <pos x="12934950" y="281197050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5860,7 +5860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="283044900"/>
+    <pos x="7391400" y="283044900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5880,7 +5880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="286569150"/>
+    <pos x="7391400" y="286569150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5900,7 +5900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="286569150"/>
+    <pos x="9239250" y="286569150"/>
     <ext cx="1809750" cy="1085850"/>
     <pic>
       <nvPicPr>
@@ -5920,7 +5920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="286569150"/>
+    <pos x="11087100" y="286569150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5940,7 +5940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="286569150"/>
+    <pos x="12934950" y="286569150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5960,7 +5960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="288417000"/>
+    <pos x="7391400" y="288417000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5980,7 +5980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="293160450"/>
+    <pos x="7391400" y="293160450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6000,7 +6000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="293160450"/>
+    <pos x="9239250" y="293160450"/>
     <ext cx="1809750" cy="1095375"/>
     <pic>
       <nvPicPr>
@@ -6020,7 +6020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="293160450"/>
+    <pos x="11087100" y="293160450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6040,7 +6040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="293160450"/>
+    <pos x="12934950" y="293160450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6060,7 +6060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="295008300"/>
+    <pos x="7391400" y="295008300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6080,7 +6080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="300158150"/>
+    <pos x="7391400" y="300158150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6100,7 +6100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="300158150"/>
+    <pos x="9239250" y="300158150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6120,7 +6120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="300158150"/>
+    <pos x="11087100" y="300158150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6140,7 +6140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="300158150"/>
+    <pos x="12934950" y="300158150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6160,7 +6160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="302006000"/>
+    <pos x="7391400" y="302006000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6180,7 +6180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="302006000"/>
+    <pos x="9239250" y="302006000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6200,7 +6200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="302006000"/>
+    <pos x="11087100" y="302006000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6220,7 +6220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="302006000"/>
+    <pos x="12934950" y="302006000"/>
     <ext cx="1809750" cy="876300"/>
     <pic>
       <nvPicPr>
@@ -6240,7 +6240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="309594250"/>
+    <pos x="7391400" y="309594250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6260,7 +6260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="309594250"/>
+    <pos x="9239250" y="309594250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6280,7 +6280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="309594250"/>
+    <pos x="11087100" y="309594250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6300,7 +6300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="309594250"/>
+    <pos x="12934950" y="309594250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6320,7 +6320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="315575950"/>
+    <pos x="7391400" y="315575950"/>
     <ext cx="1381125" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6340,7 +6340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="315575950"/>
+    <pos x="9239250" y="315575950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6360,7 +6360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="315575950"/>
+    <pos x="11087100" y="315575950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6380,7 +6380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="315575950"/>
+    <pos x="12934950" y="315575950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6400,7 +6400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="322370450"/>
+    <pos x="7391400" y="322370450"/>
     <ext cx="1466850" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6420,7 +6420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="322370450"/>
+    <pos x="9239250" y="322370450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6440,7 +6440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="322370450"/>
+    <pos x="11087100" y="322370450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6460,7 +6460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="322370450"/>
+    <pos x="12934950" y="322370450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6480,7 +6480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="329977750"/>
+    <pos x="7391400" y="329977750"/>
     <ext cx="1809750" cy="1533525"/>
     <pic>
       <nvPicPr>
@@ -6500,7 +6500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="329977750"/>
+    <pos x="9239250" y="329977750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6520,7 +6520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="329977750"/>
+    <pos x="11087100" y="329977750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6540,7 +6540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="329977750"/>
+    <pos x="12934950" y="329977750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6560,7 +6560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="335756250"/>
+    <pos x="7391400" y="335756250"/>
     <ext cx="1647825" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6580,7 +6580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="335756250"/>
+    <pos x="9239250" y="335756250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6600,7 +6600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="335756250"/>
+    <pos x="11087100" y="335756250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6620,7 +6620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="335756250"/>
+    <pos x="12934950" y="335756250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6640,7 +6640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="337604100"/>
+    <pos x="7391400" y="337604100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6660,7 +6660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="337604100"/>
+    <pos x="9239250" y="337604100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6680,7 +6680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="337604100"/>
+    <pos x="11087100" y="337604100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6700,7 +6700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="342550750"/>
+    <pos x="7391400" y="342550750"/>
     <ext cx="1809750" cy="1752600"/>
     <pic>
       <nvPicPr>
@@ -6720,7 +6720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="342550750"/>
+    <pos x="9239250" y="342550750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6740,7 +6740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="342550750"/>
+    <pos x="11087100" y="342550750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6760,7 +6760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="342550750"/>
+    <pos x="12934950" y="342550750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6780,7 +6780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="344398600"/>
+    <pos x="7391400" y="344398600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6800,7 +6800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="344398600"/>
+    <pos x="9239250" y="344398600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6820,7 +6820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="344398600"/>
+    <pos x="11087100" y="344398600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6840,7 +6840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="348126050"/>
+    <pos x="7391400" y="348126050"/>
     <ext cx="1704975" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6860,7 +6860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="348126050"/>
+    <pos x="9239250" y="348126050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6880,7 +6880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="348126050"/>
+    <pos x="11087100" y="348126050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6900,7 +6900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="348126050"/>
+    <pos x="12934950" y="348126050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6920,7 +6920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="349973900"/>
+    <pos x="7391400" y="349973900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6940,7 +6940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="349973900"/>
+    <pos x="9239250" y="349973900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6960,7 +6960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="349973900"/>
+    <pos x="11087100" y="349973900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6980,7 +6980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="354107750"/>
+    <pos x="7391400" y="354107750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7000,7 +7000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="354107750"/>
+    <pos x="9239250" y="354107750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7020,7 +7020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="354107750"/>
+    <pos x="11087100" y="354107750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7040,7 +7040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="354107750"/>
+    <pos x="12934950" y="354107750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7060,7 +7060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="355955600"/>
+    <pos x="7391400" y="355955600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7080,7 +7080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="355955600"/>
+    <pos x="9239250" y="355955600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7100,7 +7100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="355955600"/>
+    <pos x="11087100" y="355955600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7120,7 +7120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="360902250"/>
+    <pos x="7391400" y="360902250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7140,7 +7140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="360902250"/>
+    <pos x="9239250" y="360902250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7160,7 +7160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="360902250"/>
+    <pos x="11087100" y="360902250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7180,7 +7180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="360902250"/>
+    <pos x="12934950" y="360902250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7200,7 +7200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="362750100"/>
+    <pos x="7391400" y="362750100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7220,7 +7220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="362750100"/>
+    <pos x="9239250" y="362750100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7240,7 +7240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="362750100"/>
+    <pos x="11087100" y="362750100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7260,7 +7260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="367087150"/>
+    <pos x="7391400" y="367087150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7280,7 +7280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="367087150"/>
+    <pos x="9239250" y="367087150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7300,7 +7300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="367087150"/>
+    <pos x="11087100" y="367087150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7320,7 +7320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="367087150"/>
+    <pos x="12934950" y="367087150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7340,7 +7340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="368935000"/>
+    <pos x="7391400" y="368935000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7360,7 +7360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="368935000"/>
+    <pos x="9239250" y="368935000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7380,7 +7380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="368935000"/>
+    <pos x="11087100" y="368935000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7400,7 +7400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="374084850"/>
+    <pos x="7391400" y="374084850"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -7420,7 +7420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="374084850"/>
+    <pos x="9239250" y="374084850"/>
     <ext cx="1476375" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7440,7 +7440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="374084850"/>
+    <pos x="11087100" y="374084850"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -7460,7 +7460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="374084850"/>
+    <pos x="12934950" y="374084850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7480,7 +7480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="375932700"/>
+    <pos x="7391400" y="375932700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7500,7 +7500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="375932700"/>
+    <pos x="9239250" y="375932700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7520,7 +7520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="375932700"/>
+    <pos x="11087100" y="375932700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7540,7 +7540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="375932700"/>
+    <pos x="12934950" y="375932700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7560,7 +7560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="377780550"/>
+    <pos x="7391400" y="377780550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7580,7 +7580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="384536950"/>
+    <pos x="7391400" y="384536950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7600,7 +7600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="384536950"/>
+    <pos x="9239250" y="384536950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7620,7 +7620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="384536950"/>
+    <pos x="11087100" y="384536950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7640,7 +7640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="384536950"/>
+    <pos x="12934950" y="384536950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7660,7 +7660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="386384800"/>
+    <pos x="7391400" y="386384800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7680,7 +7680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="386384800"/>
+    <pos x="9239250" y="386384800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7700,7 +7700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="386384800"/>
+    <pos x="11087100" y="386384800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7720,7 +7720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="389909050"/>
+    <pos x="7391400" y="389909050"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -7740,7 +7740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="389909050"/>
+    <pos x="9239250" y="389909050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7760,7 +7760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="389909050"/>
+    <pos x="11087100" y="389909050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -7780,7 +7780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="389909050"/>
+    <pos x="12934950" y="389909050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -7800,7 +7800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="391756900"/>
+    <pos x="7391400" y="391756900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -7820,7 +7820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="391756900"/>
+    <pos x="9239250" y="391756900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -7840,7 +7840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="391756900"/>
+    <pos x="11087100" y="391756900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -7860,7 +7860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="391756900"/>
+    <pos x="12934950" y="391756900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -7880,7 +7880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="393604750"/>
+    <pos x="7391400" y="393604750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -7900,7 +7900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="393604750"/>
+    <pos x="9239250" y="393604750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -7920,7 +7920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="393604750"/>
+    <pos x="11087100" y="393604750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -7940,7 +7940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="401377150"/>
+    <pos x="7391400" y="401377150"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -7960,7 +7960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="401377150"/>
+    <pos x="9239250" y="401377150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7980,7 +7980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="401377150"/>
+    <pos x="11087100" y="401377150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8000,7 +8000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="401377150"/>
+    <pos x="12934950" y="401377150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8020,7 +8020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="409594050"/>
+    <pos x="7391400" y="409594050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8040,7 +8040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="409594050"/>
+    <pos x="9239250" y="409594050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8060,7 +8060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="409594050"/>
+    <pos x="11087100" y="409594050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8080,7 +8080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="409594050"/>
+    <pos x="12934950" y="409594050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8100,7 +8100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="411441900"/>
+    <pos x="7391400" y="411441900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8120,7 +8120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="411441900"/>
+    <pos x="9239250" y="411441900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8140,7 +8140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="411441900"/>
+    <pos x="11087100" y="411441900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8160,7 +8160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="415778950"/>
+    <pos x="7391400" y="415778950"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -8180,7 +8180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="415778950"/>
+    <pos x="9239250" y="415778950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8200,7 +8200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="415778950"/>
+    <pos x="11087100" y="415778950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8220,7 +8220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="415778950"/>
+    <pos x="12934950" y="415778950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8240,7 +8240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="417626800"/>
+    <pos x="7391400" y="417626800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8260,7 +8260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="417626800"/>
+    <pos x="9239250" y="417626800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8280,7 +8280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="417626800"/>
+    <pos x="11087100" y="417626800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8300,7 +8300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="417626800"/>
+    <pos x="12934950" y="417626800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8320,7 +8320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="421963850"/>
+    <pos x="7391400" y="421963850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8340,7 +8340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="421963850"/>
+    <pos x="9239250" y="421963850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8360,7 +8360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="421963850"/>
+    <pos x="11087100" y="421963850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8380,7 +8380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="421963850"/>
+    <pos x="12934950" y="421963850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8400,7 +8400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="423811700"/>
+    <pos x="7391400" y="423811700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8420,7 +8420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="423811700"/>
+    <pos x="9239250" y="423811700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8440,7 +8440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="423811700"/>
+    <pos x="11087100" y="423811700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8460,7 +8460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="423811700"/>
+    <pos x="12934950" y="423811700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8480,7 +8480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="425659550"/>
+    <pos x="7391400" y="425659550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8500,7 +8500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="425659550"/>
+    <pos x="9239250" y="425659550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8520,7 +8520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="432415950"/>
+    <pos x="7391400" y="432415950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8540,7 +8540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="432415950"/>
+    <pos x="9239250" y="432415950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8560,7 +8560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="432415950"/>
+    <pos x="11087100" y="432415950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8580,7 +8580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="432415950"/>
+    <pos x="12934950" y="432415950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8600,7 +8600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="434263800"/>
+    <pos x="7391400" y="434263800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8620,7 +8620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="434263800"/>
+    <pos x="9239250" y="434263800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8640,7 +8640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="441039250"/>
+    <pos x="7391400" y="441039250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8660,7 +8660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="441039250"/>
+    <pos x="9239250" y="441039250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8680,7 +8680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="441039250"/>
+    <pos x="11087100" y="441039250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8700,7 +8700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="441039250"/>
+    <pos x="12934950" y="441039250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8720,7 +8720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="442887100"/>
+    <pos x="7391400" y="442887100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8740,7 +8740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="442887100"/>
+    <pos x="9239250" y="442887100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8760,7 +8760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="442887100"/>
+    <pos x="11087100" y="442887100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8780,7 +8780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="442887100"/>
+    <pos x="12934950" y="442887100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8800,7 +8800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="444734950"/>
+    <pos x="7391400" y="444734950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8820,7 +8820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="444734950"/>
+    <pos x="9239250" y="444734950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8840,7 +8840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="444734950"/>
+    <pos x="11087100" y="444734950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8860,7 +8860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="444734950"/>
+    <pos x="12934950" y="444734950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8880,7 +8880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="446582800"/>
+    <pos x="7391400" y="446582800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8900,7 +8900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="448506850"/>
+    <pos x="7391400" y="448506850"/>
     <ext cx="1809750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -8920,7 +8920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="448506850"/>
+    <pos x="9239250" y="448506850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8940,7 +8940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="448506850"/>
+    <pos x="11087100" y="448506850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8960,7 +8960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="448506850"/>
+    <pos x="12934950" y="448506850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8980,7 +8980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="450354700"/>
+    <pos x="7391400" y="450354700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9000,7 +9000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="450354700"/>
+    <pos x="9239250" y="450354700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9020,7 +9020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="450354700"/>
+    <pos x="11087100" y="450354700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9040,7 +9040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="450354700"/>
+    <pos x="12934950" y="450354700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9060,7 +9060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="452202550"/>
+    <pos x="7391400" y="452202550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9080,7 +9080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="452202550"/>
+    <pos x="9239250" y="452202550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9100,7 +9100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="452202550"/>
+    <pos x="11087100" y="452202550"/>
     <ext cx="1809750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -9120,7 +9120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="452202550"/>
+    <pos x="12934950" y="452202550"/>
     <ext cx="1809750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -9140,7 +9140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="457130150"/>
+    <pos x="7391400" y="457130150"/>
     <ext cx="1809750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -9160,7 +9160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="457130150"/>
+    <pos x="9239250" y="457130150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9180,7 +9180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="457130150"/>
+    <pos x="11087100" y="457130150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9200,7 +9200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="457130150"/>
+    <pos x="12934950" y="457130150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9220,7 +9220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="458978000"/>
+    <pos x="7391400" y="458978000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9240,7 +9240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="458978000"/>
+    <pos x="9239250" y="458978000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9260,7 +9260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="458978000"/>
+    <pos x="11087100" y="458978000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9280,7 +9280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="466769450"/>
+    <pos x="7391400" y="466769450"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -9300,7 +9300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="466769450"/>
+    <pos x="9239250" y="466769450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9320,7 +9320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="466769450"/>
+    <pos x="11087100" y="466769450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9340,7 +9340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="466769450"/>
+    <pos x="12934950" y="466769450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9360,7 +9360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="468617300"/>
+    <pos x="7391400" y="468617300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9380,7 +9380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="468617300"/>
+    <pos x="9239250" y="468617300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9400,7 +9400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="468617300"/>
+    <pos x="11087100" y="468617300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9420,7 +9420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="468617300"/>
+    <pos x="12934950" y="468617300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9440,7 +9440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="472547950"/>
+    <pos x="7391400" y="472547950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9460,7 +9460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="472547950"/>
+    <pos x="9239250" y="472547950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9480,7 +9480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="472547950"/>
+    <pos x="11087100" y="472547950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9500,7 +9500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="472547950"/>
+    <pos x="12934950" y="472547950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9520,7 +9520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="474395800"/>
+    <pos x="7391400" y="474395800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9540,7 +9540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="474395800"/>
+    <pos x="9239250" y="474395800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9560,7 +9560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="474395800"/>
+    <pos x="11087100" y="474395800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9580,7 +9580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="479952050"/>
+    <pos x="7391400" y="479952050"/>
     <ext cx="1647825" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9600,7 +9600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="479952050"/>
+    <pos x="9239250" y="479952050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9620,7 +9620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="479952050"/>
+    <pos x="11087100" y="479952050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9640,7 +9640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="479952050"/>
+    <pos x="12934950" y="479952050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9660,7 +9660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="481799900"/>
+    <pos x="7391400" y="481799900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9680,7 +9680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="481799900"/>
+    <pos x="9239250" y="481799900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9700,7 +9700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="481799900"/>
+    <pos x="11087100" y="481799900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9720,7 +9720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="486746550"/>
+    <pos x="7391400" y="486746550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9740,7 +9740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="486746550"/>
+    <pos x="9239250" y="486746550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9760,7 +9760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="486746550"/>
+    <pos x="11087100" y="486746550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9780,7 +9780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="486746550"/>
+    <pos x="12934950" y="486746550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9800,7 +9800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="488594400"/>
+    <pos x="7391400" y="488594400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9820,7 +9820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="488594400"/>
+    <pos x="9239250" y="488594400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9840,7 +9840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="488594400"/>
+    <pos x="11087100" y="488594400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9860,7 +9860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="488594400"/>
+    <pos x="12934950" y="488594400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9880,7 +9880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="490442250"/>
+    <pos x="7391400" y="490442250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9900,7 +9900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="490442250"/>
+    <pos x="9239250" y="490442250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9920,7 +9920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="490442250"/>
+    <pos x="11087100" y="490442250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9940,7 +9940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="498011450"/>
+    <pos x="7391400" y="498011450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9960,7 +9960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="498011450"/>
+    <pos x="9239250" y="498011450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9980,7 +9980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="498011450"/>
+    <pos x="11087100" y="498011450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10000,7 +10000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="498011450"/>
+    <pos x="12934950" y="498011450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10020,7 +10020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="499859300"/>
+    <pos x="7391400" y="499859300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10040,7 +10040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="499859300"/>
+    <pos x="9239250" y="499859300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10060,7 +10060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="499859300"/>
+    <pos x="11087100" y="499859300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10080,7 +10080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="499859300"/>
+    <pos x="12934950" y="499859300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10100,7 +10100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="501707150"/>
+    <pos x="7391400" y="501707150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10120,7 +10120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="501707150"/>
+    <pos x="9239250" y="501707150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10140,7 +10140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="501707150"/>
+    <pos x="11087100" y="501707150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10160,7 +10160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="501707150"/>
+    <pos x="12934950" y="501707150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10180,7 +10180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="503555000"/>
+    <pos x="7391400" y="503555000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10200,7 +10200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="507853950"/>
+    <pos x="7391400" y="507853950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10220,7 +10220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="507853950"/>
+    <pos x="9239250" y="507853950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10240,7 +10240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="507853950"/>
+    <pos x="11087100" y="507853950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10260,7 +10260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="507853950"/>
+    <pos x="12934950" y="507853950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10280,7 +10280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="515867650"/>
+    <pos x="7391400" y="515867650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10300,7 +10300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="515867650"/>
+    <pos x="9239250" y="515867650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10320,7 +10320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="515867650"/>
+    <pos x="11087100" y="515867650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10340,7 +10340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="515867650"/>
+    <pos x="12934950" y="515867650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10360,7 +10360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="517715500"/>
+    <pos x="7391400" y="517715500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10380,7 +10380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="517715500"/>
+    <pos x="9239250" y="517715500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10400,7 +10400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="517715500"/>
+    <pos x="11087100" y="517715500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10420,7 +10420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="517715500"/>
+    <pos x="12934950" y="517715500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10440,7 +10440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="519563350"/>
+    <pos x="7391400" y="519563350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10460,7 +10460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="519563350"/>
+    <pos x="9239250" y="519563350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10778,7 +10778,7 @@
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="2" customWidth="1" min="5" max="5"/>
+    <col width="3" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">

--- a/카드_아키타입/12_완제베이스+활성.xlsx
+++ b/카드_아키타입/12_완제베이스+활성.xlsx
@@ -580,7 +580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="18034000"/>
+    <pos x="7848600" y="17830800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -600,7 +600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="18034000"/>
+    <pos x="9696450" y="17830800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -620,7 +620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="18034000"/>
+    <pos x="11544300" y="17830800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -640,7 +640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="18034000"/>
+    <pos x="13392150" y="17830800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -660,7 +660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="19881849"/>
+    <pos x="7848600" y="19678650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -680,7 +680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="19881849"/>
+    <pos x="9696450" y="19678650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -700,7 +700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="19881849"/>
+    <pos x="11544300" y="19678650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -720,7 +720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="25412700"/>
+    <pos x="7848600" y="25209500"/>
     <ext cx="1809750" cy="1752600"/>
     <pic>
       <nvPicPr>
@@ -740,7 +740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="25412700"/>
+    <pos x="9696450" y="25209500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -760,7 +760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="25412700"/>
+    <pos x="11544300" y="25209500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -780,7 +780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="25412700"/>
+    <pos x="13392150" y="25209500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -800,7 +800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="27260550"/>
+    <pos x="7848600" y="27057350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -820,7 +820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="27260550"/>
+    <pos x="9696450" y="27057350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -840,7 +840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="27260550"/>
+    <pos x="11544300" y="27057350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -860,7 +860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="31572200"/>
+    <pos x="7848600" y="31369000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -880,7 +880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="31572200"/>
+    <pos x="9696450" y="31369000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -900,7 +900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="31572200"/>
+    <pos x="11544300" y="31369000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -920,7 +920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="31572200"/>
+    <pos x="13392150" y="31369000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -940,7 +940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="33420050"/>
+    <pos x="7848600" y="33216850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -960,7 +960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="33420050"/>
+    <pos x="9696450" y="33216850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -980,7 +980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="33420050"/>
+    <pos x="11544300" y="33216850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1000,7 +1000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="39560500"/>
+    <pos x="7848600" y="39357300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1020,7 +1020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="39560500"/>
+    <pos x="9696450" y="39357300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1040,7 +1040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="39560500"/>
+    <pos x="11544300" y="39357300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1060,7 +1060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="39560500"/>
+    <pos x="13392150" y="39357300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1080,7 +1080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="46329600"/>
+    <pos x="7848600" y="46126400"/>
     <ext cx="1466850" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1100,7 +1100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="46329600"/>
+    <pos x="9696450" y="46126400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1120,7 +1120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="46329600"/>
+    <pos x="11544300" y="46126400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1140,7 +1140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="46329600"/>
+    <pos x="13392150" y="46126400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1160,7 +1160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="53301900"/>
+    <pos x="7848600" y="53098700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1180,7 +1180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="53301900"/>
+    <pos x="9696450" y="53098700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1200,7 +1200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="53301900"/>
+    <pos x="11544300" y="53098700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1220,7 +1220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="53301900"/>
+    <pos x="13392150" y="53098700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1240,7 +1240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="55149750"/>
+    <pos x="7848600" y="54946550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1260,7 +1260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="55149750"/>
+    <pos x="9696450" y="54946550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1280,7 +1280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="55149750"/>
+    <pos x="11544300" y="54946550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1300,7 +1300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="61087000"/>
+    <pos x="7848600" y="60883800"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1320,7 +1320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="61087000"/>
+    <pos x="9696450" y="60883800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1340,7 +1340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="61087000"/>
+    <pos x="11544300" y="60883800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1360,7 +1360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="61087000"/>
+    <pos x="13392150" y="60883800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1380,7 +1380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="62934850"/>
+    <pos x="7848600" y="62731650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1400,7 +1400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="62934850"/>
+    <pos x="9696450" y="62731650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1420,7 +1420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="62934850"/>
+    <pos x="11544300" y="62731650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1440,7 +1440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="62934850"/>
+    <pos x="13392150" y="62731650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1460,7 +1460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="66840100"/>
+    <pos x="7848600" y="66433700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1480,7 +1480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="66840100"/>
+    <pos x="9696450" y="66433700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1500,7 +1500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="66840100"/>
+    <pos x="11544300" y="66433700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1520,7 +1520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="66840100"/>
+    <pos x="13392150" y="66433700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1540,7 +1540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="68687950"/>
+    <pos x="7848600" y="68281550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1560,7 +1560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="68687950"/>
+    <pos x="9696450" y="68281550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1580,7 +1580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="68687950"/>
+    <pos x="11544300" y="68281550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1600,7 +1600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="74422000"/>
+    <pos x="7848600" y="74015600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1620,7 +1620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="74422000"/>
+    <pos x="9696450" y="74015600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1640,7 +1640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="74422000"/>
+    <pos x="11544300" y="74015600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1660,7 +1660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="74422000"/>
+    <pos x="13392150" y="74015600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1680,7 +1680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="76269850"/>
+    <pos x="7848600" y="75863450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1700,7 +1700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="76269850"/>
+    <pos x="9696450" y="75863450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1720,7 +1720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="76269850"/>
+    <pos x="11544300" y="75863450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1740,7 +1740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="76269850"/>
+    <pos x="13392150" y="75863450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1760,7 +1760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="78117699"/>
+    <pos x="7848600" y="77711300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1780,7 +1780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="78117699"/>
+    <pos x="9696450" y="77711300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1800,7 +1800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="78117699"/>
+    <pos x="11544300" y="77711300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1820,7 +1820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="78117699"/>
+    <pos x="13392150" y="77711300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1840,7 +1840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="79965549"/>
+    <pos x="7848600" y="79559150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1860,7 +1860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="84035900"/>
+    <pos x="7848600" y="83629500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1880,7 +1880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="84035900"/>
+    <pos x="9696450" y="83629500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1900,7 +1900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="84035900"/>
+    <pos x="11544300" y="83629500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1920,7 +1920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="84035900"/>
+    <pos x="13392150" y="83629500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1940,7 +1940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="85883750"/>
+    <pos x="7848600" y="85477350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1960,7 +1960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="85883750"/>
+    <pos x="9696450" y="85477350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1980,7 +1980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="85883750"/>
+    <pos x="11544300" y="85477350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2000,7 +2000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="85883750"/>
+    <pos x="13392150" y="85477350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2020,7 +2020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="87731600"/>
+    <pos x="7848600" y="87325200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2040,7 +2040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="87731600"/>
+    <pos x="9696450" y="87325200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2060,7 +2060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="87731600"/>
+    <pos x="11544300" y="87325200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2080,7 +2080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="87731600"/>
+    <pos x="13392150" y="87325200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2100,7 +2100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="89579450"/>
+    <pos x="7848600" y="89173050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2120,7 +2120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="93649800"/>
+    <pos x="7848600" y="93243400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2140,7 +2140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="93649800"/>
+    <pos x="9696450" y="93243400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2160,7 +2160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="93649800"/>
+    <pos x="11544300" y="93243400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2180,7 +2180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="93649800"/>
+    <pos x="13392150" y="93243400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2200,7 +2200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="95497650"/>
+    <pos x="7848600" y="95091250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2220,7 +2220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="95497650"/>
+    <pos x="9696450" y="95091250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2240,7 +2240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="95497650"/>
+    <pos x="11544300" y="95091250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2260,7 +2260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="95497650"/>
+    <pos x="13392150" y="95091250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2280,7 +2280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="99606100"/>
+    <pos x="7848600" y="98996500"/>
     <ext cx="1704975" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2300,7 +2300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="99606100"/>
+    <pos x="9696450" y="98996500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2320,7 +2320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="99606100"/>
+    <pos x="11544300" y="98996500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2340,7 +2340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="99606100"/>
+    <pos x="13392150" y="98996500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2360,7 +2360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="101453950"/>
+    <pos x="7848600" y="100844350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2380,7 +2380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="101453950"/>
+    <pos x="9696450" y="100844350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2400,7 +2400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="101453950"/>
+    <pos x="11544300" y="100844350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2420,7 +2420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="106172000"/>
+    <pos x="7848600" y="105562400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2440,7 +2440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="106172000"/>
+    <pos x="9696450" y="105562400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2460,7 +2460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="106172000"/>
+    <pos x="11544300" y="105562400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2480,7 +2480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="106172000"/>
+    <pos x="13392150" y="105562400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2500,7 +2500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="108019850"/>
+    <pos x="7848600" y="107410250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2520,7 +2520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="108019850"/>
+    <pos x="9696450" y="107410250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2540,7 +2540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="114769900"/>
+    <pos x="7848600" y="114160300"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2560,7 +2560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="114769900"/>
+    <pos x="9696450" y="114160300"/>
     <ext cx="1809750" cy="1657350"/>
     <pic>
       <nvPicPr>
@@ -2580,7 +2580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="114769900"/>
+    <pos x="11544300" y="114160300"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -2600,7 +2600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="114769900"/>
+    <pos x="13392150" y="114160300"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2620,7 +2620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="116617750"/>
+    <pos x="7848600" y="116008150"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2640,7 +2640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="116617750"/>
+    <pos x="9696450" y="116008150"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2660,7 +2660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="116617750"/>
+    <pos x="11544300" y="116008150"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2680,7 +2680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="116617750"/>
+    <pos x="13392150" y="116008150"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2700,7 +2700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="118465600"/>
+    <pos x="7848600" y="117856000"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2720,7 +2720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="120929400"/>
+    <pos x="7848600" y="120319800"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2740,7 +2740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="120929400"/>
+    <pos x="9696450" y="120319800"/>
     <ext cx="1504950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2760,7 +2760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="120929400"/>
+    <pos x="11544300" y="120319800"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2780,7 +2780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="120929400"/>
+    <pos x="13392150" y="120319800"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2800,7 +2800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="122777250"/>
+    <pos x="7848600" y="122167650"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2820,7 +2820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="122777250"/>
+    <pos x="9696450" y="122167650"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2840,7 +2840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="122777250"/>
+    <pos x="11544300" y="122167650"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2860,7 +2860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="122777250"/>
+    <pos x="13392150" y="122167650"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2880,7 +2880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="126682500"/>
+    <pos x="7848600" y="126072900"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2900,7 +2900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="126682500"/>
+    <pos x="9696450" y="126072900"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -2920,7 +2920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="126682500"/>
+    <pos x="11544300" y="126072900"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2940,7 +2940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="126682500"/>
+    <pos x="13392150" y="126072900"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2960,7 +2960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="128530350"/>
+    <pos x="7848600" y="127920750"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2980,7 +2980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="128530350"/>
+    <pos x="9696450" y="127920750"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3000,7 +3000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="128530350"/>
+    <pos x="11544300" y="127920750"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3020,7 +3020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="131419600"/>
+    <pos x="7848600" y="130810000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3040,7 +3040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="131419600"/>
+    <pos x="9696450" y="130810000"/>
     <ext cx="1809750" cy="1647825"/>
     <pic>
       <nvPicPr>
@@ -3060,7 +3060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="131419600"/>
+    <pos x="11544300" y="130810000"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3080,7 +3080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="131419600"/>
+    <pos x="13392150" y="130810000"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3100,7 +3100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="133267450"/>
+    <pos x="7848600" y="132657850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3120,7 +3120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="133267450"/>
+    <pos x="9696450" y="132657850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3140,7 +3140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="133267450"/>
+    <pos x="11544300" y="132657850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3160,7 +3160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="133267450"/>
+    <pos x="13392150" y="132657850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3180,7 +3180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="135115300"/>
+    <pos x="7848600" y="134505700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3200,7 +3200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="135115300"/>
+    <pos x="9696450" y="134505700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3220,7 +3220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="135115300"/>
+    <pos x="11544300" y="134505700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3240,7 +3240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="135115300"/>
+    <pos x="13392150" y="134505700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3260,7 +3260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="136963150"/>
+    <pos x="7848600" y="136353550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3280,7 +3280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="136963150"/>
+    <pos x="9696450" y="136353550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3300,7 +3300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="141236700"/>
+    <pos x="7848600" y="140627100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3320,7 +3320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="141236700"/>
+    <pos x="9696450" y="140627100"/>
     <ext cx="1809750" cy="1609725"/>
     <pic>
       <nvPicPr>
@@ -3340,7 +3340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="141236700"/>
+    <pos x="11544300" y="140627100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3360,7 +3360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="141236700"/>
+    <pos x="13392150" y="140627100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3380,7 +3380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="143084550"/>
+    <pos x="7848600" y="142474950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3400,7 +3400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="143084550"/>
+    <pos x="9696450" y="142474950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3420,7 +3420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="143084550"/>
+    <pos x="11544300" y="142474950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3440,7 +3440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="143084550"/>
+    <pos x="13392150" y="142474950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3460,7 +3460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="144932400"/>
+    <pos x="7848600" y="144322800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3480,7 +3480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="144932400"/>
+    <pos x="9696450" y="144322800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3500,7 +3500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="149631400"/>
+    <pos x="7848600" y="149021800"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3520,7 +3520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="149631400"/>
+    <pos x="9696450" y="149021800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3540,7 +3540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="149631400"/>
+    <pos x="11544300" y="149021800"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3560,7 +3560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="149631400"/>
+    <pos x="13392150" y="149021800"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3580,7 +3580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="151479250"/>
+    <pos x="7848600" y="150869650"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3600,7 +3600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="151479250"/>
+    <pos x="9696450" y="150869650"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3620,7 +3620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="151479250"/>
+    <pos x="11544300" y="150869650"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3640,7 +3640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="151479250"/>
+    <pos x="13392150" y="150869650"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3660,7 +3660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="153327100"/>
+    <pos x="7848600" y="152717500"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3680,7 +3680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="153327100"/>
+    <pos x="9696450" y="152717500"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3700,7 +3700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="153327100"/>
+    <pos x="11544300" y="152717500"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3720,7 +3720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="160261300"/>
+    <pos x="7848600" y="159651700"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3740,7 +3740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="160261300"/>
+    <pos x="9696450" y="159651700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3760,7 +3760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="160261300"/>
+    <pos x="11544300" y="159651700"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -3780,7 +3780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="160261300"/>
+    <pos x="13392150" y="159651700"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3800,7 +3800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="162109150"/>
+    <pos x="7848600" y="161499550"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3820,7 +3820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="162109150"/>
+    <pos x="9696450" y="161499550"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3840,7 +3840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="162109150"/>
+    <pos x="11544300" y="161499550"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3860,7 +3860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="162109150"/>
+    <pos x="13392150" y="161499550"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3880,7 +3880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="163957000"/>
+    <pos x="7848600" y="163347400"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3900,7 +3900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="166217600"/>
+    <pos x="7848600" y="165608000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3920,7 +3920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="166217600"/>
+    <pos x="9696450" y="165608000"/>
     <ext cx="1809750" cy="971550"/>
     <pic>
       <nvPicPr>
@@ -3940,7 +3940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="166217600"/>
+    <pos x="11544300" y="165608000"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3960,7 +3960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="166217600"/>
+    <pos x="13392150" y="165608000"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3980,7 +3980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="168065450"/>
+    <pos x="7848600" y="167455850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4000,7 +4000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="168065450"/>
+    <pos x="9696450" y="167455850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4020,7 +4020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="168065450"/>
+    <pos x="11544300" y="167455850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4040,7 +4040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="168065450"/>
+    <pos x="13392150" y="167455850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4060,7 +4060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="169913300"/>
+    <pos x="7848600" y="169303700"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4080,7 +4080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="169913300"/>
+    <pos x="9696450" y="169303700"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4100,7 +4100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="179108100"/>
+    <pos x="7848600" y="178498500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4120,7 +4120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="179108100"/>
+    <pos x="9696450" y="178498500"/>
     <ext cx="1809750" cy="1609725"/>
     <pic>
       <nvPicPr>
@@ -4140,7 +4140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="179108100"/>
+    <pos x="11544300" y="178498500"/>
     <ext cx="1809750" cy="1704975"/>
     <pic>
       <nvPicPr>
@@ -4160,7 +4160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="179108100"/>
+    <pos x="13392150" y="178498500"/>
     <ext cx="1809750" cy="1162050"/>
     <pic>
       <nvPicPr>
@@ -4180,7 +4180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="182829200"/>
+    <pos x="7848600" y="182219600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4200,7 +4200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="182829200"/>
+    <pos x="9696450" y="182219600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4220,7 +4220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="182829200"/>
+    <pos x="11544300" y="182219600"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4240,7 +4240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="197319900"/>
+    <pos x="7848600" y="196710300"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4260,7 +4260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="197319900"/>
+    <pos x="9696450" y="196710300"/>
     <ext cx="1809750" cy="1447800"/>
     <pic>
       <nvPicPr>
@@ -4280,7 +4280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="197319900"/>
+    <pos x="11544300" y="196710300"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4300,7 +4300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="197319900"/>
+    <pos x="13392150" y="196710300"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4320,7 +4320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="199167750"/>
+    <pos x="7848600" y="198558150"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4340,7 +4340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="202260200"/>
+    <pos x="7848600" y="201650600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4360,7 +4360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="202260200"/>
+    <pos x="9696450" y="201650600"/>
     <ext cx="1428750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4380,7 +4380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="202260200"/>
+    <pos x="11544300" y="201650600"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4400,7 +4400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="202260200"/>
+    <pos x="13392150" y="201650600"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4420,7 +4420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="204108050"/>
+    <pos x="7848600" y="203498450"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4440,7 +4440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="210045300"/>
+    <pos x="7848600" y="209435700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4460,7 +4460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="210045300"/>
+    <pos x="9696450" y="209435700"/>
     <ext cx="1809750" cy="523875"/>
     <pic>
       <nvPicPr>
@@ -4480,7 +4480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="210045300"/>
+    <pos x="11544300" y="209435700"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4500,7 +4500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="210045300"/>
+    <pos x="13392150" y="209435700"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4520,7 +4520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="211893150"/>
+    <pos x="7848600" y="211283550"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4540,7 +4540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="211893150"/>
+    <pos x="9696450" y="211283550"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4560,7 +4560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="211893150"/>
+    <pos x="11544300" y="211283550"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4580,7 +4580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="211893150"/>
+    <pos x="13392150" y="211283550"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4600,7 +4600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="217017600"/>
+    <pos x="7848600" y="216408000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4620,7 +4620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="217017600"/>
+    <pos x="9696450" y="216408000"/>
     <ext cx="1809750" cy="1609725"/>
     <pic>
       <nvPicPr>
@@ -4640,7 +4640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="217017600"/>
+    <pos x="11544300" y="216408000"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4660,7 +4660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="217017600"/>
+    <pos x="13392150" y="216408000"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4680,7 +4680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="218865450"/>
+    <pos x="7848600" y="218255850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4700,7 +4700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="218865450"/>
+    <pos x="9696450" y="218255850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4720,7 +4720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="218865450"/>
+    <pos x="11544300" y="218255850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4740,7 +4740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="218865450"/>
+    <pos x="13392150" y="218255850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4760,7 +4760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="221957900"/>
+    <pos x="7848600" y="221348300"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4780,7 +4780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="221957900"/>
+    <pos x="9696450" y="221348300"/>
     <ext cx="1809750" cy="1304925"/>
     <pic>
       <nvPicPr>
@@ -4800,7 +4800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="221957900"/>
+    <pos x="11544300" y="221348300"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4820,7 +4820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="221957900"/>
+    <pos x="13392150" y="221348300"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4840,7 +4840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="223805750"/>
+    <pos x="7848600" y="223196150"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4860,7 +4860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="230149400"/>
+    <pos x="7848600" y="229539800"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4880,7 +4880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="230149400"/>
+    <pos x="9696450" y="229539800"/>
     <ext cx="1809750" cy="1476375"/>
     <pic>
       <nvPicPr>
@@ -4900,7 +4900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="230149400"/>
+    <pos x="11544300" y="229539800"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -4920,7 +4920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="230149400"/>
+    <pos x="13392150" y="229539800"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4940,7 +4940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="231997250"/>
+    <pos x="7848600" y="231387650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4960,7 +4960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="231997250"/>
+    <pos x="9696450" y="231387650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4980,7 +4980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="231997250"/>
+    <pos x="11544300" y="231387650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5000,7 +5000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="231997250"/>
+    <pos x="13392150" y="231387650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5020,7 +5020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="233845100"/>
+    <pos x="7848600" y="233235500"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5040,7 +5040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="233845100"/>
+    <pos x="9696450" y="233235500"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5060,7 +5060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="233845100"/>
+    <pos x="11544300" y="233235500"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5080,7 +5080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="233845100"/>
+    <pos x="13392150" y="233235500"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5100,7 +5100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="241795300"/>
+    <pos x="7848600" y="240779300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5120,7 +5120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="241795300"/>
+    <pos x="9696450" y="240779300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5140,7 +5140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="241795300"/>
+    <pos x="11544300" y="240779300"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5160,7 +5160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="241795300"/>
+    <pos x="13392150" y="240779300"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5180,7 +5180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="243643150"/>
+    <pos x="7848600" y="242627150"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5200,7 +5200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="243643150"/>
+    <pos x="9696450" y="242627150"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5220,7 +5220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="243643150"/>
+    <pos x="11544300" y="242627150"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5240,7 +5240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="243643150"/>
+    <pos x="13392150" y="242627150"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5260,7 +5260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="245491000"/>
+    <pos x="7848600" y="244475000"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5280,7 +5280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="245491000"/>
+    <pos x="9696450" y="244475000"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5300,7 +5300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="245491000"/>
+    <pos x="11544300" y="244475000"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5320,7 +5320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="251612400"/>
+    <pos x="7848600" y="250596400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5340,7 +5340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="251612400"/>
+    <pos x="9696450" y="250596400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5360,7 +5360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="251612400"/>
+    <pos x="11544300" y="250596400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5380,7 +5380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="251612400"/>
+    <pos x="13392150" y="250596400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5400,7 +5400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="258991100"/>
+    <pos x="7848600" y="257975100"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -5420,7 +5420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="258991100"/>
+    <pos x="9696450" y="257975100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5440,7 +5440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="258991100"/>
+    <pos x="11544300" y="257975100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5460,7 +5460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="258991100"/>
+    <pos x="13392150" y="257975100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5480,7 +5480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="265760200"/>
+    <pos x="7848600" y="264744200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5500,7 +5500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="265760200"/>
+    <pos x="9696450" y="264744200"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5520,7 +5520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="265760200"/>
+    <pos x="11544300" y="264744200"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5540,7 +5540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="265760200"/>
+    <pos x="13392150" y="264744200"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5560,7 +5560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="275983700"/>
+    <pos x="7848600" y="274967700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5580,7 +5580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="275983700"/>
+    <pos x="9696450" y="274967700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5600,7 +5600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="275983700"/>
+    <pos x="11544300" y="274967700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5620,7 +5620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="275983700"/>
+    <pos x="13392150" y="274967700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5640,7 +5640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="277831550"/>
+    <pos x="7848600" y="276815550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5660,7 +5660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="277831550"/>
+    <pos x="9696450" y="276815550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5680,7 +5680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="277831550"/>
+    <pos x="11544300" y="276815550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5700,7 +5700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="281940000"/>
+    <pos x="7848600" y="280924000"/>
     <ext cx="1809750" cy="1695450"/>
     <pic>
       <nvPicPr>
@@ -5720,7 +5720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="281940000"/>
+    <pos x="9696450" y="280924000"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5740,7 +5740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="281940000"/>
+    <pos x="11544300" y="280924000"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5760,7 +5760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="281940000"/>
+    <pos x="13392150" y="280924000"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5780,7 +5780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="290537900"/>
+    <pos x="7848600" y="289521900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5800,7 +5800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="290537900"/>
+    <pos x="9696450" y="289521900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5820,7 +5820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="290537900"/>
+    <pos x="11544300" y="289521900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5840,7 +5840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="290537900"/>
+    <pos x="13392150" y="289521900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5860,7 +5860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="292385750"/>
+    <pos x="7848600" y="291369750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5880,7 +5880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="292385750"/>
+    <pos x="9696450" y="291369750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5900,7 +5900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="292385750"/>
+    <pos x="11544300" y="291369750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5920,7 +5920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="298729400"/>
+    <pos x="7848600" y="297713400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5940,7 +5940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="298729400"/>
+    <pos x="9696450" y="297713400"/>
     <ext cx="1809750" cy="1085850"/>
     <pic>
       <nvPicPr>
@@ -5960,7 +5960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="298729400"/>
+    <pos x="11544300" y="297713400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5980,7 +5980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="298729400"/>
+    <pos x="13392150" y="297713400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6000,7 +6000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="300577250"/>
+    <pos x="7848600" y="299561250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6020,7 +6020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="304482500"/>
+    <pos x="7848600" y="303466500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6040,7 +6040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="304482500"/>
+    <pos x="9696450" y="303466500"/>
     <ext cx="1809750" cy="1085850"/>
     <pic>
       <nvPicPr>
@@ -6060,7 +6060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="304482500"/>
+    <pos x="11544300" y="303466500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6080,7 +6080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="304482500"/>
+    <pos x="13392150" y="303466500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6100,7 +6100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="306330350"/>
+    <pos x="7848600" y="305314350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6120,7 +6120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="311454800"/>
+    <pos x="7848600" y="310438800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6140,7 +6140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="311454800"/>
+    <pos x="9696450" y="310438800"/>
     <ext cx="1809750" cy="1095375"/>
     <pic>
       <nvPicPr>
@@ -6160,7 +6160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="311454800"/>
+    <pos x="11544300" y="310438800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6180,7 +6180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="311454800"/>
+    <pos x="13392150" y="310438800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6200,7 +6200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="313302650"/>
+    <pos x="7848600" y="312286650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6220,7 +6220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="318833500"/>
+    <pos x="7848600" y="317817500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6240,7 +6240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="318833500"/>
+    <pos x="9696450" y="317817500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6260,7 +6260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="318833500"/>
+    <pos x="11544300" y="317817500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6280,7 +6280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="318833500"/>
+    <pos x="13392150" y="317817500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6300,7 +6300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="320681350"/>
+    <pos x="7848600" y="319665350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6320,7 +6320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="320681350"/>
+    <pos x="9696450" y="319665350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6340,7 +6340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="320681350"/>
+    <pos x="11544300" y="319665350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6360,7 +6360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="320681350"/>
+    <pos x="13392150" y="319665350"/>
     <ext cx="1809750" cy="876300"/>
     <pic>
       <nvPicPr>
@@ -6380,7 +6380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="328853800"/>
+    <pos x="7848600" y="327837800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6400,7 +6400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="328853800"/>
+    <pos x="9696450" y="327837800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6420,7 +6420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="328853800"/>
+    <pos x="11544300" y="327837800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6440,7 +6440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="328853800"/>
+    <pos x="13392150" y="327837800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6460,7 +6460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="335013300"/>
+    <pos x="7848600" y="333997300"/>
     <ext cx="1381125" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6480,7 +6480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="335013300"/>
+    <pos x="9696450" y="333997300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6500,7 +6500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="335013300"/>
+    <pos x="11544300" y="333997300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6520,7 +6520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="335013300"/>
+    <pos x="13392150" y="333997300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6540,7 +6540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="341985600"/>
+    <pos x="7848600" y="340969600"/>
     <ext cx="1466850" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6560,7 +6560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="341985600"/>
+    <pos x="9696450" y="340969600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6580,7 +6580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="341985600"/>
+    <pos x="11544300" y="340969600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6600,7 +6600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="341985600"/>
+    <pos x="13392150" y="340969600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6620,7 +6620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="350177100"/>
+    <pos x="7848600" y="349161100"/>
     <ext cx="1809750" cy="1533525"/>
     <pic>
       <nvPicPr>
@@ -6640,7 +6640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="350177100"/>
+    <pos x="9696450" y="349161100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6660,7 +6660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="350177100"/>
+    <pos x="11544300" y="349161100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6680,7 +6680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="350177100"/>
+    <pos x="13392150" y="349161100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6700,7 +6700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="356133400"/>
+    <pos x="7848600" y="355117400"/>
     <ext cx="1647825" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6720,7 +6720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="356133400"/>
+    <pos x="9696450" y="355117400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6740,7 +6740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="356133400"/>
+    <pos x="11544300" y="355117400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6760,7 +6760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="356133400"/>
+    <pos x="13392150" y="355117400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6780,7 +6780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="357981250"/>
+    <pos x="7848600" y="356965250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6800,7 +6800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="357981250"/>
+    <pos x="9696450" y="356965250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6820,7 +6820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="357981250"/>
+    <pos x="11544300" y="356965250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6840,7 +6840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="363512100"/>
+    <pos x="7848600" y="362496100"/>
     <ext cx="1809750" cy="1752600"/>
     <pic>
       <nvPicPr>
@@ -6860,7 +6860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="363512100"/>
+    <pos x="9696450" y="362496100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6880,7 +6880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="363512100"/>
+    <pos x="11544300" y="362496100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6900,7 +6900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="363512100"/>
+    <pos x="13392150" y="362496100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6920,7 +6920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="365359950"/>
+    <pos x="7848600" y="364343950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6940,7 +6940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="365359950"/>
+    <pos x="9696450" y="364343950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6960,7 +6960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="365359950"/>
+    <pos x="11544300" y="364343950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6980,7 +6980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="369671600"/>
+    <pos x="7848600" y="368655600"/>
     <ext cx="1704975" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7000,7 +7000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="369671600"/>
+    <pos x="9696450" y="368655600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7020,7 +7020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="369671600"/>
+    <pos x="11544300" y="368655600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7040,7 +7040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="369671600"/>
+    <pos x="13392150" y="368655600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7060,7 +7060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="371519450"/>
+    <pos x="7848600" y="370503450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7080,7 +7080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="371519450"/>
+    <pos x="9696450" y="370503450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7100,7 +7100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="371519450"/>
+    <pos x="11544300" y="370503450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7120,7 +7120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="376237500"/>
+    <pos x="7848600" y="375221500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7140,7 +7140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="376237500"/>
+    <pos x="9696450" y="375221500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7160,7 +7160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="376237500"/>
+    <pos x="11544300" y="375221500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7180,7 +7180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="376237500"/>
+    <pos x="13392150" y="375221500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7200,7 +7200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="378085350"/>
+    <pos x="7848600" y="377069350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7220,7 +7220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="378085350"/>
+    <pos x="9696450" y="377069350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7240,7 +7240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="378085350"/>
+    <pos x="11544300" y="377069350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7260,7 +7260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="383819400"/>
+    <pos x="7848600" y="382803400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7280,7 +7280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="383819400"/>
+    <pos x="9696450" y="382803400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7300,7 +7300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="383819400"/>
+    <pos x="11544300" y="382803400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7320,7 +7320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="383819400"/>
+    <pos x="13392150" y="382803400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7340,7 +7340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="385667250"/>
+    <pos x="7848600" y="384651250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7360,7 +7360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="385667250"/>
+    <pos x="9696450" y="384651250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7380,7 +7380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="385667250"/>
+    <pos x="11544300" y="384651250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7400,7 +7400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="390385300"/>
+    <pos x="7848600" y="389369300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7420,7 +7420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="390385300"/>
+    <pos x="9696450" y="389369300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7440,7 +7440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="390385300"/>
+    <pos x="11544300" y="389369300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7460,7 +7460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="390385300"/>
+    <pos x="13392150" y="389369300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7480,7 +7480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="392233150"/>
+    <pos x="7848600" y="391217150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7500,7 +7500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="392233150"/>
+    <pos x="9696450" y="391217150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7520,7 +7520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="392233150"/>
+    <pos x="11544300" y="391217150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7540,7 +7540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="397764000"/>
+    <pos x="7848600" y="396748000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -7560,7 +7560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="397764000"/>
+    <pos x="9696450" y="396748000"/>
     <ext cx="1476375" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7580,7 +7580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="397764000"/>
+    <pos x="11544300" y="396748000"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -7600,7 +7600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="397764000"/>
+    <pos x="13392150" y="396748000"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7620,7 +7620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="399611850"/>
+    <pos x="7848600" y="398595850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7640,7 +7640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="399611850"/>
+    <pos x="9696450" y="398595850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7660,7 +7660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="399611850"/>
+    <pos x="11544300" y="398595850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7680,7 +7680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="399611850"/>
+    <pos x="13392150" y="398595850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7700,7 +7700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="401459700"/>
+    <pos x="7848600" y="400443700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7720,7 +7720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="408393900"/>
+    <pos x="7848600" y="407377900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7740,7 +7740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="408393900"/>
+    <pos x="9696450" y="407377900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7760,7 +7760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="408393900"/>
+    <pos x="11544300" y="407377900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7780,7 +7780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="408393900"/>
+    <pos x="13392150" y="407377900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7800,7 +7800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="410241750"/>
+    <pos x="7848600" y="409225750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7820,7 +7820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="410241750"/>
+    <pos x="9696450" y="409225750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7840,7 +7840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="410241750"/>
+    <pos x="11544300" y="409225750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7860,7 +7860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="414147000"/>
+    <pos x="7848600" y="413131000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -7880,7 +7880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="414147000"/>
+    <pos x="9696450" y="413131000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7900,7 +7900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="414147000"/>
+    <pos x="11544300" y="413131000"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -7920,7 +7920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="414147000"/>
+    <pos x="13392150" y="413131000"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -7940,7 +7940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="415994850"/>
+    <pos x="7848600" y="414978850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -7960,7 +7960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="415994850"/>
+    <pos x="9696450" y="414978850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -7980,7 +7980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="415994850"/>
+    <pos x="11544300" y="414978850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -8000,7 +8000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="415994850"/>
+    <pos x="13392150" y="414978850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -8020,7 +8020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="417842700"/>
+    <pos x="7848600" y="416826700"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -8040,7 +8040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="417842700"/>
+    <pos x="9696450" y="416826700"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -8060,7 +8060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="417842700"/>
+    <pos x="11544300" y="416826700"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -8080,7 +8080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="425792900"/>
+    <pos x="7848600" y="424776900"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -8100,7 +8100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="425792900"/>
+    <pos x="9696450" y="424776900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8120,7 +8120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="425792900"/>
+    <pos x="11544300" y="424776900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8140,7 +8140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="425792900"/>
+    <pos x="13392150" y="424776900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8160,7 +8160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="434594000"/>
+    <pos x="7848600" y="433374800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8180,7 +8180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="434594000"/>
+    <pos x="9696450" y="433374800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8200,7 +8200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="434594000"/>
+    <pos x="11544300" y="433374800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8220,7 +8220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="434594000"/>
+    <pos x="13392150" y="433374800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8240,7 +8240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="436441850"/>
+    <pos x="7848600" y="435222650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8260,7 +8260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="436441850"/>
+    <pos x="9696450" y="435222650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8280,7 +8280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="436441850"/>
+    <pos x="11544300" y="435222650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8300,7 +8300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="441159900"/>
+    <pos x="7848600" y="439940700"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -8320,7 +8320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="441159900"/>
+    <pos x="9696450" y="439940700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8340,7 +8340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="441159900"/>
+    <pos x="11544300" y="439940700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8360,7 +8360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="441159900"/>
+    <pos x="13392150" y="439940700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8380,7 +8380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="443007750"/>
+    <pos x="7848600" y="441788550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8400,7 +8400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="443007750"/>
+    <pos x="9696450" y="441788550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8420,7 +8420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="443007750"/>
+    <pos x="11544300" y="441788550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8440,7 +8440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="443007750"/>
+    <pos x="13392150" y="441788550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8460,7 +8460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="447929000"/>
+    <pos x="7848600" y="446506600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8480,7 +8480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="447929000"/>
+    <pos x="9696450" y="446506600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8500,7 +8500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="447929000"/>
+    <pos x="11544300" y="446506600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8520,7 +8520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="447929000"/>
+    <pos x="13392150" y="446506600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8540,7 +8540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="449776850"/>
+    <pos x="7848600" y="448354450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8560,7 +8560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="449776850"/>
+    <pos x="9696450" y="448354450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8580,7 +8580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="449776850"/>
+    <pos x="11544300" y="448354450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8600,7 +8600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="449776850"/>
+    <pos x="13392150" y="448354450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8620,7 +8620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="451624700"/>
+    <pos x="7848600" y="450202300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8640,7 +8640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="451624700"/>
+    <pos x="9696450" y="450202300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8660,7 +8660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="458965300"/>
+    <pos x="7848600" y="457542900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8680,7 +8680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="458965300"/>
+    <pos x="9696450" y="457542900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8700,7 +8700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="458965300"/>
+    <pos x="11544300" y="457542900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8720,7 +8720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="458965300"/>
+    <pos x="13392150" y="457542900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8740,7 +8740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="460813150"/>
+    <pos x="7848600" y="459390750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8760,7 +8760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="460813150"/>
+    <pos x="9696450" y="459390750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8780,7 +8780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="467766400"/>
+    <pos x="7848600" y="466344000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8800,7 +8800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="467766400"/>
+    <pos x="9696450" y="466344000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8820,7 +8820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="467766400"/>
+    <pos x="11544300" y="466344000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8840,7 +8840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="467766400"/>
+    <pos x="13392150" y="466344000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8860,7 +8860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="469614250"/>
+    <pos x="7848600" y="468191850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8880,7 +8880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="469614250"/>
+    <pos x="9696450" y="468191850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8900,7 +8900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="469614250"/>
+    <pos x="11544300" y="468191850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8920,7 +8920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="469614250"/>
+    <pos x="13392150" y="468191850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8940,7 +8940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="471462100"/>
+    <pos x="7848600" y="470039700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8960,7 +8960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="471462100"/>
+    <pos x="9696450" y="470039700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8980,7 +8980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="471462100"/>
+    <pos x="11544300" y="470039700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9000,7 +9000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="471462100"/>
+    <pos x="13392150" y="470039700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9020,7 +9020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="473309950"/>
+    <pos x="7848600" y="471887550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9040,7 +9040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="475551500"/>
+    <pos x="7848600" y="474129100"/>
     <ext cx="1809750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -9060,7 +9060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="475551500"/>
+    <pos x="9696450" y="474129100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9080,7 +9080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="475551500"/>
+    <pos x="11544300" y="474129100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9100,7 +9100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="475551500"/>
+    <pos x="13392150" y="474129100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9120,7 +9120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="477399350"/>
+    <pos x="7848600" y="475976950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9140,7 +9140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="477399350"/>
+    <pos x="9696450" y="475976950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9160,7 +9160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="477399350"/>
+    <pos x="11544300" y="475976950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9180,7 +9180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="477399350"/>
+    <pos x="13392150" y="475976950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9200,7 +9200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="479247200"/>
+    <pos x="7848600" y="477824800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9220,7 +9220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="479247200"/>
+    <pos x="9696450" y="477824800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9240,7 +9240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="479247200"/>
+    <pos x="11544300" y="477824800"/>
     <ext cx="1809750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -9260,7 +9260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="479247200"/>
+    <pos x="13392150" y="477824800"/>
     <ext cx="1809750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -9280,7 +9280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="484962200"/>
+    <pos x="7848600" y="483539800"/>
     <ext cx="1809750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -9300,7 +9300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="484962200"/>
+    <pos x="9696450" y="483539800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9320,7 +9320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="484962200"/>
+    <pos x="11544300" y="483539800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9340,7 +9340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="484962200"/>
+    <pos x="13392150" y="483539800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9360,7 +9360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="486810050"/>
+    <pos x="7848600" y="485387650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9380,7 +9380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="486810050"/>
+    <pos x="9696450" y="485387650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9400,7 +9400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="486810050"/>
+    <pos x="11544300" y="485387650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9420,7 +9420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="495592100"/>
+    <pos x="7848600" y="494169700"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -9440,7 +9440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="495592100"/>
+    <pos x="9696450" y="494169700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9460,7 +9460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="495592100"/>
+    <pos x="11544300" y="494169700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9480,7 +9480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="495592100"/>
+    <pos x="13392150" y="494169700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9500,7 +9500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="497439950"/>
+    <pos x="7848600" y="496017550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9520,7 +9520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="497439950"/>
+    <pos x="9696450" y="496017550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9540,7 +9540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="497439950"/>
+    <pos x="11544300" y="496017550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9560,7 +9560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="497439950"/>
+    <pos x="13392150" y="496017550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9580,7 +9580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="501751600"/>
+    <pos x="7848600" y="500329200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9600,7 +9600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="501751600"/>
+    <pos x="9696450" y="500329200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9620,7 +9620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="501751600"/>
+    <pos x="11544300" y="500329200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9640,7 +9640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="501751600"/>
+    <pos x="13392150" y="500329200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9660,7 +9660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="503599450"/>
+    <pos x="7848600" y="502177050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9680,7 +9680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="503599450"/>
+    <pos x="9696450" y="502177050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9700,7 +9700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="503599450"/>
+    <pos x="11544300" y="502177050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9720,7 +9720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="509333500"/>
+    <pos x="7848600" y="507911100"/>
     <ext cx="1647825" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9740,7 +9740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="509333500"/>
+    <pos x="9696450" y="507911100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9760,7 +9760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="509333500"/>
+    <pos x="11544300" y="507911100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9780,7 +9780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="509333500"/>
+    <pos x="13392150" y="507911100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9800,7 +9800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="511181350"/>
+    <pos x="7848600" y="509758950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9820,7 +9820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="511181350"/>
+    <pos x="9696450" y="509758950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9840,7 +9840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="511181350"/>
+    <pos x="11544300" y="509758950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9860,7 +9860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="516712200"/>
+    <pos x="7848600" y="515289800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9880,7 +9880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="516712200"/>
+    <pos x="9696450" y="515289800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9900,7 +9900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="516712200"/>
+    <pos x="11544300" y="515289800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9920,7 +9920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="516712200"/>
+    <pos x="13392150" y="515289800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9940,7 +9940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="518560050"/>
+    <pos x="7848600" y="517137650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9960,7 +9960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="518560050"/>
+    <pos x="9696450" y="517137650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9980,7 +9980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="518560050"/>
+    <pos x="11544300" y="517137650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10000,7 +10000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="518560050"/>
+    <pos x="13392150" y="517137650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10020,7 +10020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="520407900"/>
+    <pos x="7848600" y="518985500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10040,7 +10040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="520407900"/>
+    <pos x="9696450" y="518985500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10060,7 +10060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="520407900"/>
+    <pos x="11544300" y="518985500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10080,7 +10080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="528154900"/>
+    <pos x="7848600" y="526732500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10100,7 +10100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="528154900"/>
+    <pos x="9696450" y="526732500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10120,7 +10120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="528154900"/>
+    <pos x="11544300" y="526732500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10140,7 +10140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="528154900"/>
+    <pos x="13392150" y="526732500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10160,7 +10160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="530002750"/>
+    <pos x="7848600" y="528580350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10180,7 +10180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="530002750"/>
+    <pos x="9696450" y="528580350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10200,7 +10200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="530002750"/>
+    <pos x="11544300" y="528580350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10220,7 +10220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="530002750"/>
+    <pos x="13392150" y="528580350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10240,7 +10240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="531850600"/>
+    <pos x="7848600" y="530428200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10260,7 +10260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="531850600"/>
+    <pos x="9696450" y="530428200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10280,7 +10280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="531850600"/>
+    <pos x="11544300" y="530428200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10300,7 +10300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="531850600"/>
+    <pos x="13392150" y="530428200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10320,7 +10320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="533698450"/>
+    <pos x="7848600" y="532276050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10340,7 +10340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="538581600"/>
+    <pos x="7848600" y="537159200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10360,7 +10360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="538581600"/>
+    <pos x="9696450" y="537159200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10380,7 +10380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="538581600"/>
+    <pos x="11544300" y="537159200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10400,7 +10400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="538581600"/>
+    <pos x="13392150" y="537159200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10420,7 +10420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="546976300"/>
+    <pos x="7848600" y="545553900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10440,7 +10440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="546976300"/>
+    <pos x="9696450" y="545553900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10460,7 +10460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="546976300"/>
+    <pos x="11544300" y="545553900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10480,7 +10480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="546976300"/>
+    <pos x="13392150" y="545553900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10500,7 +10500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="548824150"/>
+    <pos x="7848600" y="547401750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10520,7 +10520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="548824150"/>
+    <pos x="9696450" y="547401750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10540,7 +10540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="548824150"/>
+    <pos x="11544300" y="547401750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10560,7 +10560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="548824150"/>
+    <pos x="13392150" y="547401750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10580,7 +10580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="550672000"/>
+    <pos x="7848600" y="549249600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10600,7 +10600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="550672000"/>
+    <pos x="9696450" y="549249600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -11042,7 +11042,7 @@
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>프랑스 세더마, 지모뿌리유래 / 지용성, 볼륨UP, 지방활성, / 페이셜, 바디 적용</t>
+          <t>프랑스 세더마, 지모뿌리유래 · 지용성, 볼륨UP, 지방활성 · 페이셜, 바디 적용</t>
         </is>
       </c>
       <c r="F8" s="10" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>유기농 불가리안 로즈워터 함유, / 젤타입</t>
+          <t>유기농 불가리안 로즈워터 함유 · 젤타입</t>
         </is>
       </c>
       <c r="F9" s="10" t="inlineStr">
@@ -11106,10 +11106,10 @@
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>미백 인증, 비건처방 / 병풀 핵심성분 4가지, / 재생보습 덱스판테놀, / 유기농 오렌지꽃워터 함유.</t>
-        </is>
-      </c>
-      <c r="F10" s="10" t="n"/>
+          <t>미백 인증, 비건처방 · 병풀 핵심성분 4가지 · 재생보습 덱스판테놀 · 유기농 오렌지꽃워터 함유.</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr"/>
     </row>
     <row r="11" ht="14" customHeight="1">
       <c r="A11" s="13" t="inlineStr">
@@ -11269,10 +11269,10 @@
       </c>
       <c r="E20" s="18" t="inlineStr">
         <is>
-          <t>식약처 인증 미백기능성, / 24시 수분테스트 완료</t>
-        </is>
-      </c>
-      <c r="F20" s="18" t="n"/>
+          <t>식약처 인증 미백기능성 · 24시 수분테스트 완료</t>
+        </is>
+      </c>
+      <c r="F20" s="18" t="inlineStr"/>
     </row>
     <row r="21" ht="32" customHeight="1">
       <c r="A21" s="18" t="inlineStr">
@@ -11297,16 +11297,16 @@
       </c>
       <c r="E21" s="18" t="inlineStr">
         <is>
-          <t>비타민 펩타이드, / 화이트닝</t>
+          <t>비타민 펩타이드 · 화이트닝</t>
         </is>
       </c>
       <c r="F21" s="18" t="inlineStr">
         <is>
-          <t>트라넥삼산 / 펩타이드</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="48" customHeight="1">
+          <t>트라넥삼산 · 펩타이드</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1">
       <c r="A22" s="18" t="inlineStr">
         <is>
           <t>브라이트닝 블렌딩오일</t>
@@ -11329,12 +11329,12 @@
       </c>
       <c r="E22" s="18" t="inlineStr">
         <is>
-          <t>네롤리, 버가못FCF / 일링일랑, 프랑킨센스, / 복합 블렌딩오일</t>
+          <t>네롤리, 버가못FCF · 일링일랑, 프랑킨센스 · 복합 블렌딩오일</t>
         </is>
       </c>
       <c r="F22" s="18" t="inlineStr">
         <is>
-          <t>원하는 / 에센셜오일</t>
+          <t>원하는 · 에센셜오일</t>
         </is>
       </c>
     </row>
@@ -11478,10 +11478,10 @@
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
-          <t>슈퍼시카4, 덱스판테놀, / 내추럴 바세린 / 함유 / 강력 보습&amp;진정</t>
-        </is>
-      </c>
-      <c r="F31" s="10" t="n"/>
+          <t>슈퍼시카4, 덱스판테놀 · 내추럴 바세린 · 함유 · 강력 보습&amp;진정</t>
+        </is>
+      </c>
+      <c r="F31" s="10" t="inlineStr"/>
     </row>
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="10" t="inlineStr">
@@ -11506,7 +11506,7 @@
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
-          <t>금잔화 추출물, / 피부진정</t>
+          <t>금잔화 추출물 · 피부진정</t>
         </is>
       </c>
       <c r="F32" s="10" t="inlineStr">
@@ -11538,12 +11538,12 @@
       </c>
       <c r="E33" s="10" t="inlineStr">
         <is>
-          <t>누룩(천연효모) 발효여과물, / 보습, 탄력, 아미노산, 미네랄, 영양공급</t>
+          <t>누룩(천연효모) 발효여과물 · 보습, 탄력, 아미노산, 미네랄, 영양공급</t>
         </is>
       </c>
       <c r="F33" s="10" t="inlineStr">
         <is>
-          <t>비피다발효용해물, / 사카로미세스발효여과물</t>
+          <t>비피다발효용해물 · 사카로미세스발효여과물</t>
         </is>
       </c>
     </row>
@@ -11570,12 +11570,12 @@
       </c>
       <c r="E34" s="10" t="inlineStr">
         <is>
-          <t>허브의 여왕, / 진정, 재생, 항균</t>
+          <t>허브의 여왕 · 진정, 재생, 항균</t>
         </is>
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
-          <t>베베보 / 블렌딩오일</t>
+          <t>베베보 · 블렌딩오일</t>
         </is>
       </c>
     </row>
@@ -11717,10 +11717,10 @@
       </c>
       <c r="E43" s="18" t="inlineStr">
         <is>
-          <t>슈퍼시카4, 덱스판테놀, / 내추럴 바세린 / 함유 / 강력 보습&amp;진정</t>
-        </is>
-      </c>
-      <c r="F43" s="18" t="n"/>
+          <t>슈퍼시카4, 덱스판테놀 · 내추럴 바세린 · 함유 · 강력 보습&amp;진정</t>
+        </is>
+      </c>
+      <c r="F43" s="18" t="inlineStr"/>
     </row>
     <row r="44" ht="16" customHeight="1">
       <c r="A44" s="18" t="inlineStr">
@@ -11782,7 +11782,7 @@
       </c>
       <c r="F45" s="18" t="inlineStr">
         <is>
-          <t>스쿠알란, / 보르피린</t>
+          <t>스쿠알란 · 보르피린</t>
         </is>
       </c>
     </row>
@@ -11814,7 +11814,7 @@
       </c>
       <c r="F46" s="18" t="inlineStr">
         <is>
-          <t>만다린, / 스윗오렌지에센셜오일</t>
+          <t>만다린 · 스윗오렌지에센셜오일</t>
         </is>
       </c>
     </row>
@@ -11960,7 +11960,7 @@
       </c>
       <c r="E55" s="10" t="inlineStr">
         <is>
-          <t>미백 주름 개선 기능성 / 나이아신아미이드, 아데노신, 마데카소사이드, 아시아티코사이드, 마데카식애씨드, 아시아틱애씨드, 덱스판테놀 등</t>
+          <t>미백 주름 개선 기능성 · 나이아신아미이드, 아데노신, 마데카소사이드, 아시아티코사이드, 마데카식애씨드, 아시아틱애씨드, 덱스판테놀 등</t>
         </is>
       </c>
       <c r="F55" s="10" t="inlineStr">
@@ -11995,7 +11995,7 @@
           <t>실제 피부 각질층 아미노산 구성과 유사한 17가지 아미노산, 보습·톤오버 유도·재생·톤업</t>
         </is>
       </c>
-      <c r="F56" s="10" t="n"/>
+      <c r="F56" s="10" t="inlineStr"/>
     </row>
     <row r="57" ht="14" customHeight="1">
       <c r="A57" s="13" t="inlineStr">
@@ -12138,7 +12138,7 @@
       </c>
       <c r="E65" s="18" t="inlineStr">
         <is>
-          <t>병풀 핵심 성분 4가지, 덱스 판테놀 함유, / 미백&amp; 주름 이중 기능성</t>
+          <t>병풀 핵심 성분 4가지, 덱스 판테놀 함유 · 미백&amp; 주름 이중 기능성</t>
         </is>
       </c>
       <c r="F65" s="18" t="inlineStr">
@@ -12170,7 +12170,7 @@
       </c>
       <c r="E66" s="18" t="inlineStr">
         <is>
-          <t>EGF, FGF, IGF, TGF / 복합 펩타이드</t>
+          <t>EGF, FGF, IGF, TGF · 복합 펩타이드</t>
         </is>
       </c>
       <c r="F66" s="18" t="inlineStr">
@@ -12207,7 +12207,7 @@
       </c>
       <c r="F67" s="18" t="inlineStr">
         <is>
-          <t>원하는 / 에센셜오일</t>
+          <t>원하는 · 에센셜오일</t>
         </is>
       </c>
     </row>
@@ -12357,7 +12357,7 @@
       </c>
       <c r="E76" s="10" t="inlineStr">
         <is>
-          <t>병풀 핵심성분 4가지 함유, / 보습, 재생효과 덱스판테놀 함유</t>
+          <t>병풀 핵심성분 4가지 함유 · 보습, 재생효과 덱스판테놀 함유</t>
         </is>
       </c>
       <c r="F76" s="10" t="inlineStr">
@@ -12421,12 +12421,12 @@
       </c>
       <c r="E78" s="10" t="inlineStr">
         <is>
-          <t>네롤리, 프랑킨센스, 버가못FCF / 복합 블렌딩오일</t>
+          <t>네롤리, 프랑킨센스, 버가못FCF · 복합 블렌딩오일</t>
         </is>
       </c>
       <c r="F78" s="10" t="inlineStr">
         <is>
-          <t>원하는 / 에센셜오일</t>
+          <t>원하는 · 에센셜오일</t>
         </is>
       </c>
     </row>
@@ -12569,7 +12569,7 @@
       </c>
       <c r="E87" s="18" t="inlineStr">
         <is>
-          <t>미백 주름 개선 기능성 / 나이아신아미이드, 아데노신, 마데카소사이드, 아시아티코사이드, 마데카식애씨드, 아시아틱애씨드, 덱스판테놀 등</t>
+          <t>미백 주름 개선 기능성 · 나이아신아미이드, 아데노신, 마데카소사이드, 아시아티코사이드, 마데카식애씨드, 아시아틱애씨드, 덱스판테놀 등</t>
         </is>
       </c>
       <c r="F87" s="18" t="inlineStr">
@@ -12606,7 +12606,7 @@
       </c>
       <c r="F88" s="18" t="inlineStr">
         <is>
-          <t>아카시아, / 마린콜라겐</t>
+          <t>아카시아 · 마린콜라겐</t>
         </is>
       </c>
     </row>
@@ -12737,7 +12737,7 @@
         </is>
       </c>
     </row>
-    <row r="97" ht="48" customHeight="1">
+    <row r="97" ht="32" customHeight="1">
       <c r="A97" s="10" t="inlineStr">
         <is>
           <t>시카 판테놀 수딩젤 베이스</t>
@@ -12760,10 +12760,10 @@
       </c>
       <c r="E97" s="10" t="inlineStr">
         <is>
-          <t>슈퍼시카4, 덱스판테놀, / 비타민B5,B3, 오렌지블라썸워터 함유</t>
-        </is>
-      </c>
-      <c r="F97" s="10" t="n"/>
+          <t>슈퍼시카4, 덱스판테놀 · 비타민B5,B3, 오렌지블라썸워터 함유</t>
+        </is>
+      </c>
+      <c r="F97" s="10" t="inlineStr"/>
     </row>
     <row r="98" ht="16" customHeight="1">
       <c r="A98" s="10" t="inlineStr">
@@ -12820,12 +12820,12 @@
       </c>
       <c r="E99" s="10" t="inlineStr">
         <is>
-          <t>진정, 고농축 허브오일, / 아로마테라피 / 생략 가능</t>
+          <t>진정, 고농축 허브오일 · 아로마테라피 · 생략 가능</t>
         </is>
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
-          <t>원하는 / 에센셜오일</t>
+          <t>원하는 · 에센셜오일</t>
         </is>
       </c>
     </row>
@@ -12961,10 +12961,10 @@
       </c>
       <c r="E108" s="18" t="inlineStr">
         <is>
-          <t>슈퍼시카4, 덱스판테놀, / 내추럴 바세린 / 함유 / 강력 보습&amp;진정</t>
-        </is>
-      </c>
-      <c r="F108" s="18" t="n"/>
+          <t>슈퍼시카4, 덱스판테놀 · 내추럴 바세린 · 함유 · 강력 보습&amp;진정</t>
+        </is>
+      </c>
+      <c r="F108" s="18" t="inlineStr"/>
     </row>
     <row r="109" ht="32" customHeight="1">
       <c r="A109" s="18" t="inlineStr">
@@ -12989,12 +12989,12 @@
       </c>
       <c r="E109" s="18" t="inlineStr">
         <is>
-          <t>보습, / 코포아수버터 리포좀</t>
+          <t>보습 · 코포아수버터 리포좀</t>
         </is>
       </c>
       <c r="F109" s="18" t="inlineStr">
         <is>
-          <t>워터 아르간, / 워터 호호바</t>
+          <t>워터 아르간 · 워터 호호바</t>
         </is>
       </c>
     </row>
@@ -13026,7 +13026,7 @@
       </c>
       <c r="F110" s="18" t="inlineStr">
         <is>
-          <t>스쿠알란, / 보르피린</t>
+          <t>스쿠알란 · 보르피린</t>
         </is>
       </c>
     </row>
@@ -13053,12 +13053,12 @@
       </c>
       <c r="E111" s="18" t="inlineStr">
         <is>
-          <t>네롤리, 버가못FCF 일링일랑, 프랑킨센스, / 복합 블렌딩오일</t>
+          <t>네롤리, 버가못FCF 일링일랑, 프랑킨센스 · 복합 블렌딩오일</t>
         </is>
       </c>
       <c r="F111" s="18" t="inlineStr">
         <is>
-          <t>버가못에센셜오일, / 레몬쥬스블렌딩오일</t>
+          <t>버가못에센셜오일 · 레몬쥬스블렌딩오일</t>
         </is>
       </c>
     </row>
@@ -13209,7 +13209,7 @@
       </c>
       <c r="E120" s="10" t="inlineStr">
         <is>
-          <t>미백 주름 개선 기능성 / 나이아신아미이드, 아데노신, 마데카소사이드, 아시아티코사이드, 마데카식애씨드, 아시아틱애씨드, 덱스판테놀 등</t>
+          <t>미백 주름 개선 기능성 · 나이아신아미이드, 아데노신, 마데카소사이드, 아시아티코사이드, 마데카식애씨드, 아시아틱애씨드, 덱스판테놀 등</t>
         </is>
       </c>
       <c r="F120" s="10" t="inlineStr">
@@ -13273,7 +13273,7 @@
       </c>
       <c r="E122" s="10" t="inlineStr">
         <is>
-          <t>병풀 핵심성분 4가지 함유, 보습, 재생효과 덱스판테놀 함유/td&gt;</t>
+          <t>병풀 핵심성분 4가지 함유, 보습, 재생효과 덱스판테놀 함유 · td&gt;</t>
         </is>
       </c>
       <c r="F122" s="10" t="inlineStr">
@@ -13429,7 +13429,7 @@
       </c>
       <c r="E131" s="18" t="inlineStr">
         <is>
-          <t>미백 주름 개선 기능성 / 나이아신아미이드, 아데노신, 마데카소사이드, 아시아티코사이드, 마데카식애씨드, 아시아틱애씨드, 덱스판테놀 등</t>
+          <t>미백 주름 개선 기능성 · 나이아신아미이드, 아데노신, 마데카소사이드, 아시아티코사이드, 마데카식애씨드, 아시아틱애씨드, 덱스판테놀 등</t>
         </is>
       </c>
       <c r="F131" s="18" t="inlineStr">
@@ -13493,7 +13493,7 @@
       </c>
       <c r="E133" s="18" t="inlineStr">
         <is>
-          <t>병풀 핵심성분 4가지 함유, 보습, 재생효과 덱스판테놀 함유/td&gt;</t>
+          <t>병풀 핵심성분 4가지 함유, 보습, 재생효과 덱스판테놀 함유 · td&gt;</t>
         </is>
       </c>
       <c r="F133" s="18" t="inlineStr">
@@ -13636,7 +13636,7 @@
         </is>
       </c>
     </row>
-    <row r="142" ht="48" customHeight="1">
+    <row r="142" ht="32" customHeight="1">
       <c r="A142" s="10" t="inlineStr">
         <is>
           <t>시카 판테놀 수딩젤 베이스</t>
@@ -13659,10 +13659,10 @@
       </c>
       <c r="E142" s="10" t="inlineStr">
         <is>
-          <t>슈퍼시카4, 덱스판테놀, / 비타민B5,B3, 오렌지블라썸워터 함유</t>
-        </is>
-      </c>
-      <c r="F142" s="10" t="n"/>
+          <t>슈퍼시카4, 덱스판테놀 · 비타민B5,B3, 오렌지블라썸워터 함유</t>
+        </is>
+      </c>
+      <c r="F142" s="10" t="inlineStr"/>
     </row>
     <row r="143" ht="48" customHeight="1">
       <c r="A143" s="10" t="inlineStr">
@@ -13687,7 +13687,7 @@
       </c>
       <c r="E143" s="10" t="inlineStr">
         <is>
-          <t>누룩(천연효모)발효여과물, / 보습, 탄력, / 미네럴 영양 공급</t>
+          <t>누룩(천연효모)발효여과물 · 보습, 탄력 · 미네럴 영양 공급</t>
         </is>
       </c>
       <c r="F143" s="10" t="inlineStr">
@@ -13719,7 +13719,7 @@
       </c>
       <c r="E144" s="10" t="inlineStr">
         <is>
-          <t>아로마 테라피효과, / 생략 가능</t>
+          <t>아로마 테라피효과 · 생략 가능</t>
         </is>
       </c>
       <c r="F144" s="10" t="inlineStr">
@@ -13860,10 +13860,10 @@
       </c>
       <c r="E153" s="18" t="inlineStr">
         <is>
-          <t>슈퍼시카4, 덱스판테놀, / 내추럴 바세린 / 함유 / 강력 보습&amp;진정</t>
-        </is>
-      </c>
-      <c r="F153" s="18" t="n"/>
+          <t>슈퍼시카4, 덱스판테놀 · 내추럴 바세린 · 함유 · 강력 보습&amp;진정</t>
+        </is>
+      </c>
+      <c r="F153" s="18" t="inlineStr"/>
     </row>
     <row r="154" ht="32" customHeight="1">
       <c r="A154" s="18" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="F154" s="18" t="inlineStr">
         <is>
-          <t>스쿠알란, / 보르피린</t>
+          <t>스쿠알란 · 보르피린</t>
         </is>
       </c>
     </row>
@@ -13920,12 +13920,12 @@
       </c>
       <c r="E155" s="18" t="inlineStr">
         <is>
-          <t>로즈앱솔루트EO, 로즈제라늄EO, / 로즈우드EO, 프랑킨센스EO / 블렌딩오일</t>
+          <t>로즈앱솔루트EO, 로즈제라늄EO · 로즈우드EO, 프랑킨센스EO · 블렌딩오일</t>
         </is>
       </c>
       <c r="F155" s="18" t="inlineStr">
         <is>
-          <t>로즈제라늄, / 로즈우드에센셜오일</t>
+          <t>로즈제라늄 · 로즈우드에센셜오일</t>
         </is>
       </c>
     </row>
@@ -14074,7 +14074,7 @@
       </c>
       <c r="E164" s="10" t="inlineStr">
         <is>
-          <t>크기가 다른 11가지 히아루론산, / 수분 레이어링으로 피부 겉과 속까지 수분 전달 / 수분충전부터 피부결까지 한 번에 해결 / 단독 사용 가능</t>
+          <t>크기가 다른 11가지 히아루론산 · 수분 레이어링으로 피부 겉과 속까지 수분 전달 · 수분충전부터 피부결까지 한 번에 해결 · 단독 사용 가능</t>
         </is>
       </c>
       <c r="F164" s="10" t="inlineStr">
@@ -14106,10 +14106,10 @@
       </c>
       <c r="E165" s="10" t="inlineStr">
         <is>
-          <t>피부톤 개선 / (식약처 미백 기능성 원료 비타민나무열매추출물, / 유자추출물, 오미자추출물 등)</t>
-        </is>
-      </c>
-      <c r="F165" s="10" t="n"/>
+          <t>피부톤 개선 · (식약처 미백 기능성 원료 비타민나무열매추출물 · 유자추출물, 오미자추출물 등)</t>
+        </is>
+      </c>
+      <c r="F165" s="10" t="inlineStr"/>
     </row>
     <row r="166" ht="64" customHeight="1">
       <c r="A166" s="10" t="inlineStr">
@@ -14134,10 +14134,10 @@
       </c>
       <c r="E166" s="10" t="inlineStr">
         <is>
-          <t>주름 개선 / (식약처 주름개선인증 원료 아데노신, 동백꽃추출물, / 히비스커스꽃추출물, 동백꽃추출물, 샤프란꽃추출물 등)</t>
-        </is>
-      </c>
-      <c r="F166" s="10" t="n"/>
+          <t>주름 개선 · (식약처 주름개선인증 원료 아데노신, 동백꽃추출물 · 히비스커스꽃추출물, 동백꽃추출물, 샤프란꽃추출물 등)</t>
+        </is>
+      </c>
+      <c r="F166" s="10" t="inlineStr"/>
     </row>
     <row r="167" ht="32" customHeight="1">
       <c r="A167" s="10" t="inlineStr">
@@ -14162,10 +14162,10 @@
       </c>
       <c r="E167" s="10" t="inlineStr">
         <is>
-          <t>피부 진정 / (병풀추출물, 녹차추출물, 로즈마리잎추출물 등)</t>
-        </is>
-      </c>
-      <c r="F167" s="10" t="n"/>
+          <t>피부 진정 · (병풀추출물, 녹차추출물, 로즈마리잎추출물 등)</t>
+        </is>
+      </c>
+      <c r="F167" s="10" t="inlineStr"/>
     </row>
     <row r="168" ht="14" customHeight="1">
       <c r="A168" s="13" t="inlineStr">
@@ -14305,10 +14305,10 @@
       </c>
       <c r="E176" s="18" t="inlineStr">
         <is>
-          <t>피부장벽강화, 보습, 미백 / 고기능성 크림베이스</t>
-        </is>
-      </c>
-      <c r="F176" s="18" t="n"/>
+          <t>피부장벽강화, 보습, 미백 · 고기능성 크림베이스</t>
+        </is>
+      </c>
+      <c r="F176" s="18" t="inlineStr"/>
     </row>
     <row r="177" ht="48" customHeight="1">
       <c r="A177" s="18" t="inlineStr">
@@ -14333,12 +14333,12 @@
       </c>
       <c r="E177" s="18" t="inlineStr">
         <is>
-          <t>상피 재생관여, / 농도 1ppm 또는 10ppm 중 택</t>
+          <t>상피 재생관여 · 농도 1ppm 또는 10ppm 중 택</t>
         </is>
       </c>
       <c r="F177" s="18" t="inlineStr">
         <is>
-          <t>FGF10/1ppm,아세틸헥사펩타이드, 쿠퍼펩타이드 등</t>
+          <t>FGF10 · 1ppm,아세틸헥사펩타이드, 쿠퍼펩타이드 등</t>
         </is>
       </c>
     </row>
@@ -14370,7 +14370,7 @@
       </c>
       <c r="F178" s="18" t="inlineStr">
         <is>
-          <t>원하는 / 에센셜오일</t>
+          <t>원하는 · 에센셜오일</t>
         </is>
       </c>
     </row>
@@ -14521,7 +14521,7 @@
           <t>향수&amp; 룸스프레이 전용베이스, 식물성 에탄올, 정제수, 가용화제 등 향 함량이 높아도 분리되지 않도록.</t>
         </is>
       </c>
-      <c r="F187" s="10" t="n"/>
+      <c r="F187" s="10" t="inlineStr"/>
     </row>
     <row r="188" ht="128" customHeight="1">
       <c r="A188" s="10" t="inlineStr">
@@ -14546,12 +14546,12 @@
       </c>
       <c r="E188" s="10" t="inlineStr">
         <is>
-          <t>8% , 프탈레이트프리. / 취향에 따라 양조절해서 사용가능</t>
+          <t>8% , 프탈레이트프리. · 취향에 따라 양조절해서 사용가능</t>
         </is>
       </c>
       <c r="F188" s="10" t="inlineStr">
         <is>
-          <t>화이트 머스크, / 로즈듀에, / 잉글리쉬 페어 &amp; 프리지아 / 화이트쟈스민&amp;민트 / 잉글리쉬페어&amp;프리지아 / 라임 바질&amp; 만다린 그린티 시트러스</t>
+          <t>화이트 머스크 · 로즈듀에 · 잉글리쉬 페어 &amp; 프리지아 · 화이트쟈스민&amp;민트 · 잉글리쉬페어&amp;프리지아 · 라임 바질&amp; 만다린 그린티 시트러스</t>
         </is>
       </c>
     </row>
@@ -14685,7 +14685,7 @@
           <t>향수&amp; 룸스프레이 전용베이스, 식물성 에탄올, 정제수, 가용화제 등 향 함량이 높아도 분리되지 않도록.</t>
         </is>
       </c>
-      <c r="F197" s="18" t="n"/>
+      <c r="F197" s="18" t="inlineStr"/>
     </row>
     <row r="198" ht="48" customHeight="1">
       <c r="A198" s="18" t="inlineStr">
@@ -14710,7 +14710,7 @@
       </c>
       <c r="E198" s="18" t="inlineStr">
         <is>
-          <t>~10% 함량 , 프탈레이트 프리. / 취향에 따라 양조절해서 사용 가능</t>
+          <t>10% 함량 , 프탈레이트 프리. · 취향에 따라 양조절해서 사용 가능</t>
         </is>
       </c>
       <c r="F198" s="18" t="inlineStr">
@@ -14859,7 +14859,7 @@
           <t>보습과 미백동시에, 미백기능성베이스, 유기농 알로에베라, 호호바오일, 코포아수버터 리포좀으로 보습 지속력. 히아루론산, 알란토인 등</t>
         </is>
       </c>
-      <c r="F207" s="10" t="n"/>
+      <c r="F207" s="10" t="inlineStr"/>
     </row>
     <row r="208" ht="48" customHeight="1">
       <c r="A208" s="10" t="inlineStr">
@@ -14884,7 +14884,7 @@
       </c>
       <c r="E208" s="10" t="inlineStr">
         <is>
-          <t>장미 줄기세포 추출물은 높은 안정성, 생체친화성을 바탕으로 항산화/염원료</t>
+          <t>장미 줄기세포 추출물은 높은 안정성, 생체친화성을 바탕으로 항산화 · 염원료</t>
         </is>
       </c>
       <c r="F208" s="10" t="inlineStr">
@@ -14921,7 +14921,7 @@
       </c>
       <c r="F209" s="10" t="inlineStr">
         <is>
-          <t>탄력을 원하면 / EGF, FGF 등 대체</t>
+          <t>탄력을 원하면 · EGF, FGF 등 대체</t>
         </is>
       </c>
     </row>
@@ -15104,10 +15104,10 @@
       </c>
       <c r="E219" s="18" t="inlineStr">
         <is>
-          <t>유기농 알로에베라, / 미백인증 원료 나이아신아마이드, / 알란토인, 히아루론산, / 코포아수버터, 호호바오일 / 끈적임없이, 촉촉함이 오래.</t>
-        </is>
-      </c>
-      <c r="F219" s="18" t="n"/>
+          <t>유기농 알로에베라 · 미백인증 원료 나이아신아마이드 · 알란토인, 히아루론산 · 코포아수버터, 호호바오일 · 끈적임없이, 촉촉함이 오래.</t>
+        </is>
+      </c>
+      <c r="F219" s="18" t="inlineStr"/>
     </row>
     <row r="220" ht="48" customHeight="1">
       <c r="A220" s="18" t="inlineStr">
@@ -15132,10 +15132,10 @@
       </c>
       <c r="E220" s="18" t="inlineStr">
         <is>
-          <t>베트남산 해초, / 모양이 포도같아 바다포도, / 풍부한 미네럴, 후코이단 등 함유</t>
-        </is>
-      </c>
-      <c r="F220" s="18" t="n"/>
+          <t>베트남산 해초 · 모양이 포도같아 바다포도 · 풍부한 미네럴, 후코이단 등 함유</t>
+        </is>
+      </c>
+      <c r="F220" s="18" t="inlineStr"/>
     </row>
     <row r="221" ht="48" customHeight="1">
       <c r="A221" s="18" t="inlineStr">
@@ -15160,7 +15160,7 @@
       </c>
       <c r="E221" s="18" t="inlineStr">
         <is>
-          <t>깨끗한 스카이 블루색 / 아미노산나열시 구리(Cu)을 함유, / 피부의 활력을 증가</t>
+          <t>깨끗한 스카이 블루색 · 아미노산나열시 구리(Cu)을 함유 · 피부의 활력을 증가</t>
         </is>
       </c>
       <c r="F221" s="18" t="inlineStr">
@@ -15192,7 +15192,7 @@
       </c>
       <c r="E222" s="18" t="inlineStr">
         <is>
-          <t>장미향이 나는 제라늄오일, / 균형의 오일, 피지 균형.</t>
+          <t>장미향이 나는 제라늄오일 · 균형의 오일, 피지 균형.</t>
         </is>
       </c>
       <c r="F222" s="18" t="inlineStr">
@@ -15350,10 +15350,10 @@
       </c>
       <c r="E231" s="10" t="inlineStr">
         <is>
-          <t>보습과 미백동시에, 미백기능성 베이스, / 유기농 알로에베라, 호호바오일, 코포아수버터 리포좀으로 보습 지속력. 히아루론산, 알란토인 등 .</t>
-        </is>
-      </c>
-      <c r="F231" s="10" t="n"/>
+          <t>보습과 미백동시에, 미백기능성 베이스 · 유기농 알로에베라, 호호바오일, 코포아수버터 리포좀으로 보습 지속력. 히아루론산, 알란토인 등 .</t>
+        </is>
+      </c>
+      <c r="F231" s="10" t="inlineStr"/>
     </row>
     <row r="232" ht="96" customHeight="1">
       <c r="A232" s="10" t="inlineStr">
@@ -15410,7 +15410,7 @@
       </c>
       <c r="E233" s="10" t="inlineStr">
         <is>
-          <t>양조장 누룩의 본질이 사카로 미세스입니다. / 사카로마세스 안에는 수많은 발효 효모가 들어있고 그중에 하나가 갈락토미세스입니다..</t>
+          <t>양조장 누룩의 본질이 사카로 미세스입니다. · 사카로마세스 안에는 수많은 발효 효모가 들어있고 그중에 하나가 갈락토미세스입니다..</t>
         </is>
       </c>
       <c r="F233" s="10" t="inlineStr">
@@ -15442,7 +15442,7 @@
       </c>
       <c r="E234" s="10" t="inlineStr">
         <is>
-          <t>오렌지꽃 오일,</t>
+          <t>오렌지꽃 오일</t>
         </is>
       </c>
       <c r="F234" s="10" t="inlineStr">
@@ -15597,10 +15597,10 @@
       </c>
       <c r="E243" s="18" t="inlineStr">
         <is>
-          <t>미백, 주름 개선 2중 기능성, / 아르간 가득 크림 베이스</t>
-        </is>
-      </c>
-      <c r="F243" s="18" t="n"/>
+          <t>미백, 주름 개선 2중 기능성 · 아르간 가득 크림 베이스</t>
+        </is>
+      </c>
+      <c r="F243" s="18" t="inlineStr"/>
     </row>
     <row r="244" ht="48" customHeight="1">
       <c r="A244" s="18" t="inlineStr">
@@ -15625,12 +15625,12 @@
       </c>
       <c r="E244" s="18" t="inlineStr">
         <is>
-          <t>EGF, FGF, IGF, TGF / 복합 펩타이드</t>
+          <t>EGF, FGF, IGF, TGF · 복합 펩타이드</t>
         </is>
       </c>
       <c r="F244" s="18" t="inlineStr">
         <is>
-          <t>아세틸헥사, / 씨네이크펩타이드, 화이트펩타이드 등</t>
+          <t>아세틸헥사 · 씨네이크펩타이드, 화이트펩타이드 등</t>
         </is>
       </c>
     </row>
@@ -15657,12 +15657,12 @@
       </c>
       <c r="E245" s="18" t="inlineStr">
         <is>
-          <t>오렌지꽃 에센셜오일, / 생기</t>
+          <t>오렌지꽃 에센셜오일 · 생기</t>
         </is>
       </c>
       <c r="F245" s="18" t="inlineStr">
         <is>
-          <t>원하는 / 에센셜오일</t>
+          <t>원하는 · 에센셜오일</t>
         </is>
       </c>
     </row>
@@ -15808,7 +15808,7 @@
           <t>향수전용베이스</t>
         </is>
       </c>
-      <c r="F254" s="10" t="n"/>
+      <c r="F254" s="10" t="inlineStr"/>
     </row>
     <row r="255" ht="32" customHeight="1">
       <c r="A255" s="10" t="inlineStr">
@@ -15829,7 +15829,7 @@
       </c>
       <c r="E255" s="10" t="inlineStr">
         <is>
-          <t>프탈레이트 프리, / 은은한 장미향</t>
+          <t>프탈레이트 프리 · 은은한 장미향</t>
         </is>
       </c>
       <c r="F255" s="10" t="inlineStr">
@@ -15857,7 +15857,7 @@
       </c>
       <c r="E256" s="10" t="inlineStr">
         <is>
-          <t>아로마테라피 / 여드름-티트리, / 바디 용도별 추천오일 / -쿨링 :페파민트, / -다이어트 : 레몬+자몽오일 / -이완 : 라벤더오일 등</t>
+          <t>아로마테라피 · 여드름-티트리 · 바디 용도별 추천오일 · 쿨링 :페파민트 · 다이어트 : 레몬+자몽오일 · 이완 : 라벤더오일 등</t>
         </is>
       </c>
       <c r="F256" s="10" t="inlineStr">
@@ -16026,7 +16026,7 @@
       </c>
       <c r="E265" s="18" t="inlineStr">
         <is>
-          <t>장미수, 수분공급 / 수분흡수 후 코인마스크팩이 펼쳐짐.</t>
+          <t>장미수, 수분공급 · 수분흡수 후 코인마스크팩이 펼쳐짐.</t>
         </is>
       </c>
       <c r="F265" s="18" t="inlineStr">
@@ -16202,7 +16202,7 @@
       </c>
       <c r="E275" s="10" t="inlineStr">
         <is>
-          <t>가볍지만 촉~촉-한 보습, / 끈적임 없음 / , 9가지 식물성오일 블렌딩, / 로즈힙, 유기농 호호바, 스쿠알란, 발효동백, 아르간, 녹차, 카프릴릭/카프릭 트리글리세라이드, 비타민E</t>
+          <t>가볍지만 촉~촉-한 보습 · 끈적임 없음 · 9가지 식물성오일 블렌딩 · 로즈힙, 유기농 호호바, 스쿠알란, 발효동백, 아르간, 녹차, 카프릴릭 · 카프릭 트리글리세라이드, 비타민E</t>
         </is>
       </c>
       <c r="F275" s="10" t="inlineStr">
@@ -16234,7 +16234,7 @@
       </c>
       <c r="E276" s="10" t="inlineStr">
         <is>
-          <t>네롤리, 프랑킨센스 / 등 블렌딩 / 아로마테라피효과</t>
+          <t>네롤리, 프랑킨센스 · 등 블렌딩 · 아로마테라피효과</t>
         </is>
       </c>
       <c r="F276" s="10" t="inlineStr">
@@ -16422,10 +16422,10 @@
       </c>
       <c r="E286" s="18" t="inlineStr">
         <is>
-          <t>보습과 미백동시에, / 미백기능성 수분크림베이스</t>
-        </is>
-      </c>
-      <c r="F286" s="18" t="n"/>
+          <t>보습과 미백동시에 · 미백기능성 수분크림베이스</t>
+        </is>
+      </c>
+      <c r="F286" s="18" t="inlineStr"/>
     </row>
     <row r="287" ht="80" customHeight="1">
       <c r="A287" s="18" t="inlineStr">
@@ -16482,12 +16482,12 @@
       </c>
       <c r="E288" s="18" t="inlineStr">
         <is>
-          <t>감귤류 껍질, 상큼. / 진정, 모든 피부</t>
+          <t>감귤류 껍질, 상큼. · 진정, 모든 피부</t>
         </is>
       </c>
       <c r="F288" s="18" t="inlineStr">
         <is>
-          <t>원하는 / 에센셜오일</t>
+          <t>원하는 · 에센셜오일</t>
         </is>
       </c>
     </row>
@@ -16623,10 +16623,10 @@
       </c>
       <c r="E297" s="10" t="inlineStr">
         <is>
-          <t>기능성 미백, 보습, / 수분크림베이스</t>
-        </is>
-      </c>
-      <c r="F297" s="10" t="n"/>
+          <t>기능성 미백, 보습 · 수분크림베이스</t>
+        </is>
+      </c>
+      <c r="F297" s="10" t="inlineStr"/>
     </row>
     <row r="298" ht="80" customHeight="1">
       <c r="A298" s="10" t="inlineStr">
@@ -16651,12 +16651,12 @@
       </c>
       <c r="E298" s="10" t="inlineStr">
         <is>
-          <t>양조장 누룩의 본질이 / 사카로 미세스, / 사카로마세스 안에는 수많은 / 발효 효모가 들어있고 / 그중에 하나가 갈락토미세스. / 풍부한 영양, 깊은보습</t>
+          <t>양조장 누룩의 본질이 · 사카로 미세스 · 사카로마세스 안에는 수많은 · 발효 효모가 들어있고 · 그중에 하나가 갈락토미세스. · 풍부한 영양, 깊은보습</t>
         </is>
       </c>
       <c r="F298" s="10" t="inlineStr">
         <is>
-          <t>갈락토,비피다 / 발효여과물</t>
+          <t>갈락토,비피다 · 발효여과물</t>
         </is>
       </c>
     </row>
@@ -16720,7 +16720,7 @@
       </c>
       <c r="F300" s="10" t="inlineStr">
         <is>
-          <t>1,2-헥산디올1g / (네롤리워터의 양을 48g으로 줄여주세요.)</t>
+          <t>1,2-헥산디올1g · (네롤리워터의 양을 48g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -16747,12 +16747,12 @@
       </c>
       <c r="E301" s="10" t="inlineStr">
         <is>
-          <t>감귤류껍질, 상큼, / 진정, 모든피부</t>
+          <t>감귤류껍질, 상큼 · 진정, 모든피부</t>
         </is>
       </c>
       <c r="F301" s="10" t="inlineStr">
         <is>
-          <t>원하는 / 에센셜오일</t>
+          <t>원하는 · 에센셜오일</t>
         </is>
       </c>
     </row>
@@ -16891,10 +16891,10 @@
       </c>
       <c r="E310" s="18" t="inlineStr">
         <is>
-          <t>유기적 자외선 차단성분으로 / 만들어짐. SPF 50, PA+++</t>
-        </is>
-      </c>
-      <c r="F310" s="18" t="n"/>
+          <t>유기적 자외선 차단성분으로 · 만들어짐. SPF 50, PA+++</t>
+        </is>
+      </c>
+      <c r="F310" s="18" t="inlineStr"/>
     </row>
     <row r="311" ht="32" customHeight="1">
       <c r="A311" s="18" t="inlineStr">
@@ -16919,7 +16919,7 @@
       </c>
       <c r="E311" s="18" t="inlineStr">
         <is>
-          <t>식약처 인증 미백원료. / 진정, 미백. 0.5~1% 사용</t>
+          <t>식약처 인증 미백원료. · 진정, 미백. 0.5~1% 사용</t>
         </is>
       </c>
       <c r="F311" s="18" t="inlineStr">
@@ -17109,10 +17109,10 @@
       </c>
       <c r="E321" s="10" t="inlineStr">
         <is>
-          <t>투명, / 유기적 자외선 차단성분으로 / 만들어짐. SPF 50, PA+++</t>
-        </is>
-      </c>
-      <c r="F321" s="10" t="n"/>
+          <t>투명 · 유기적 자외선 차단성분으로 · 만들어짐. SPF 50, PA+++</t>
+        </is>
+      </c>
+      <c r="F321" s="10" t="inlineStr"/>
     </row>
     <row r="322" ht="16" customHeight="1">
       <c r="A322" s="10" t="inlineStr">
@@ -17274,7 +17274,7 @@
       </c>
       <c r="E331" s="18" t="inlineStr">
         <is>
-          <t>항산화, 비타민 풍부, / 피부장벽 튼튼, 환한 피부</t>
+          <t>항산화, 비타민 풍부 · 피부장벽 튼튼, 환한 피부</t>
         </is>
       </c>
       <c r="F331" s="18" t="inlineStr">
@@ -17306,10 +17306,10 @@
       </c>
       <c r="E332" s="18" t="inlineStr">
         <is>
-          <t>식약처 미백인증 수분크림, / 히아루론산, 호호바오일, / 알란토인 등 함유</t>
-        </is>
-      </c>
-      <c r="F332" s="18" t="n"/>
+          <t>식약처 미백인증 수분크림 · 히아루론산, 호호바오일 · 알란토인 등 함유</t>
+        </is>
+      </c>
+      <c r="F332" s="18" t="inlineStr"/>
     </row>
     <row r="333" ht="32" customHeight="1">
       <c r="A333" s="18" t="inlineStr">
@@ -17334,12 +17334,12 @@
       </c>
       <c r="E333" s="18" t="inlineStr">
         <is>
-          <t>표피, 진피 4가지 재생인자 / 더 탄탄, 촘촘하게</t>
+          <t>표피, 진피 4가지 재생인자 · 더 탄탄, 촘촘하게</t>
         </is>
       </c>
       <c r="F333" s="18" t="inlineStr">
         <is>
-          <t>원하는 펩타이드나 / 기능성 추출물</t>
+          <t>원하는 펩타이드나 · 기능성 추출물</t>
         </is>
       </c>
     </row>
@@ -17401,7 +17401,7 @@
           <t>진한 초록색, 트러블성 피부에 탁월</t>
         </is>
       </c>
-      <c r="F335" s="18" t="n"/>
+      <c r="F335" s="18" t="inlineStr"/>
     </row>
     <row r="336" ht="14" customHeight="1">
       <c r="A336" s="13" t="inlineStr">
@@ -17561,7 +17561,7 @@
         </is>
       </c>
     </row>
-    <row r="345" ht="48" customHeight="1">
+    <row r="345" ht="32" customHeight="1">
       <c r="A345" s="10" t="inlineStr">
         <is>
           <t>아르간 가득한 / 크림베이스</t>
@@ -17584,10 +17584,10 @@
       </c>
       <c r="E345" s="10" t="inlineStr">
         <is>
-          <t>유기농 아르간, 유기농 코포아수버터 등 보습과 미백을 동시에,</t>
-        </is>
-      </c>
-      <c r="F345" s="10" t="n"/>
+          <t>유기농 아르간, 유기농 코포아수버터 등 보습과 미백을 동시에</t>
+        </is>
+      </c>
+      <c r="F345" s="10" t="inlineStr"/>
     </row>
     <row r="346" ht="80" customHeight="1">
       <c r="A346" s="10" t="inlineStr">
@@ -17621,7 +17621,7 @@
         </is>
       </c>
     </row>
-    <row r="347" ht="96" customHeight="1">
+    <row r="347" ht="80" customHeight="1">
       <c r="A347" s="10" t="inlineStr">
         <is>
           <t>갈락토미세스 / 발효여과물</t>
@@ -17644,7 +17644,7 @@
       </c>
       <c r="E347" s="10" t="inlineStr">
         <is>
-          <t>술을 빚을 때 사용하는 누룩을 발효시켜 얻음. / 피부에 아미노산과 미네럴 등 풍부한 영양을 공급, 유수분 조절, / 피부장벽강화 및 칙칙한 피부 톤을 개선</t>
+          <t>술을 빚을 때 사용하는 누룩을 발효시켜 얻음. · 피부에 아미노산과 미네럴 등 풍부한 영양을 공급, 유수분 조절 · 피부장벽강화 및 칙칙한 피부 톤을 개선</t>
         </is>
       </c>
       <c r="F347" s="10" t="inlineStr">
@@ -17674,8 +17674,8 @@
           <t>기타</t>
         </is>
       </c>
-      <c r="E348" s="10" t="n"/>
-      <c r="F348" s="10" t="n"/>
+      <c r="E348" s="10" t="inlineStr"/>
+      <c r="F348" s="10" t="inlineStr"/>
     </row>
     <row r="349" ht="80" customHeight="1">
       <c r="A349" s="10" t="inlineStr">
@@ -17696,12 +17696,12 @@
       </c>
       <c r="E349" s="10" t="inlineStr">
         <is>
-          <t>천연한방보존제는 생약 중 항균력이 우수한 오배자, 가자, 석곡, 산초를 초음파 방식으로 / 추출하여 조합한 화장품용 천연유래 항균제입니다</t>
+          <t>천연한방보존제는 생약 중 항균력이 우수한 오배자, 가자, 석곡, 산초를 초음파 방식으로 · 추출하여 조합한 화장품용 천연유래 항균제입니다</t>
         </is>
       </c>
       <c r="F349" s="10" t="inlineStr">
         <is>
-          <t>1,2-헥산디올1g / (갈락토미세스 발효여과물의 양을 59.5g으로 줄여주세요.)</t>
+          <t>1,2-헥산디올1g · (갈락토미세스 발효여과물의 양을 59.5g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -17912,7 +17912,7 @@
       </c>
       <c r="E360" s="18" t="inlineStr">
         <is>
-          <t>위의 레시피로 / 미리 만들것.</t>
+          <t>위의 레시피로 · 미리 만들것.</t>
         </is>
       </c>
       <c r="F360" s="18" t="inlineStr">
@@ -17944,12 +17944,12 @@
       </c>
       <c r="E361" s="18" t="inlineStr">
         <is>
-          <t>레드27 0.1g / + 레드6 0.1g</t>
+          <t>레드27 0.1g · + 레드6 0.1g</t>
         </is>
       </c>
       <c r="F361" s="18" t="inlineStr">
         <is>
-          <t>원하는 / 색상</t>
+          <t>원하는 · 색상</t>
         </is>
       </c>
     </row>
@@ -17976,12 +17976,12 @@
       </c>
       <c r="E362" s="18" t="inlineStr">
         <is>
-          <t>넣지 않으면 코코넛향이 은은함 / 강한 향을 원하면 원하는 식향을 추가</t>
+          <t>넣지 않으면 코코넛향이 은은함 · 강한 향을 원하면 원하는 식향을 추가</t>
         </is>
       </c>
       <c r="F362" s="18" t="inlineStr">
         <is>
-          <t>원하는 / EO</t>
+          <t>원하는 · EO</t>
         </is>
       </c>
     </row>
@@ -18148,7 +18148,7 @@
           <t>식약처 미백 기능성 인증, 나이아신아마이드, 호호바오일, 코포아수버터, 트레할로스, 알로에베라겔, 알란토인, 히아루론산 등</t>
         </is>
       </c>
-      <c r="F371" s="10" t="n"/>
+      <c r="F371" s="10" t="inlineStr"/>
     </row>
     <row r="372" ht="64" customHeight="1">
       <c r="A372" s="10" t="inlineStr">
@@ -18173,7 +18173,7 @@
       </c>
       <c r="E372" s="10" t="inlineStr">
         <is>
-          <t>기미 개선효과가 뛰어난 트라넥사민산(을 / 펩타이드 말단에 합성으로 / 도입시킨 비타민 펩타이드)</t>
+          <t>기미 개선효과가 뛰어난 트라넥사민산(을 · 펩타이드 말단에 합성으로 · 도입시킨 비타민 펩타이드)</t>
         </is>
       </c>
       <c r="F372" s="10" t="inlineStr">
@@ -18205,12 +18205,12 @@
       </c>
       <c r="E373" s="10" t="inlineStr">
         <is>
-          <t>EGF, FGF, IGF, TGF / 복합 펩타이드</t>
+          <t>EGF, FGF, IGF, TGF · 복합 펩타이드</t>
         </is>
       </c>
       <c r="F373" s="10" t="inlineStr">
         <is>
-          <t>아세틸헥사, / 씨네이크펩타이드, 화이트펩타이드 등</t>
+          <t>아세틸헥사 · 씨네이크펩타이드, 화이트펩타이드 등</t>
         </is>
       </c>
     </row>
@@ -18237,7 +18237,7 @@
       </c>
       <c r="E374" s="10" t="inlineStr">
         <is>
-          <t>네롤리, 일랑일랑, 버가못FCF, / 프랑킨센스 EO 블렌딩오일</t>
+          <t>네롤리, 일랑일랑, 버가못FCF · 프랑킨센스 EO 블렌딩오일</t>
         </is>
       </c>
       <c r="F374" s="10" t="inlineStr">
@@ -18384,7 +18384,7 @@
       </c>
       <c r="F383" s="18" t="inlineStr">
         <is>
-          <t>유기농 카밍 5솔루션, / 캐모마일, 카렌듈라 등.</t>
+          <t>유기농 카밍 5솔루션 · 캐모마일, 카렌듈라 등.</t>
         </is>
       </c>
     </row>
@@ -18411,10 +18411,10 @@
       </c>
       <c r="E384" s="18" t="inlineStr">
         <is>
-          <t>미백기능성 식약처 인증, / 텍스처가 통통한 수분크림 / 히아루론산, 호호바오일, / 알란토인 등 함유</t>
-        </is>
-      </c>
-      <c r="F384" s="18" t="n"/>
+          <t>미백기능성 식약처 인증 · 텍스처가 통통한 수분크림 · 히아루론산, 호호바오일 · 알란토인 등 함유</t>
+        </is>
+      </c>
+      <c r="F384" s="18" t="inlineStr"/>
     </row>
     <row r="385" ht="32" customHeight="1">
       <c r="A385" s="18" t="inlineStr">
@@ -18439,7 +18439,7 @@
       </c>
       <c r="E385" s="18" t="inlineStr">
         <is>
-          <t>네롤리, 프랑킨센스, / 일랑일랑, 버가못FCF 위한 블렌딩</t>
+          <t>네롤리, 프랑킨센스 · 일랑일랑, 버가못FCF 위한 블렌딩</t>
         </is>
       </c>
       <c r="F385" s="18" t="inlineStr">
@@ -18593,12 +18593,12 @@
       </c>
       <c r="E394" s="10" t="inlineStr">
         <is>
-          <t>오렌지꽃수, 알란토인, / 오렌지꽃에센셜오일, 민감,</t>
+          <t>오렌지꽃수, 알란토인 · 오렌지꽃에센셜오일, 민감</t>
         </is>
       </c>
       <c r="F394" s="10" t="inlineStr">
         <is>
-          <t>로즈플라워겔, / 알로에겔</t>
+          <t>로즈플라워겔 · 알로에겔</t>
         </is>
       </c>
     </row>
@@ -18657,10 +18657,10 @@
       </c>
       <c r="E396" s="10" t="inlineStr">
         <is>
-          <t>알로에, 참마, 미역, / 흰목이버섯추출물 / 수딩, 항산화, 항염, 모이스춰</t>
-        </is>
-      </c>
-      <c r="F396" s="10" t="n"/>
+          <t>알로에, 참마, 미역 · 흰목이버섯추출물 · 수딩, 항산화, 항염, 모이스춰</t>
+        </is>
+      </c>
+      <c r="F396" s="10" t="inlineStr"/>
     </row>
     <row r="397" ht="48" customHeight="1">
       <c r="A397" s="10" t="inlineStr">
@@ -18690,7 +18690,7 @@
       </c>
       <c r="F397" s="10" t="inlineStr">
         <is>
-          <t>다중)히아루론산, 에코보습제 / 글리세린 등</t>
+          <t>다중)히아루론산, 에코보습제 · 글리세린 등</t>
         </is>
       </c>
     </row>
@@ -18722,7 +18722,7 @@
       </c>
       <c r="F398" s="10" t="inlineStr">
         <is>
-          <t>1,2-헥산디올2g / (캐모마일워터의 양을 35g으로 줄여주세요.)</t>
+          <t>1,2-헥산디올2g · (캐모마일워터의 양을 35g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -18874,12 +18874,12 @@
       </c>
       <c r="E407" s="18" t="inlineStr">
         <is>
-          <t>동백, 아르간, 마카다미아넛, / 스윗 아몬드, 피마자, 비타민E 등 / 밤 레시피 최적의 / 고급 식물성 오일 블렌딩</t>
+          <t>동백, 아르간, 마카다미아넛 · 스윗 아몬드, 피마자, 비타민E 등 · 밤 레시피 최적의 · 고급 식물성 오일 블렌딩</t>
         </is>
       </c>
       <c r="F407" s="18" t="inlineStr">
         <is>
-          <t>멀티오일베이스 / 또는 원하는 오일</t>
+          <t>멀티오일베이스 · 또는 원하는 오일</t>
         </is>
       </c>
     </row>
@@ -18906,7 +18906,7 @@
       </c>
       <c r="E408" s="18" t="inlineStr">
         <is>
-          <t>식물성 왁스, 경화제,</t>
+          <t>식물성 왁스, 경화제</t>
         </is>
       </c>
       <c r="F408" s="18" t="inlineStr">
@@ -18938,12 +18938,12 @@
       </c>
       <c r="E409" s="18" t="inlineStr">
         <is>
-          <t>레몬, 레몬글라스, 로즈우드 / 에센셜오일 블렌딩,</t>
+          <t>레몬, 레몬글라스, 로즈우드 · 에센셜오일 블렌딩</t>
         </is>
       </c>
       <c r="F409" s="18" t="inlineStr">
         <is>
-          <t>원하는 / 에센셜오일</t>
+          <t>원하는 · 에센셜오일</t>
         </is>
       </c>
     </row>
@@ -19089,10 +19089,10 @@
       </c>
       <c r="E418" s="10" t="inlineStr">
         <is>
-          <t>수분자석 우레아, 각질연화, / EWG 1등급, 하이드록실에틸 우레아</t>
-        </is>
-      </c>
-      <c r="F418" s="10" t="n"/>
+          <t>수분자석 우레아, 각질연화 · EWG 1등급, 하이드록실에틸 우레아</t>
+        </is>
+      </c>
+      <c r="F418" s="10" t="inlineStr"/>
     </row>
     <row r="419" ht="32" customHeight="1">
       <c r="A419" s="10" t="inlineStr">
@@ -19117,10 +19117,10 @@
       </c>
       <c r="E419" s="10" t="inlineStr">
         <is>
-          <t>식약처 인증 미백기능성, / 24시 수분테스트 완료</t>
-        </is>
-      </c>
-      <c r="F419" s="10" t="n"/>
+          <t>식약처 인증 미백기능성 · 24시 수분테스트 완료</t>
+        </is>
+      </c>
+      <c r="F419" s="10" t="inlineStr"/>
     </row>
     <row r="420" ht="48" customHeight="1">
       <c r="A420" s="10" t="inlineStr">
@@ -19145,12 +19145,12 @@
       </c>
       <c r="E420" s="10" t="inlineStr">
         <is>
-          <t>네롤리, 버가못FCF, 프랑킨센스EO / 브라이트닝에 도움주는 에센셜 블렌딩</t>
+          <t>네롤리, 버가못FCF, 프랑킨센스EO · 브라이트닝에 도움주는 에센셜 블렌딩</t>
         </is>
       </c>
       <c r="F420" s="10" t="inlineStr">
         <is>
-          <t>원하는 / 에센셜오일</t>
+          <t>원하는 · 에센셜오일</t>
         </is>
       </c>
     </row>
@@ -19182,7 +19182,7 @@
       </c>
       <c r="F421" s="10" t="inlineStr">
         <is>
-          <t>4GF, 이데베논, / 트라넥삼산, 갈락토, 비피다 등</t>
+          <t>4GF, 이데베논 · 트라넥삼산, 갈락토, 비피다 등</t>
         </is>
       </c>
     </row>
@@ -19328,12 +19328,12 @@
       </c>
       <c r="E430" s="18" t="inlineStr">
         <is>
-          <t>동백, 아르간, 마카다미아넛, / 스윗 아몬드, 피마자, 비타민E 등 / 밤 레시피 최적의고급 식물성 오일 블렌딩</t>
+          <t>동백, 아르간, 마카다미아넛 · 스윗 아몬드, 피마자, 비타민E 등 · 밤 레시피 최적의고급 식물성 오일 블렌딩</t>
         </is>
       </c>
       <c r="F430" s="18" t="inlineStr">
         <is>
-          <t>멀티오일베이스 / 또는 원하는 오일</t>
+          <t>멀티오일베이스 · 또는 원하는 오일</t>
         </is>
       </c>
     </row>
@@ -19392,7 +19392,7 @@
       </c>
       <c r="E432" s="18" t="inlineStr">
         <is>
-          <t>기호에 따라 양조절 가능, / 박하오일</t>
+          <t>기호에 따라 양조절 가능 · 박하오일</t>
         </is>
       </c>
       <c r="F432" s="18" t="inlineStr">
@@ -19588,7 +19588,7 @@
           <t>비타민나무열매추출물, 유자추출물, 오미자추출물 등 피부톤 개선에 탁월한 성분을 최적의 배합</t>
         </is>
       </c>
-      <c r="F442" s="10" t="n"/>
+      <c r="F442" s="10" t="inlineStr"/>
     </row>
     <row r="443" ht="48" customHeight="1">
       <c r="A443" s="10" t="inlineStr">
@@ -19613,12 +19613,12 @@
       </c>
       <c r="E443" s="10" t="inlineStr">
         <is>
-          <t>비타민성분이 함유된 펩타이드, / 화이트 원료.</t>
+          <t>비타민성분이 함유된 펩타이드 · 화이트 원료.</t>
         </is>
       </c>
       <c r="F443" s="10" t="inlineStr">
         <is>
-          <t>노화주름 관리를 원하면 EGF, FGF로 / 대체가능</t>
+          <t>노화주름 관리를 원하면 EGF, FGF로 · 대체가능</t>
         </is>
       </c>
     </row>
@@ -19757,7 +19757,7 @@
           <t>히비스커스꽃추출물, 동백꽃추출물, 샤프란꽃추출물 등 주름개선에 탁월한 성분을 최적의 배합</t>
         </is>
       </c>
-      <c r="F452" s="18" t="n"/>
+      <c r="F452" s="18" t="inlineStr"/>
     </row>
     <row r="453" ht="32" customHeight="1">
       <c r="A453" s="18" t="inlineStr">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="E453" s="18" t="inlineStr">
         <is>
-          <t>EGF, FGF, IGF, TGF / 복합 펩타이드</t>
+          <t>EGF, FGF, IGF, TGF · 복합 펩타이드</t>
         </is>
       </c>
       <c r="F453" s="18" t="inlineStr">
@@ -19943,7 +19943,7 @@
           <t>병풀추출물(센텔라아시아티카), 녹차추출물, 로즈마리잎추출물 등 피부 진정과 회복에 탁월한 성분을 최적의 배합</t>
         </is>
       </c>
-      <c r="F462" s="10" t="n"/>
+      <c r="F462" s="10" t="inlineStr"/>
     </row>
     <row r="463" ht="80" customHeight="1">
       <c r="A463" s="10" t="inlineStr">
@@ -19968,7 +19968,7 @@
       </c>
       <c r="E463" s="10" t="inlineStr">
         <is>
-          <t>테트라펩타이드-44, 쿠퍼펩타이드-1, / 헥사펩타이드-9, 화이트펩타이드-23로 / 구성된 4가지 복합 펩타이드,1000ppm / 트러블관리에 도움</t>
+          <t>테트라펩타이드-44, 쿠퍼펩타이드-1 · 헥사펩타이드-9, 화이트펩타이드-23로 · 구성된 4가지 복합 펩타이드,1000ppm · 트러블관리에 도움</t>
         </is>
       </c>
       <c r="F463" s="10" t="inlineStr">
@@ -20147,7 +20147,7 @@
       </c>
       <c r="E473" s="18" t="inlineStr">
         <is>
-          <t>칸데릴라왁스+ 밀랍 / (단단함과 윤기 적절한 조화)</t>
+          <t>칸데릴라왁스+ 밀랍 · (단단함과 윤기 적절한 조화)</t>
         </is>
       </c>
       <c r="F473" s="18" t="inlineStr">
@@ -20380,7 +20380,7 @@
           <t>병풀추출물(센텔라아시아티카), 녹차추출물, 로즈마리잎추출물 등 피부 진정과 회복에 탁월한 성분을 최적의 배합</t>
         </is>
       </c>
-      <c r="F484" s="10" t="n"/>
+      <c r="F484" s="10" t="inlineStr"/>
     </row>
     <row r="485" ht="32" customHeight="1">
       <c r="A485" s="10" t="inlineStr">
@@ -20405,7 +20405,7 @@
       </c>
       <c r="E485" s="10" t="inlineStr">
         <is>
-          <t>약모밀, 빠른 진정효과, / 각종 피부트러블, 피부 개선에 사용</t>
+          <t>약모밀, 빠른 진정효과 · 각종 피부트러블, 피부 개선에 사용</t>
         </is>
       </c>
       <c r="F485" s="10" t="inlineStr">
@@ -20586,7 +20586,7 @@
       </c>
       <c r="F495" s="18" t="inlineStr">
         <is>
-          <t>비피다, / 사카로미세스발효여과물</t>
+          <t>비피다 · 사카로미세스발효여과물</t>
         </is>
       </c>
     </row>
@@ -20613,7 +20613,7 @@
       </c>
       <c r="E496" s="18" t="inlineStr">
         <is>
-          <t>EGF, FGF, IGF, TGF / 복합 펩타이드</t>
+          <t>EGF, FGF, IGF, TGF · 복합 펩타이드</t>
         </is>
       </c>
       <c r="F496" s="18" t="inlineStr">
@@ -20645,12 +20645,12 @@
       </c>
       <c r="E497" s="18" t="inlineStr">
         <is>
-          <t>로먼 캐모마일, 라벤더, 만다린 / 복합 블렌딩오일</t>
+          <t>로먼 캐모마일, 라벤더, 만다린 · 복합 블렌딩오일</t>
         </is>
       </c>
       <c r="F497" s="18" t="inlineStr">
         <is>
-          <t>원하는 / 에센셜오일</t>
+          <t>원하는 · 에센셜오일</t>
         </is>
       </c>
     </row>
@@ -20799,7 +20799,7 @@
       </c>
       <c r="E506" s="10" t="inlineStr">
         <is>
-          <t>병풀 핵심성분 4가지 함유, / 보습, 재생효과 덱스판테놀 함유</t>
+          <t>병풀 핵심성분 4가지 함유 · 보습, 재생효과 덱스판테놀 함유</t>
         </is>
       </c>
       <c r="F506" s="10" t="inlineStr">
@@ -20831,7 +20831,7 @@
       </c>
       <c r="E507" s="10" t="inlineStr">
         <is>
-          <t>피부장벽강화, 면역력강화 / 3가지 유산균</t>
+          <t>피부장벽강화, 면역력강화 · 3가지 유산균</t>
         </is>
       </c>
       <c r="F507" s="10" t="inlineStr">
@@ -20895,12 +20895,12 @@
       </c>
       <c r="E509" s="10" t="inlineStr">
         <is>
-          <t>네롤리, 일링일랑, 프랑킨센스, / 버가못FCF 복합 블렌딩오일</t>
+          <t>네롤리, 일링일랑, 프랑킨센스 · 버가못FCF 복합 블렌딩오일</t>
         </is>
       </c>
       <c r="F509" s="10" t="inlineStr">
         <is>
-          <t>원하는 / 에센셜오일</t>
+          <t>원하는 · 에센셜오일</t>
         </is>
       </c>
     </row>
@@ -21078,7 +21078,7 @@
       </c>
       <c r="E519" s="18" t="inlineStr">
         <is>
-          <t>진정부터 자국케어까지 / 4가지 펩타이드 복합</t>
+          <t>진정부터 자국케어까지 · 4가지 펩타이드 복합</t>
         </is>
       </c>
       <c r="F519" s="18" t="inlineStr">
@@ -21142,12 +21142,12 @@
       </c>
       <c r="E521" s="18" t="inlineStr">
         <is>
-          <t>티트리, 버가못FCF, 라벤더EO / 복합 블렌딩오일</t>
+          <t>티트리, 버가못FCF, 라벤더EO · 복합 블렌딩오일</t>
         </is>
       </c>
       <c r="F521" s="18" t="inlineStr">
         <is>
-          <t>라벤더, 티트리 / 에센셜오일</t>
+          <t>라벤더, 티트리 · 에센셜오일</t>
         </is>
       </c>
     </row>
@@ -21294,10 +21294,10 @@
       </c>
       <c r="E530" s="10" t="inlineStr">
         <is>
-          <t>슈퍼시카4, 덱스판테놀, / 내추럴 바세린 / 함유 / 강력 보습&amp;진정</t>
-        </is>
-      </c>
-      <c r="F530" s="10" t="n"/>
+          <t>슈퍼시카4, 덱스판테놀 · 내추럴 바세린 · 함유 · 강력 보습&amp;진정</t>
+        </is>
+      </c>
+      <c r="F530" s="10" t="inlineStr"/>
     </row>
     <row r="531" ht="48" customHeight="1">
       <c r="A531" s="10" t="inlineStr">
@@ -21322,7 +21322,7 @@
       </c>
       <c r="E531" s="10" t="inlineStr">
         <is>
-          <t>락토바실러스 람노서스, 비피다발효용해물, 락토코쿠스발효용해물 / 3가지 유산균 복합 성분</t>
+          <t>락토바실러스 람노서스, 비피다발효용해물, 락토코쿠스발효용해물 · 3가지 유산균 복합 성분</t>
         </is>
       </c>
       <c r="F531" s="10" t="inlineStr">
@@ -21354,7 +21354,7 @@
       </c>
       <c r="E532" s="10" t="inlineStr">
         <is>
-          <t>약모밀, 빠른 진정효과, / 각종 피부트러블, 피부 개선에 사용</t>
+          <t>약모밀, 빠른 진정효과 · 각종 피부트러블, 피부 개선에 사용</t>
         </is>
       </c>
       <c r="F532" s="10" t="inlineStr">
@@ -21386,12 +21386,12 @@
       </c>
       <c r="E533" s="10" t="inlineStr">
         <is>
-          <t>라벤더. 만다린 / 로먼캐모마일 에센셜오일, / 민감피부를 위한 블렌딩</t>
+          <t>라벤더. 만다린 · 로먼캐모마일 에센셜오일 · 민감피부를 위한 블렌딩</t>
         </is>
       </c>
       <c r="F533" s="10" t="inlineStr">
         <is>
-          <t>로먼캐모마일, / 네롤리에센셜오일</t>
+          <t>로먼캐모마일 · 네롤리에센셜오일</t>
         </is>
       </c>
     </row>
@@ -21530,10 +21530,10 @@
       </c>
       <c r="E542" s="18" t="inlineStr">
         <is>
-          <t>슈퍼시카4, 덱스판테놀, / 내추럴 바세린 / 함유 / 강력 보습&amp;진정</t>
-        </is>
-      </c>
-      <c r="F542" s="18" t="n"/>
+          <t>슈퍼시카4, 덱스판테놀 · 내추럴 바세린 · 함유 · 강력 보습&amp;진정</t>
+        </is>
+      </c>
+      <c r="F542" s="18" t="inlineStr"/>
     </row>
     <row r="543" ht="16" customHeight="1">
       <c r="A543" s="18" t="inlineStr">
@@ -21595,7 +21595,7 @@
       </c>
       <c r="F544" s="18" t="inlineStr">
         <is>
-          <t>스쿠알란, / 보르피린</t>
+          <t>스쿠알란 · 보르피린</t>
         </is>
       </c>
     </row>
@@ -21627,7 +21627,7 @@
       </c>
       <c r="F545" s="18" t="inlineStr">
         <is>
-          <t>만다린, / 스윗오렌지에센셜오일</t>
+          <t>만다린 · 스윗오렌지에센셜오일</t>
         </is>
       </c>
     </row>
@@ -21773,10 +21773,10 @@
       </c>
       <c r="E554" s="10" t="inlineStr">
         <is>
-          <t>슈퍼시카4, 덱스판테놀, / 내추럴 바세린 / 함유 / 강력 보습&amp;진정</t>
-        </is>
-      </c>
-      <c r="F554" s="10" t="n"/>
+          <t>슈퍼시카4, 덱스판테놀 · 내추럴 바세린 · 함유 · 강력 보습&amp;진정</t>
+        </is>
+      </c>
+      <c r="F554" s="10" t="inlineStr"/>
     </row>
     <row r="555" ht="32" customHeight="1">
       <c r="A555" s="10" t="inlineStr">
@@ -21806,7 +21806,7 @@
       </c>
       <c r="F555" s="10" t="inlineStr">
         <is>
-          <t>스쿠알란, / 보르피린</t>
+          <t>스쿠알란 · 보르피린</t>
         </is>
       </c>
     </row>
@@ -21833,12 +21833,12 @@
       </c>
       <c r="E556" s="10" t="inlineStr">
         <is>
-          <t>로즈앱솔루트EO, 로즈제라늄EO, / 로즈우드EO, 프랑킨센스EO / 블렌딩오일</t>
+          <t>로즈앱솔루트EO, 로즈제라늄EO · 로즈우드EO, 프랑킨센스EO · 블렌딩오일</t>
         </is>
       </c>
       <c r="F556" s="10" t="inlineStr">
         <is>
-          <t>로즈제라늄, / 로즈우드에센셜오일</t>
+          <t>로즈제라늄 · 로즈우드에센셜오일</t>
         </is>
       </c>
     </row>
@@ -21977,10 +21977,10 @@
       </c>
       <c r="E565" s="18" t="inlineStr">
         <is>
-          <t>슈퍼시카4, 덱스판테놀, / 내추럴 바세린 / 함유 / 강력 보습&amp;진정</t>
-        </is>
-      </c>
-      <c r="F565" s="18" t="n"/>
+          <t>슈퍼시카4, 덱스판테놀 · 내추럴 바세린 · 함유 · 강력 보습&amp;진정</t>
+        </is>
+      </c>
+      <c r="F565" s="18" t="inlineStr"/>
     </row>
     <row r="566" ht="32" customHeight="1">
       <c r="A566" s="18" t="inlineStr">
@@ -22005,12 +22005,12 @@
       </c>
       <c r="E566" s="18" t="inlineStr">
         <is>
-          <t>보습, / 코포아수버터 리포좀</t>
+          <t>보습 · 코포아수버터 리포좀</t>
         </is>
       </c>
       <c r="F566" s="18" t="inlineStr">
         <is>
-          <t>워터 아르간, / 워터 호호바</t>
+          <t>워터 아르간 · 워터 호호바</t>
         </is>
       </c>
     </row>
@@ -22042,7 +22042,7 @@
       </c>
       <c r="F567" s="18" t="inlineStr">
         <is>
-          <t>스쿠알란, / 보르피린</t>
+          <t>스쿠알란 · 보르피린</t>
         </is>
       </c>
     </row>
@@ -22069,12 +22069,12 @@
       </c>
       <c r="E568" s="18" t="inlineStr">
         <is>
-          <t>네롤리, 버가못FCF 일링일랑, 프랑킨센스, / 복합 블렌딩오일</t>
+          <t>네롤리, 버가못FCF 일링일랑, 프랑킨센스 · 복합 블렌딩오일</t>
         </is>
       </c>
       <c r="F568" s="18" t="inlineStr">
         <is>
-          <t>버가못에센셜오일, / 레몬쥬스블렌딩오일</t>
+          <t>버가못에센셜오일 · 레몬쥬스블렌딩오일</t>
         </is>
       </c>
     </row>
@@ -22225,10 +22225,10 @@
       </c>
       <c r="E577" s="10" t="inlineStr">
         <is>
-          <t>슈퍼시카4, 덱스판테놀, / 내추럴 바세린 / 함유 / 강력 보습&amp;진정</t>
-        </is>
-      </c>
-      <c r="F577" s="10" t="n"/>
+          <t>슈퍼시카4, 덱스판테놀 · 내추럴 바세린 · 함유 · 강력 보습&amp;진정</t>
+        </is>
+      </c>
+      <c r="F577" s="10" t="inlineStr"/>
     </row>
     <row r="578" ht="16" customHeight="1">
       <c r="A578" s="10" t="inlineStr">
@@ -22317,12 +22317,12 @@
       </c>
       <c r="E580" s="10" t="inlineStr">
         <is>
-          <t>레몬, 레몬그라스, 로즈우드 / 에센셜오일 블렌딩</t>
+          <t>레몬, 레몬그라스, 로즈우드 · 에센셜오일 블렌딩</t>
         </is>
       </c>
       <c r="F580" s="10" t="inlineStr">
         <is>
-          <t>버가못, 스윗오렌지 / 에센셜오일</t>
+          <t>버가못, 스윗오렌지 · 에센셜오일</t>
         </is>
       </c>
     </row>
@@ -22462,10 +22462,10 @@
       </c>
       <c r="E589" s="18" t="inlineStr">
         <is>
-          <t>슈퍼시카4, 덱스판테놀, / 내추럴 바세린 / 함유 / 강력 보습&amp;진정</t>
-        </is>
-      </c>
-      <c r="F589" s="18" t="n"/>
+          <t>슈퍼시카4, 덱스판테놀 · 내추럴 바세린 · 함유 · 강력 보습&amp;진정</t>
+        </is>
+      </c>
+      <c r="F589" s="18" t="inlineStr"/>
     </row>
     <row r="590" ht="16" customHeight="1">
       <c r="A590" s="18" t="inlineStr">
@@ -22490,7 +22490,7 @@
       </c>
       <c r="E590" s="18" t="inlineStr">
         <is>
-          <t>금잔화 추출물, / 피부진정</t>
+          <t>금잔화 추출물 · 피부진정</t>
         </is>
       </c>
       <c r="F590" s="18" t="inlineStr">
@@ -22522,12 +22522,12 @@
       </c>
       <c r="E591" s="18" t="inlineStr">
         <is>
-          <t>누룩(천연효모) 발효여과물, / 보습, 탄력, 아미노산, 미네랄, 영양공급</t>
+          <t>누룩(천연효모) 발효여과물 · 보습, 탄력, 아미노산, 미네랄, 영양공급</t>
         </is>
       </c>
       <c r="F591" s="18" t="inlineStr">
         <is>
-          <t>비피다발효용해물, / 사카로미세스발효여과물</t>
+          <t>비피다발효용해물 · 사카로미세스발효여과물</t>
         </is>
       </c>
     </row>
@@ -22554,12 +22554,12 @@
       </c>
       <c r="E592" s="18" t="inlineStr">
         <is>
-          <t>허브의 여왕, / 진정, 재생, 항균</t>
+          <t>허브의 여왕 · 진정, 재생, 항균</t>
         </is>
       </c>
       <c r="F592" s="18" t="inlineStr">
         <is>
-          <t>베베보 / 블렌딩오일</t>
+          <t>베베보 · 블렌딩오일</t>
         </is>
       </c>
     </row>
@@ -22711,10 +22711,10 @@
       </c>
       <c r="E601" s="10" t="inlineStr">
         <is>
-          <t>미백/ 보습 /진정 고기능성 베이스, / (유기농 알로에베라, 호호바오일, 코포아수버터 리포좀, 히아루론산, 알란토인 , 나이아신아마이드 등 함유).</t>
-        </is>
-      </c>
-      <c r="F601" s="10" t="n"/>
+          <t>미백 · 보습 · 진정 고기능성 베이스 · (유기농 알로에베라, 호호바오일, 코포아수버터 리포좀, 히아루론산, 알란토인 , 나이아신아마이드 등 함유).</t>
+        </is>
+      </c>
+      <c r="F601" s="10" t="inlineStr"/>
     </row>
     <row r="602" ht="48" customHeight="1">
       <c r="A602" s="10" t="inlineStr">
@@ -22739,12 +22739,12 @@
       </c>
       <c r="E602" s="10" t="inlineStr">
         <is>
-          <t>상피 재생관여, 농도 1ppm 또는 10ppm 중 택, / 식약처 기준은 10ppm까지 사용가능</t>
+          <t>상피 재생관여, 농도 1ppm 또는 10ppm 중 택 · 식약처 기준은 10ppm까지 사용가능</t>
         </is>
       </c>
       <c r="F602" s="10" t="inlineStr">
         <is>
-          <t>FGF10/1ppm,아세틸헥사펩타이드, 쿠퍼펩타이드 등</t>
+          <t>FGF10 · 1ppm,아세틸헥사펩타이드, 쿠퍼펩타이드 등</t>
         </is>
       </c>
     </row>
@@ -22771,7 +22771,7 @@
       </c>
       <c r="E603" s="10" t="inlineStr">
         <is>
-          <t>진피재생관여,농도 1ppm 또는 10ppm 중 택, / 식약처 기준은 10ppm까지 사용가능</t>
+          <t>진피재생관여,농도 1ppm 또는 10ppm 중 택 · 식약처 기준은 10ppm까지 사용가능</t>
         </is>
       </c>
       <c r="F603" s="10" t="inlineStr">
@@ -22968,7 +22968,7 @@
       </c>
       <c r="E614" s="18" t="inlineStr">
         <is>
-          <t>~10% 함량, 프탈레이트 프리. 취향에 따라 양조절해서 사용가능</t>
+          <t>10% 함량, 프탈레이트 프리. 취향에 따라 양조절해서 사용가능</t>
         </is>
       </c>
       <c r="F614" s="18" t="inlineStr">
@@ -23126,7 +23126,7 @@
           <t>자초근추출물, 호호바오일, 피마자, 해바라기, 스윗아몬드오일, 비타민E 등으로 구성된 오일</t>
         </is>
       </c>
-      <c r="F623" s="10" t="n"/>
+      <c r="F623" s="10" t="inlineStr"/>
     </row>
     <row r="624" ht="32" customHeight="1">
       <c r="A624" s="10" t="inlineStr">
@@ -23183,7 +23183,7 @@
       </c>
       <c r="E625" s="10" t="inlineStr">
         <is>
-          <t>넣지 않으면 코코넛향이 은은함 / 강한 향을 원하면 원하는 식향을 추가</t>
+          <t>넣지 않으면 코코넛향이 은은함 · 강한 향을 원하면 원하는 식향을 추가</t>
         </is>
       </c>
       <c r="F625" s="10" t="inlineStr">
@@ -23247,12 +23247,12 @@
       </c>
       <c r="E627" s="10" t="inlineStr">
         <is>
-          <t>오래가는 보습오일, / 끈적함</t>
+          <t>오래가는 보습오일 · 끈적함</t>
         </is>
       </c>
       <c r="F627" s="10" t="inlineStr">
         <is>
-          <t>비타민E를 피마자오일양 중 일부로 대체,</t>
+          <t>비타민E를 피마자오일양 중 일부로 대체</t>
         </is>
       </c>
     </row>
@@ -23279,7 +23279,7 @@
       </c>
       <c r="E628" s="10" t="inlineStr">
         <is>
-          <t>고보습, / 식물성 유기농 버터</t>
+          <t>고보습 · 식물성 유기농 버터</t>
         </is>
       </c>
       <c r="F628" s="10" t="inlineStr">
@@ -23311,7 +23311,7 @@
       </c>
       <c r="E629" s="10" t="inlineStr">
         <is>
-          <t>넣지 않으면 코코넛향이 은은함 / 강한 향을 원하면 원하는 식향을 추가</t>
+          <t>넣지 않으면 코코넛향이 은은함 · 강한 향을 원하면 원하는 식향을 추가</t>
         </is>
       </c>
       <c r="F629" s="10" t="inlineStr">
@@ -23469,12 +23469,12 @@
       </c>
       <c r="E638" s="18" t="inlineStr">
         <is>
-          <t>식약처 인증 미백기능성, / 24시 수분테스트 완료</t>
-        </is>
-      </c>
-      <c r="F638" s="18" t="n"/>
-    </row>
-    <row r="639" ht="48" customHeight="1">
+          <t>식약처 인증 미백기능성 · 24시 수분테스트 완료</t>
+        </is>
+      </c>
+      <c r="F638" s="18" t="inlineStr"/>
+    </row>
+    <row r="639" ht="32" customHeight="1">
       <c r="A639" s="18" t="inlineStr">
         <is>
           <t>어성초추출물</t>
@@ -23497,7 +23497,7 @@
       </c>
       <c r="E639" s="18" t="inlineStr">
         <is>
-          <t>약모밀, 빠른 진정효과, / 각종 피부 트러블, 피부 개선에 사용</t>
+          <t>약모밀, 빠른 진정효과 · 각종 피부 트러블, 피부 개선에 사용</t>
         </is>
       </c>
       <c r="F639" s="18" t="inlineStr">
@@ -23561,10 +23561,10 @@
       </c>
       <c r="E641" s="18" t="inlineStr">
         <is>
-          <t>천연 항균 물질인 멜리틴함유, / 트러블 피부 개선</t>
-        </is>
-      </c>
-      <c r="F641" s="18" t="n"/>
+          <t>천연 항균 물질인 멜리틴함유 · 트러블 피부 개선</t>
+        </is>
+      </c>
+      <c r="F641" s="18" t="inlineStr"/>
     </row>
     <row r="642" ht="32" customHeight="1">
       <c r="A642" s="18" t="inlineStr">
@@ -23594,7 +23594,7 @@
       </c>
       <c r="F642" s="18" t="inlineStr">
         <is>
-          <t>AC클리어 / 블렌딩오일</t>
+          <t>AC클리어 · 블렌딩오일</t>
         </is>
       </c>
     </row>
@@ -23751,10 +23751,10 @@
       </c>
       <c r="E651" s="10" t="inlineStr">
         <is>
-          <t>슈퍼시카4, 덱스판테놀, / 내추럴 바세린 / 함유 / 강력 보습&amp;진정</t>
-        </is>
-      </c>
-      <c r="F651" s="10" t="n"/>
+          <t>슈퍼시카4, 덱스판테놀 · 내추럴 바세린 · 함유 · 강력 보습&amp;진정</t>
+        </is>
+      </c>
+      <c r="F651" s="10" t="inlineStr"/>
     </row>
     <row r="652" ht="16" customHeight="1">
       <c r="A652" s="10" t="inlineStr">
@@ -23843,12 +23843,12 @@
       </c>
       <c r="E654" s="10" t="inlineStr">
         <is>
-          <t>레몬, 레몬그라스, 로즈우드 / 에센셜오일 블렌딩</t>
+          <t>레몬, 레몬그라스, 로즈우드 · 에센셜오일 블렌딩</t>
         </is>
       </c>
       <c r="F654" s="10" t="inlineStr">
         <is>
-          <t>버가못, 스윗오렌지 / 에센셜오일</t>
+          <t>버가못, 스윗오렌지 · 에센셜오일</t>
         </is>
       </c>
     </row>
@@ -23965,7 +23965,7 @@
         </is>
       </c>
     </row>
-    <row r="663" ht="48" customHeight="1">
+    <row r="663" ht="32" customHeight="1">
       <c r="A663" s="18" t="inlineStr">
         <is>
           <t>시카 판테놀 수딩젤 베이스</t>
@@ -23988,10 +23988,10 @@
       </c>
       <c r="E663" s="18" t="inlineStr">
         <is>
-          <t>슈퍼시카4, 덱스판테놀, / 비타민B5,B3, 오렌지블라썸워터 함유</t>
-        </is>
-      </c>
-      <c r="F663" s="18" t="n"/>
+          <t>슈퍼시카4, 덱스판테놀 · 비타민B5,B3, 오렌지블라썸워터 함유</t>
+        </is>
+      </c>
+      <c r="F663" s="18" t="inlineStr"/>
     </row>
     <row r="664" ht="32" customHeight="1">
       <c r="A664" s="18" t="inlineStr">
@@ -24016,7 +24016,7 @@
       </c>
       <c r="E664" s="18" t="inlineStr">
         <is>
-          <t>약모밀, 빠른 효과, / 각종 트러블피부, / 개선에 사용</t>
+          <t>약모밀, 빠른 효과 · 각종 트러블피부 · 개선에 사용</t>
         </is>
       </c>
       <c r="F664" s="18" t="inlineStr">
@@ -24048,7 +24048,7 @@
       </c>
       <c r="E665" s="18" t="inlineStr">
         <is>
-          <t>아로마 테라피 효과, / 생략 가능</t>
+          <t>아로마 테라피 효과 · 생략 가능</t>
         </is>
       </c>
       <c r="F665" s="18" t="inlineStr">
@@ -24208,7 +24208,7 @@
       </c>
       <c r="F674" s="10" t="inlineStr">
         <is>
-          <t>사용하던 립스틱, / 다양한 색은 / 아래 색조합 참고</t>
+          <t>사용하던 립스틱 · 다양한 색은 · 아래 색조합 참고</t>
         </is>
       </c>
     </row>
@@ -24240,7 +24240,7 @@
       </c>
       <c r="F675" s="10" t="inlineStr">
         <is>
-          <t>멀티오일베이스 / 또는 원하는 오일</t>
+          <t>멀티오일베이스 · 또는 원하는 오일</t>
         </is>
       </c>
     </row>
@@ -24299,7 +24299,7 @@
       </c>
       <c r="E677" s="10" t="inlineStr">
         <is>
-          <t>프랑스 세더마, / 하이드로제네이티드 폴리이소부텐+지모추출물=보르피린, 보르피린 5% 임상실험에서 볼륨 반응 , 지용성 원료. / 열안정성.(80℃에서 4시간 견딤)</t>
+          <t>프랑스 세더마 · 하이드로제네이티드 폴리이소부텐+지모추출물=보르피린, 보르피린 5% 임상실험에서 볼륨 반응 , 지용성 원료. · 열안정성.(80℃에서 4시간 견딤)</t>
         </is>
       </c>
       <c r="F677" s="10" t="inlineStr">
@@ -24331,7 +24331,7 @@
       </c>
       <c r="E678" s="10" t="inlineStr">
         <is>
-          <t>무향을 원하면 생략가능, / 네롤리, 일링일랑, 프랑킨센스, / 버가못FCF 블렌딩</t>
+          <t>무향을 원하면 생략가능 · 네롤리, 일링일랑, 프랑킨센스 · 버가못FCF 블렌딩</t>
         </is>
       </c>
       <c r="F678" s="10" t="inlineStr">
@@ -24491,7 +24491,7 @@
           <t>피부톤 개선 (식약처 미백 기능성 원료 비타민나무열매추출물, 유자추출물, 오미자추출물 등)</t>
         </is>
       </c>
-      <c r="F687" s="18" t="n"/>
+      <c r="F687" s="18" t="inlineStr"/>
     </row>
     <row r="688" ht="48" customHeight="1">
       <c r="A688" s="18" t="inlineStr">
@@ -24519,7 +24519,7 @@
           <t>피부 내부의 재생 신호를 자극하여 콜라겐 생성을 돕는 메신저 펩타이드</t>
         </is>
       </c>
-      <c r="F688" s="18" t="n"/>
+      <c r="F688" s="18" t="inlineStr"/>
     </row>
     <row r="689" ht="64" customHeight="1">
       <c r="A689" s="18" t="inlineStr">
@@ -24547,7 +24547,7 @@
           <t>주름 개선 (식약처 주름개선인증 원료 아데노신, 동백꽃추출물, 히비스커스꽃추출물, 동백꽃추출물, 샤프란꽃추출물 등)</t>
         </is>
       </c>
-      <c r="F689" s="18" t="n"/>
+      <c r="F689" s="18" t="inlineStr"/>
     </row>
     <row r="690" ht="32" customHeight="1">
       <c r="A690" s="18" t="inlineStr">
@@ -24575,7 +24575,7 @@
           <t>피부 진정 (병풀추출물, 녹차추출물, 로즈마리잎추출물 등)</t>
         </is>
       </c>
-      <c r="F690" s="18" t="n"/>
+      <c r="F690" s="18" t="inlineStr"/>
     </row>
     <row r="691" ht="14" customHeight="1">
       <c r="A691" s="13" t="inlineStr">
@@ -24943,7 +24943,7 @@
       </c>
       <c r="E710" s="18" t="inlineStr">
         <is>
-          <t>밤류에 최적화된 8가지 / 식물성오일블렌딩.</t>
+          <t>밤류에 최적화된 8가지 · 식물성오일블렌딩.</t>
         </is>
       </c>
       <c r="F710" s="18" t="inlineStr">
@@ -24975,7 +24975,7 @@
       </c>
       <c r="E711" s="18" t="inlineStr">
         <is>
-          <t>경화제, / 밀랍과 칸데릴라왁스가 반반</t>
+          <t>경화제 · 밀랍과 칸데릴라왁스가 반반</t>
         </is>
       </c>
       <c r="F711" s="18" t="inlineStr">
@@ -25007,7 +25007,7 @@
       </c>
       <c r="E712" s="18" t="inlineStr">
         <is>
-          <t>레몬껍질오일, / 아로마테라피</t>
+          <t>레몬껍질오일 · 아로마테라피</t>
         </is>
       </c>
       <c r="F712" s="18" t="inlineStr">
@@ -25171,7 +25171,7 @@
       </c>
       <c r="E721" s="10" t="inlineStr">
         <is>
-          <t>밤류에 최적화된 8가지 / 식물성오일블렌딩.</t>
+          <t>밤류에 최적화된 8가지 · 식물성오일블렌딩.</t>
         </is>
       </c>
       <c r="F721" s="10" t="inlineStr">
@@ -25203,7 +25203,7 @@
       </c>
       <c r="E722" s="10" t="inlineStr">
         <is>
-          <t>경화제, / 밀랍과 칸데릴라왁스가 반반</t>
+          <t>경화제 · 밀랍과 칸데릴라왁스가 반반</t>
         </is>
       </c>
       <c r="F722" s="10" t="inlineStr">
@@ -25235,7 +25235,7 @@
       </c>
       <c r="E723" s="10" t="inlineStr">
         <is>
-          <t>레몬껍질오일, / 아로마테라피</t>
+          <t>레몬껍질오일 · 아로마테라피</t>
         </is>
       </c>
       <c r="F723" s="10" t="inlineStr">
@@ -25267,12 +25267,12 @@
       </c>
       <c r="E724" s="10" t="inlineStr">
         <is>
-          <t>유칼립튜스잎오일, / 아로마테라피</t>
+          <t>유칼립튜스잎오일 · 아로마테라피</t>
         </is>
       </c>
       <c r="F724" s="10" t="inlineStr">
         <is>
-          <t>제라늄EO, 시나몬EO, / 페파민트EO 등 벌레퇴치효과있는 것</t>
+          <t>제라늄EO, 시나몬EO · 페파민트EO 등 벌레퇴치효과있는 것</t>
         </is>
       </c>
     </row>
@@ -25423,10 +25423,10 @@
       </c>
       <c r="E733" s="18" t="inlineStr">
         <is>
-          <t>슈퍼시카4, 덱스판테놀, / 비타민B5, B3, 오렌지블라썸워터 함유</t>
-        </is>
-      </c>
-      <c r="F733" s="18" t="n"/>
+          <t>슈퍼시카4, 덱스판테놀 · 비타민B5, B3, 오렌지블라썸워터 함유</t>
+        </is>
+      </c>
+      <c r="F733" s="18" t="inlineStr"/>
     </row>
     <row r="734" ht="32" customHeight="1">
       <c r="A734" s="18" t="inlineStr">
@@ -25451,12 +25451,12 @@
       </c>
       <c r="E734" s="18" t="inlineStr">
         <is>
-          <t>수분, 영양, / 7가지 유기농 과일/야채 추출물</t>
+          <t>수분, 영양 · 7가지 유기농 과일 · 야채 추출물</t>
         </is>
       </c>
       <c r="F734" s="18" t="inlineStr">
         <is>
-          <t>유기농 / 브라이트닝 / 솔루션</t>
+          <t>유기농 · 브라이트닝 · 솔루션</t>
         </is>
       </c>
     </row>
@@ -25483,12 +25483,12 @@
       </c>
       <c r="E735" s="18" t="inlineStr">
         <is>
-          <t>진정, 고농축 허브오일, / 아로마테라피</t>
+          <t>진정, 고농축 허브오일 · 아로마테라피</t>
         </is>
       </c>
       <c r="F735" s="18" t="inlineStr">
         <is>
-          <t>원하는 / 에센셜오일</t>
+          <t>원하는 · 에센셜오일</t>
         </is>
       </c>
     </row>
@@ -25634,7 +25634,7 @@
       </c>
       <c r="E744" s="10" t="inlineStr">
         <is>
-          <t>미백 주름 개선 기능성 / 나이아신아미이드, 아데노신, 마데카소사이드, 아시아티코사이드, 마데카식애씨드, 아시아틱애씨드, 덱스판테놀 등</t>
+          <t>미백 주름 개선 기능성 · 나이아신아미이드, 아데노신, 마데카소사이드, 아시아티코사이드, 마데카식애씨드, 아시아틱애씨드, 덱스판테놀 등</t>
         </is>
       </c>
       <c r="F744" s="10" t="inlineStr">
@@ -25669,7 +25669,7 @@
           <t>연어DNA, 항염, 재생</t>
         </is>
       </c>
-      <c r="F745" s="10" t="n"/>
+      <c r="F745" s="10" t="inlineStr"/>
     </row>
     <row r="746" ht="14" customHeight="1">
       <c r="A746" s="13" t="inlineStr">
@@ -25812,10 +25812,10 @@
       </c>
       <c r="E754" s="18" t="inlineStr">
         <is>
-          <t>슈퍼시카4, 덱스판테놀, / 내추럴 바세린 / 함유 / 강력 보습&amp;진정</t>
-        </is>
-      </c>
-      <c r="F754" s="18" t="n"/>
+          <t>슈퍼시카4, 덱스판테놀 · 내추럴 바세린 · 함유 · 강력 보습&amp;진정</t>
+        </is>
+      </c>
+      <c r="F754" s="18" t="inlineStr"/>
     </row>
     <row r="755" ht="48" customHeight="1">
       <c r="A755" s="18" t="inlineStr">
@@ -25840,7 +25840,7 @@
       </c>
       <c r="E755" s="18" t="inlineStr">
         <is>
-          <t>락토바실러스 람노서스, 비피다발효용해물, 락토코쿠스발효용해물 / 3가지 유산균 복합 성분</t>
+          <t>락토바실러스 람노서스, 비피다발효용해물, 락토코쿠스발효용해물 · 3가지 유산균 복합 성분</t>
         </is>
       </c>
       <c r="F755" s="18" t="inlineStr">
@@ -25872,7 +25872,7 @@
       </c>
       <c r="E756" s="18" t="inlineStr">
         <is>
-          <t>약모밀, 빠른 진정효과, / 각종 피부트러블, 피부 개선에 사용</t>
+          <t>약모밀, 빠른 진정효과 · 각종 피부트러블, 피부 개선에 사용</t>
         </is>
       </c>
       <c r="F756" s="18" t="inlineStr">
@@ -25904,12 +25904,12 @@
       </c>
       <c r="E757" s="18" t="inlineStr">
         <is>
-          <t>라벤더. 만다린 / 로먼캐모마일 에센셜오일, / 민감피부를 위한 블렌딩</t>
+          <t>라벤더. 만다린 · 로먼캐모마일 에센셜오일 · 민감피부를 위한 블렌딩</t>
         </is>
       </c>
       <c r="F757" s="18" t="inlineStr">
         <is>
-          <t>로먼캐모마일, / 네롤리에센셜오일</t>
+          <t>로먼캐모마일 · 네롤리에센셜오일</t>
         </is>
       </c>
     </row>
@@ -26127,7 +26127,7 @@
       </c>
       <c r="F768" s="10" t="inlineStr">
         <is>
-          <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
+          <t>올리브유화왁스4g · (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
@@ -26157,7 +26157,7 @@
           <t>유화 보조제</t>
         </is>
       </c>
-      <c r="F769" s="10" t="n"/>
+      <c r="F769" s="10" t="inlineStr"/>
     </row>
     <row r="770" ht="16" customHeight="1">
       <c r="A770" s="10" t="inlineStr">
@@ -26249,7 +26249,7 @@
           <t>실제 피부 각질층 아미노산 구성과 유사한 17가지 아미노산, 보습·톤오버 유도·재생·톤업</t>
         </is>
       </c>
-      <c r="F772" s="10" t="n"/>
+      <c r="F772" s="10" t="inlineStr"/>
     </row>
     <row r="773" ht="32" customHeight="1">
       <c r="A773" s="10" t="inlineStr">
@@ -26274,10 +26274,10 @@
       </c>
       <c r="E773" s="10" t="inlineStr">
         <is>
-          <t>저분자 콜라겐 + 히아루론산 / 피부 온도에 녹는 실 콜라겐</t>
-        </is>
-      </c>
-      <c r="F773" s="10" t="n"/>
+          <t>저분자 콜라겐 + 히아루론산 · 피부 온도에 녹는 실 콜라겐</t>
+        </is>
+      </c>
+      <c r="F773" s="10" t="inlineStr"/>
     </row>
     <row r="774" ht="32" customHeight="1">
       <c r="A774" s="10" t="inlineStr">
@@ -26302,7 +26302,7 @@
       </c>
       <c r="E774" s="10" t="inlineStr">
         <is>
-          <t>비타민B3, / 식약처 기능성 고시원료</t>
+          <t>비타민B3 · 식약처 기능성 고시원료</t>
         </is>
       </c>
       <c r="F774" s="10" t="inlineStr">
@@ -26339,7 +26339,7 @@
       </c>
       <c r="F775" s="10" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
@@ -26366,7 +26366,7 @@
       </c>
       <c r="E776" s="10" t="inlineStr">
         <is>
-          <t>불가리아 다마스크 / 장미수 함유 / 점증, 수분공급, 진정</t>
+          <t>불가리아 다마스크 · 장미수 함유 · 점증, 수분공급, 진정</t>
         </is>
       </c>
       <c r="F776" s="10" t="inlineStr">
@@ -26519,7 +26519,7 @@
       </c>
       <c r="E785" s="18" t="inlineStr">
         <is>
-          <t>미백 주름 개선 기능성 / 나이아신아미이드, 아데노신, 마데카소사이드, 아시아티코사이드, 마데카식애씨드, 아시아틱애씨드, 덱스판테놀 등</t>
+          <t>미백 주름 개선 기능성 · 나이아신아미이드, 아데노신, 마데카소사이드, 아시아티코사이드, 마데카식애씨드, 아시아틱애씨드, 덱스판테놀 등</t>
         </is>
       </c>
       <c r="F785" s="18" t="inlineStr">
@@ -26586,7 +26586,7 @@
           <t>미백효과, 항산화 효과</t>
         </is>
       </c>
-      <c r="F787" s="18" t="n"/>
+      <c r="F787" s="18" t="inlineStr"/>
     </row>
     <row r="788" ht="14" customHeight="1">
       <c r="A788" s="13" t="inlineStr">
@@ -26746,10 +26746,10 @@
       </c>
       <c r="E796" s="10" t="inlineStr">
         <is>
-          <t>식약처 인증 미백기능성, / 24시간 수분 테스트 완료. / 나이아신아미이드, 워터호호바 함유</t>
-        </is>
-      </c>
-      <c r="F796" s="10" t="n"/>
+          <t>식약처 인증 미백기능성 · 24시간 수분 테스트 완료. · 나이아신아미이드, 워터호호바 함유</t>
+        </is>
+      </c>
+      <c r="F796" s="10" t="inlineStr"/>
     </row>
     <row r="797" ht="48" customHeight="1">
       <c r="A797" s="10" t="inlineStr">
@@ -26774,10 +26774,10 @@
       </c>
       <c r="E797" s="10" t="inlineStr">
         <is>
-          <t>비타민C의 장점은 살리고 단점은 보완, / 식약처 미백 고시 원료, 미백, 탄력</t>
-        </is>
-      </c>
-      <c r="F797" s="10" t="n"/>
+          <t>비타민C의 장점은 살리고 단점은 보완 · 식약처 미백 고시 원료, 미백, 탄력</t>
+        </is>
+      </c>
+      <c r="F797" s="10" t="inlineStr"/>
     </row>
     <row r="798" ht="32" customHeight="1">
       <c r="A798" s="10" t="inlineStr">
@@ -26955,12 +26955,12 @@
       </c>
       <c r="E807" s="18" t="inlineStr">
         <is>
-          <t>가벼운 보습 / 로즈힙, 유기농 호호바, / 스쿠알란,녹차씨, / 동백, 비타민E,,끈적이지 않은 보습, / 봄,가을 강력추천</t>
+          <t>가벼운 보습 · 로즈힙, 유기농 호호바 · 스쿠알란,녹차씨 · 동백, 비타민E,,끈적이지 않은 보습 · 봄,가을 강력추천</t>
         </is>
       </c>
       <c r="F807" s="18" t="inlineStr">
         <is>
-          <t>멀티오일베이스 / 또는 원하는 오일</t>
+          <t>멀티오일베이스 · 또는 원하는 오일</t>
         </is>
       </c>
     </row>
@@ -26992,7 +26992,7 @@
       </c>
       <c r="F808" s="18" t="inlineStr">
         <is>
-          <t>밀랍 또는 / 칸데릴라왁스 단독</t>
+          <t>밀랍 또는 · 칸데릴라왁스 단독</t>
         </is>
       </c>
     </row>
@@ -27019,7 +27019,7 @@
       </c>
       <c r="E809" s="18" t="inlineStr">
         <is>
-          <t>9% 함량, 지모추출, / 지방증식 볼륨업</t>
+          <t>9% 함량, 지모추출 · 지방증식 볼륨업</t>
         </is>
       </c>
       <c r="F809" s="18" t="inlineStr">
@@ -27083,12 +27083,12 @@
       </c>
       <c r="E811" s="18" t="inlineStr">
         <is>
-          <t>로즈앱솔루트, 로즈제라늄, / 로즈우드, 버가못FCF, / 프랑킨센스에센셜오일 블렌딩</t>
+          <t>로즈앱솔루트, 로즈제라늄 · 로즈우드, 버가못FCF · 프랑킨센스에센셜오일 블렌딩</t>
         </is>
       </c>
       <c r="F811" s="18" t="inlineStr">
         <is>
-          <t>브라이트닝 / 블랜딩오일 등</t>
+          <t>브라이트닝 · 블랜딩오일 등</t>
         </is>
       </c>
     </row>
